--- a/Progress Tracker.xlsx
+++ b/Progress Tracker.xlsx
@@ -5,17 +5,20 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/will/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/will/Desktop/Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:11_{E02E8327-5EE5-1048-9987-DA1D00F436C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB923163-FCB4-A04C-92F7-E7C4937C89C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Project schedule" sheetId="11" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="13" r:id="rId2"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId3"/>
+  </externalReferences>
   <definedNames>
     <definedName name="Display_Week">'Project schedule'!$P$2</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Project schedule'!$4:$6</definedName>
@@ -46,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="78">
   <si>
     <t>PROGRESS</t>
   </si>
@@ -277,6 +280,9 @@
   </si>
   <si>
     <t>Joe Lindley</t>
+  </si>
+  <si>
+    <t>Actual no. Sessions</t>
   </si>
 </sst>
 </file>
@@ -1274,6 +1280,233 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="14" fontId="13" fillId="3" borderId="6" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="3" borderId="7" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="4" borderId="5" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="5" borderId="8" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="10" borderId="9" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="7" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="8" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="9" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="17" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="18" xfId="12" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="10" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="10" borderId="18" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="13" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="13" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="13" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="22" xfId="12" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="14" borderId="23" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="14" borderId="23" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="14" borderId="24" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="25" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="14" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="14" borderId="26" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="14" borderId="27" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="28" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="14" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="14" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="14" borderId="29" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="25" xfId="12" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="18" borderId="30" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="18" borderId="30" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="18" borderId="31" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="32" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="33" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="18" borderId="34" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="18" borderId="35" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="18" borderId="36" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="37" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="18" borderId="38" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="18" borderId="39" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="18" borderId="40" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="41" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="18" borderId="42" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="18" borderId="39" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="6" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="15" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="15" borderId="7" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="7" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="7" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="16" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="16" borderId="7" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="167" fontId="15" fillId="12" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="15" fillId="12" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="15" fillId="12" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180"/>
+    </xf>
+    <xf numFmtId="166" fontId="22" fillId="2" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="19" fillId="0" borderId="0" xfId="9" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="3" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1282,233 +1515,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="13" fillId="3" borderId="6" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="13" fillId="3" borderId="7" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="13" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="13" fillId="4" borderId="5" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="13" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="13" fillId="5" borderId="8" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="13" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="13" fillId="10" borderId="9" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="19" fillId="0" borderId="0" xfId="9" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="7" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="8" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="9" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="17" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="13" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="18" xfId="12" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="10" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="13" fillId="10" borderId="18" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="13" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="13" fillId="13" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="13" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="22" xfId="12" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="14" borderId="23" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="13" fillId="14" borderId="23" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="13" fillId="14" borderId="24" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="25" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="14" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="13" fillId="14" borderId="26" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="13" fillId="14" borderId="27" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="28" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="14" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="13" fillId="14" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="13" fillId="14" borderId="29" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="25" xfId="12" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="18" borderId="30" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="13" fillId="18" borderId="30" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="13" fillId="18" borderId="31" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="32" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="33" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="18" borderId="34" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="13" fillId="18" borderId="35" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="13" fillId="18" borderId="36" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="37" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="18" borderId="38" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="13" fillId="18" borderId="39" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="13" fillId="18" borderId="40" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="41" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="14" fontId="13" fillId="18" borderId="42" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="18" borderId="39" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="6" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="15" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="13" fillId="15" borderId="7" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="7" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="7" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="16" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="13" fillId="16" borderId="7" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180"/>
-    </xf>
-    <xf numFmtId="167" fontId="15" fillId="12" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="15" fillId="12" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="15" fillId="12" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="22" fillId="2" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="13">
@@ -1526,7 +1532,149 @@
     <cellStyle name="Title" xfId="5" builtinId="15" customBuiltin="1"/>
     <cellStyle name="zHiddenText" xfId="3" xr:uid="{26E66EE6-E33F-4D77-BAE4-0FB4F5BBF673}"/>
   </cellStyles>
-  <dxfs count="45">
+  <dxfs count="36">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="0" tint="-4.9989318521683403E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-4.9989318521683403E-2"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="0" tint="-4.9989318521683403E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-4.9989318521683403E-2"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="5"/>
+        </left>
+        <right style="thin">
+          <color theme="5"/>
+        </right>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9092"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left/>
+        <right/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left/>
+        <right/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left/>
+        <right/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="0" tint="-4.9989318521683403E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-4.9989318521683403E-2"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="0" tint="-4.9989318521683403E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-4.9989318521683403E-2"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="0" tint="-4.9989318521683403E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-4.9989318521683403E-2"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="5"/>
+        </left>
+        <right style="thin">
+          <color theme="5"/>
+        </right>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1557,30 +1705,6 @@
         <bottom style="thin">
           <color theme="0" tint="-4.9989318521683403E-2"/>
         </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color theme="5"/>
-        </left>
-        <right style="thin">
-          <color theme="5"/>
-        </right>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color theme="5"/>
-        </left>
-        <right style="thin">
-          <color theme="5"/>
-        </right>
-        <vertical/>
-        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -1635,16 +1759,12 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor rgb="FFFFCFD0"/>
         </patternFill>
       </fill>
       <border>
-        <top style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </bottom>
+        <left/>
+        <right/>
       </border>
     </dxf>
     <dxf>
@@ -1661,7 +1781,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFCFD0"/>
+          <bgColor theme="9" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
       <border>
@@ -1683,7 +1803,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
+          <bgColor theme="8" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
       <border>
@@ -1694,7 +1814,57 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFF0000"/>
+          <bgColor theme="8"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left/>
+        <right/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="0" tint="-4.9989318521683403E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-4.9989318521683403E-2"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="0" tint="-4.9989318521683403E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-4.9989318521683403E-2"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
       <border>
@@ -1726,291 +1896,12 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9092"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFCFD0"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor theme="4" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
       <border>
         <left/>
         <right/>
-        <top style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border>
         <top style="thin">
           <color theme="0" tint="-4.9989318521683403E-2"/>
         </top>
@@ -2115,15 +2006,15 @@
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="ToDoList" pivot="0" count="9" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" dxfId="44"/>
-      <tableStyleElement type="headerRow" dxfId="43"/>
-      <tableStyleElement type="totalRow" dxfId="42"/>
-      <tableStyleElement type="firstColumn" dxfId="41"/>
-      <tableStyleElement type="lastColumn" dxfId="40"/>
-      <tableStyleElement type="firstRowStripe" dxfId="39"/>
-      <tableStyleElement type="secondRowStripe" dxfId="38"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="37"/>
-      <tableStyleElement type="secondColumnStripe" dxfId="36"/>
+      <tableStyleElement type="wholeTable" dxfId="35"/>
+      <tableStyleElement type="headerRow" dxfId="34"/>
+      <tableStyleElement type="totalRow" dxfId="33"/>
+      <tableStyleElement type="firstColumn" dxfId="32"/>
+      <tableStyleElement type="lastColumn" dxfId="31"/>
+      <tableStyleElement type="firstRowStripe" dxfId="30"/>
+      <tableStyleElement type="secondRowStripe" dxfId="29"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="28"/>
+      <tableStyleElement type="secondColumnStripe" dxfId="27"/>
     </tableStyle>
   </tableStyles>
   <colors>
@@ -2215,6 +2106,33 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Sessions_data"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1">
+        <row r="2">
+          <cell r="B2">
+            <v>1162</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>2419</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2439,62 +2357,62 @@
   <sheetData>
     <row r="1" spans="1:142" ht="90" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A1" s="5"/>
-      <c r="B1" s="123"/>
+      <c r="B1" s="112"/>
       <c r="C1" s="7"/>
       <c r="D1" s="8"/>
       <c r="E1" s="9"/>
       <c r="G1" s="1"/>
-      <c r="H1" s="58" t="s">
+      <c r="H1" s="128" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="59"/>
-      <c r="J1" s="59"/>
-      <c r="K1" s="59"/>
-      <c r="L1" s="59"/>
-      <c r="M1" s="59"/>
-      <c r="N1" s="59"/>
+      <c r="I1" s="129"/>
+      <c r="J1" s="129"/>
+      <c r="K1" s="129"/>
+      <c r="L1" s="129"/>
+      <c r="M1" s="129"/>
+      <c r="N1" s="129"/>
       <c r="O1" s="12"/>
-      <c r="P1" s="71">
+      <c r="P1" s="126">
         <f>DATE(2026,5,6)</f>
         <v>46148</v>
       </c>
-      <c r="Q1" s="72"/>
-      <c r="R1" s="72"/>
-      <c r="S1" s="72"/>
-      <c r="T1" s="72"/>
-      <c r="U1" s="72"/>
-      <c r="V1" s="72"/>
-      <c r="W1" s="72"/>
-      <c r="X1" s="72"/>
-      <c r="Y1" s="72"/>
+      <c r="Q1" s="127"/>
+      <c r="R1" s="127"/>
+      <c r="S1" s="127"/>
+      <c r="T1" s="127"/>
+      <c r="U1" s="127"/>
+      <c r="V1" s="127"/>
+      <c r="W1" s="127"/>
+      <c r="X1" s="127"/>
+      <c r="Y1" s="127"/>
     </row>
     <row r="2" spans="1:142" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="50"/>
       <c r="C2" s="10"/>
       <c r="D2" s="11"/>
       <c r="E2" s="10"/>
-      <c r="H2" s="58" t="s">
+      <c r="H2" s="128" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="59"/>
-      <c r="J2" s="59"/>
-      <c r="K2" s="59"/>
-      <c r="L2" s="59"/>
-      <c r="M2" s="59"/>
-      <c r="N2" s="59"/>
+      <c r="I2" s="129"/>
+      <c r="J2" s="129"/>
+      <c r="K2" s="129"/>
+      <c r="L2" s="129"/>
+      <c r="M2" s="129"/>
+      <c r="N2" s="129"/>
       <c r="O2" s="12"/>
-      <c r="P2" s="56">
+      <c r="P2" s="124">
         <v>1</v>
       </c>
-      <c r="Q2" s="57"/>
-      <c r="R2" s="57"/>
-      <c r="S2" s="57"/>
-      <c r="T2" s="57"/>
-      <c r="U2" s="57"/>
-      <c r="V2" s="57"/>
-      <c r="W2" s="57"/>
-      <c r="X2" s="57"/>
-      <c r="Y2" s="57"/>
+      <c r="Q2" s="125"/>
+      <c r="R2" s="125"/>
+      <c r="S2" s="125"/>
+      <c r="T2" s="125"/>
+      <c r="U2" s="125"/>
+      <c r="V2" s="125"/>
+      <c r="W2" s="125"/>
+      <c r="X2" s="125"/>
+      <c r="Y2" s="125"/>
     </row>
     <row r="3" spans="1:142" s="14" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="4"/>
@@ -2506,703 +2424,703 @@
       <c r="A4" s="5"/>
       <c r="B4" s="17"/>
       <c r="D4" s="18"/>
-      <c r="H4" s="132" t="s">
+      <c r="H4" s="121" t="s">
         <v>54</v>
       </c>
-      <c r="I4" s="132"/>
-      <c r="J4" s="132"/>
-      <c r="K4" s="132"/>
-      <c r="L4" s="132"/>
-      <c r="M4" s="132"/>
-      <c r="N4" s="132"/>
-      <c r="O4" s="132"/>
-      <c r="P4" s="132"/>
-      <c r="Q4" s="132"/>
-      <c r="R4" s="132"/>
-      <c r="S4" s="132"/>
-      <c r="T4" s="132"/>
-      <c r="U4" s="132"/>
-      <c r="V4" s="132"/>
-      <c r="W4" s="132"/>
-      <c r="X4" s="132"/>
-      <c r="Y4" s="132"/>
-      <c r="Z4" s="132"/>
-      <c r="AA4" s="132"/>
-      <c r="AB4" s="132"/>
-      <c r="AC4" s="132"/>
-      <c r="AD4" s="132"/>
-      <c r="AE4" s="132"/>
-      <c r="AF4" s="132"/>
-      <c r="AG4" s="132"/>
-      <c r="AH4" s="132"/>
-      <c r="AI4" s="132"/>
-      <c r="AJ4" s="132" t="s">
+      <c r="I4" s="121"/>
+      <c r="J4" s="121"/>
+      <c r="K4" s="121"/>
+      <c r="L4" s="121"/>
+      <c r="M4" s="121"/>
+      <c r="N4" s="121"/>
+      <c r="O4" s="121"/>
+      <c r="P4" s="121"/>
+      <c r="Q4" s="121"/>
+      <c r="R4" s="121"/>
+      <c r="S4" s="121"/>
+      <c r="T4" s="121"/>
+      <c r="U4" s="121"/>
+      <c r="V4" s="121"/>
+      <c r="W4" s="121"/>
+      <c r="X4" s="121"/>
+      <c r="Y4" s="121"/>
+      <c r="Z4" s="121"/>
+      <c r="AA4" s="121"/>
+      <c r="AB4" s="121"/>
+      <c r="AC4" s="121"/>
+      <c r="AD4" s="121"/>
+      <c r="AE4" s="121"/>
+      <c r="AF4" s="121"/>
+      <c r="AG4" s="121"/>
+      <c r="AH4" s="121"/>
+      <c r="AI4" s="121"/>
+      <c r="AJ4" s="121" t="s">
         <v>55</v>
       </c>
-      <c r="AK4" s="132"/>
-      <c r="AL4" s="132"/>
-      <c r="AM4" s="132"/>
-      <c r="AN4" s="132"/>
-      <c r="AO4" s="132"/>
-      <c r="AP4" s="132"/>
-      <c r="AQ4" s="132"/>
-      <c r="AR4" s="132"/>
-      <c r="AS4" s="132"/>
-      <c r="AT4" s="132"/>
-      <c r="AU4" s="132"/>
-      <c r="AV4" s="132"/>
-      <c r="AW4" s="132"/>
-      <c r="AX4" s="132"/>
-      <c r="AY4" s="132"/>
-      <c r="AZ4" s="132"/>
-      <c r="BA4" s="132"/>
-      <c r="BB4" s="132"/>
-      <c r="BC4" s="132"/>
-      <c r="BD4" s="132"/>
-      <c r="BE4" s="132"/>
-      <c r="BF4" s="132"/>
-      <c r="BG4" s="132"/>
-      <c r="BH4" s="132"/>
-      <c r="BI4" s="132"/>
-      <c r="BJ4" s="132"/>
-      <c r="BK4" s="132"/>
-      <c r="BL4" s="132"/>
-      <c r="BM4" s="132"/>
-      <c r="BN4" s="132" t="s">
+      <c r="AK4" s="121"/>
+      <c r="AL4" s="121"/>
+      <c r="AM4" s="121"/>
+      <c r="AN4" s="121"/>
+      <c r="AO4" s="121"/>
+      <c r="AP4" s="121"/>
+      <c r="AQ4" s="121"/>
+      <c r="AR4" s="121"/>
+      <c r="AS4" s="121"/>
+      <c r="AT4" s="121"/>
+      <c r="AU4" s="121"/>
+      <c r="AV4" s="121"/>
+      <c r="AW4" s="121"/>
+      <c r="AX4" s="121"/>
+      <c r="AY4" s="121"/>
+      <c r="AZ4" s="121"/>
+      <c r="BA4" s="121"/>
+      <c r="BB4" s="121"/>
+      <c r="BC4" s="121"/>
+      <c r="BD4" s="121"/>
+      <c r="BE4" s="121"/>
+      <c r="BF4" s="121"/>
+      <c r="BG4" s="121"/>
+      <c r="BH4" s="121"/>
+      <c r="BI4" s="121"/>
+      <c r="BJ4" s="121"/>
+      <c r="BK4" s="121"/>
+      <c r="BL4" s="121"/>
+      <c r="BM4" s="121"/>
+      <c r="BN4" s="121" t="s">
         <v>56</v>
       </c>
-      <c r="BO4" s="132"/>
-      <c r="BP4" s="132"/>
-      <c r="BQ4" s="132"/>
-      <c r="BR4" s="132"/>
-      <c r="BS4" s="132"/>
-      <c r="BT4" s="132"/>
-      <c r="BU4" s="132"/>
-      <c r="BV4" s="132"/>
-      <c r="BW4" s="132"/>
-      <c r="BX4" s="132"/>
-      <c r="BY4" s="132"/>
-      <c r="BZ4" s="132"/>
-      <c r="CA4" s="132"/>
-      <c r="CB4" s="132"/>
-      <c r="CC4" s="132"/>
-      <c r="CD4" s="132"/>
-      <c r="CE4" s="132"/>
-      <c r="CF4" s="132"/>
-      <c r="CG4" s="132"/>
-      <c r="CH4" s="132"/>
-      <c r="CI4" s="132"/>
-      <c r="CJ4" s="132"/>
-      <c r="CK4" s="132"/>
-      <c r="CL4" s="132"/>
-      <c r="CM4" s="132"/>
-      <c r="CN4" s="132"/>
-      <c r="CO4" s="132"/>
-      <c r="CP4" s="132"/>
-      <c r="CQ4" s="132"/>
-      <c r="CR4" s="132"/>
-      <c r="CS4" s="132" t="s">
+      <c r="BO4" s="121"/>
+      <c r="BP4" s="121"/>
+      <c r="BQ4" s="121"/>
+      <c r="BR4" s="121"/>
+      <c r="BS4" s="121"/>
+      <c r="BT4" s="121"/>
+      <c r="BU4" s="121"/>
+      <c r="BV4" s="121"/>
+      <c r="BW4" s="121"/>
+      <c r="BX4" s="121"/>
+      <c r="BY4" s="121"/>
+      <c r="BZ4" s="121"/>
+      <c r="CA4" s="121"/>
+      <c r="CB4" s="121"/>
+      <c r="CC4" s="121"/>
+      <c r="CD4" s="121"/>
+      <c r="CE4" s="121"/>
+      <c r="CF4" s="121"/>
+      <c r="CG4" s="121"/>
+      <c r="CH4" s="121"/>
+      <c r="CI4" s="121"/>
+      <c r="CJ4" s="121"/>
+      <c r="CK4" s="121"/>
+      <c r="CL4" s="121"/>
+      <c r="CM4" s="121"/>
+      <c r="CN4" s="121"/>
+      <c r="CO4" s="121"/>
+      <c r="CP4" s="121"/>
+      <c r="CQ4" s="121"/>
+      <c r="CR4" s="121"/>
+      <c r="CS4" s="121" t="s">
         <v>57</v>
       </c>
-      <c r="CT4" s="132"/>
-      <c r="CU4" s="132"/>
-      <c r="CV4" s="132"/>
-      <c r="CW4" s="132"/>
-      <c r="CX4" s="132"/>
-      <c r="CY4" s="132"/>
-      <c r="CZ4" s="132"/>
-      <c r="DA4" s="132"/>
-      <c r="DB4" s="132"/>
-      <c r="DC4" s="132"/>
-      <c r="DD4" s="132"/>
-      <c r="DE4" s="132"/>
-      <c r="DF4" s="132"/>
-      <c r="DG4" s="132"/>
-      <c r="DH4" s="132"/>
-      <c r="DI4" s="132"/>
-      <c r="DJ4" s="132"/>
-      <c r="DK4" s="132"/>
-      <c r="DL4" s="132"/>
-      <c r="DM4" s="132"/>
-      <c r="DN4" s="132"/>
-      <c r="DO4" s="132"/>
-      <c r="DP4" s="132"/>
-      <c r="DQ4" s="132"/>
-      <c r="DR4" s="132"/>
-      <c r="DS4" s="132"/>
-      <c r="DT4" s="132"/>
-      <c r="DU4" s="132"/>
-      <c r="DV4" s="132"/>
-      <c r="DW4" s="132"/>
-      <c r="DX4" s="132" t="s">
+      <c r="CT4" s="121"/>
+      <c r="CU4" s="121"/>
+      <c r="CV4" s="121"/>
+      <c r="CW4" s="121"/>
+      <c r="CX4" s="121"/>
+      <c r="CY4" s="121"/>
+      <c r="CZ4" s="121"/>
+      <c r="DA4" s="121"/>
+      <c r="DB4" s="121"/>
+      <c r="DC4" s="121"/>
+      <c r="DD4" s="121"/>
+      <c r="DE4" s="121"/>
+      <c r="DF4" s="121"/>
+      <c r="DG4" s="121"/>
+      <c r="DH4" s="121"/>
+      <c r="DI4" s="121"/>
+      <c r="DJ4" s="121"/>
+      <c r="DK4" s="121"/>
+      <c r="DL4" s="121"/>
+      <c r="DM4" s="121"/>
+      <c r="DN4" s="121"/>
+      <c r="DO4" s="121"/>
+      <c r="DP4" s="121"/>
+      <c r="DQ4" s="121"/>
+      <c r="DR4" s="121"/>
+      <c r="DS4" s="121"/>
+      <c r="DT4" s="121"/>
+      <c r="DU4" s="121"/>
+      <c r="DV4" s="121"/>
+      <c r="DW4" s="121"/>
+      <c r="DX4" s="121" t="s">
         <v>58</v>
       </c>
-      <c r="DY4" s="132"/>
-      <c r="DZ4" s="132"/>
-      <c r="EA4" s="132"/>
-      <c r="EB4" s="132"/>
-      <c r="EC4" s="132"/>
-      <c r="ED4" s="132"/>
-      <c r="EE4" s="132"/>
-      <c r="EF4" s="132"/>
-      <c r="EG4" s="132"/>
-      <c r="EH4" s="132"/>
-      <c r="EI4" s="132"/>
-      <c r="EJ4" s="132"/>
+      <c r="DY4" s="121"/>
+      <c r="DZ4" s="121"/>
+      <c r="EA4" s="121"/>
+      <c r="EB4" s="121"/>
+      <c r="EC4" s="121"/>
+      <c r="ED4" s="121"/>
+      <c r="EE4" s="121"/>
+      <c r="EF4" s="121"/>
+      <c r="EG4" s="121"/>
+      <c r="EH4" s="121"/>
+      <c r="EI4" s="121"/>
+      <c r="EJ4" s="121"/>
     </row>
     <row r="5" spans="1:142" s="14" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="51"/>
-      <c r="B5" s="52" t="s">
+      <c r="A5" s="130"/>
+      <c r="B5" s="131" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="55" t="s">
+      <c r="C5" s="122" t="s">
         <v>0</v>
       </c>
-      <c r="D5" s="55" t="s">
+      <c r="D5" s="122" t="s">
         <v>1</v>
       </c>
-      <c r="E5" s="55" t="s">
+      <c r="E5" s="122" t="s">
         <v>2</v>
       </c>
-      <c r="H5" s="129">
+      <c r="H5" s="116">
         <f>Project_Start-WEEKDAY(Project_Start,1)+2+7*(Display_Week-1)</f>
         <v>46146</v>
       </c>
-      <c r="I5" s="129">
+      <c r="I5" s="116">
         <f>H5+1</f>
         <v>46147</v>
       </c>
-      <c r="J5" s="129">
+      <c r="J5" s="116">
         <f t="shared" ref="J5:AW5" si="0">I5+1</f>
         <v>46148</v>
       </c>
-      <c r="K5" s="129">
+      <c r="K5" s="116">
         <f t="shared" si="0"/>
         <v>46149</v>
       </c>
-      <c r="L5" s="129">
+      <c r="L5" s="116">
         <f t="shared" si="0"/>
         <v>46150</v>
       </c>
-      <c r="M5" s="129">
+      <c r="M5" s="116">
         <f t="shared" si="0"/>
         <v>46151</v>
       </c>
-      <c r="N5" s="130">
+      <c r="N5" s="117">
         <f t="shared" si="0"/>
         <v>46152</v>
       </c>
-      <c r="O5" s="131">
+      <c r="O5" s="118">
         <f>N5+1</f>
         <v>46153</v>
       </c>
-      <c r="P5" s="129">
+      <c r="P5" s="116">
         <f>O5+1</f>
         <v>46154</v>
       </c>
-      <c r="Q5" s="129">
+      <c r="Q5" s="116">
         <f t="shared" si="0"/>
         <v>46155</v>
       </c>
-      <c r="R5" s="129">
+      <c r="R5" s="116">
         <f t="shared" si="0"/>
         <v>46156</v>
       </c>
-      <c r="S5" s="129">
+      <c r="S5" s="116">
         <f t="shared" si="0"/>
         <v>46157</v>
       </c>
-      <c r="T5" s="129">
+      <c r="T5" s="116">
         <f t="shared" si="0"/>
         <v>46158</v>
       </c>
-      <c r="U5" s="130">
+      <c r="U5" s="117">
         <f t="shared" si="0"/>
         <v>46159</v>
       </c>
-      <c r="V5" s="131">
+      <c r="V5" s="118">
         <f>U5+1</f>
         <v>46160</v>
       </c>
-      <c r="W5" s="129">
+      <c r="W5" s="116">
         <f>V5+1</f>
         <v>46161</v>
       </c>
-      <c r="X5" s="129">
+      <c r="X5" s="116">
         <f t="shared" si="0"/>
         <v>46162</v>
       </c>
-      <c r="Y5" s="129">
+      <c r="Y5" s="116">
         <f t="shared" si="0"/>
         <v>46163</v>
       </c>
-      <c r="Z5" s="129">
+      <c r="Z5" s="116">
         <f t="shared" si="0"/>
         <v>46164</v>
       </c>
-      <c r="AA5" s="129">
+      <c r="AA5" s="116">
         <f t="shared" si="0"/>
         <v>46165</v>
       </c>
-      <c r="AB5" s="130">
+      <c r="AB5" s="117">
         <f t="shared" si="0"/>
         <v>46166</v>
       </c>
-      <c r="AC5" s="131">
+      <c r="AC5" s="118">
         <f>AB5+1</f>
         <v>46167</v>
       </c>
-      <c r="AD5" s="129">
+      <c r="AD5" s="116">
         <f>AC5+1</f>
         <v>46168</v>
       </c>
-      <c r="AE5" s="129">
+      <c r="AE5" s="116">
         <f t="shared" si="0"/>
         <v>46169</v>
       </c>
-      <c r="AF5" s="129">
+      <c r="AF5" s="116">
         <f t="shared" si="0"/>
         <v>46170</v>
       </c>
-      <c r="AG5" s="129">
+      <c r="AG5" s="116">
         <f t="shared" si="0"/>
         <v>46171</v>
       </c>
-      <c r="AH5" s="129">
+      <c r="AH5" s="116">
         <f t="shared" si="0"/>
         <v>46172</v>
       </c>
-      <c r="AI5" s="130">
+      <c r="AI5" s="117">
         <f t="shared" si="0"/>
         <v>46173</v>
       </c>
-      <c r="AJ5" s="131">
+      <c r="AJ5" s="118">
         <f>AI5+1</f>
         <v>46174</v>
       </c>
-      <c r="AK5" s="129">
+      <c r="AK5" s="116">
         <f>AJ5+1</f>
         <v>46175</v>
       </c>
-      <c r="AL5" s="129">
+      <c r="AL5" s="116">
         <f t="shared" si="0"/>
         <v>46176</v>
       </c>
-      <c r="AM5" s="129">
+      <c r="AM5" s="116">
         <f t="shared" si="0"/>
         <v>46177</v>
       </c>
-      <c r="AN5" s="129">
+      <c r="AN5" s="116">
         <f t="shared" si="0"/>
         <v>46178</v>
       </c>
-      <c r="AO5" s="129">
+      <c r="AO5" s="116">
         <f t="shared" si="0"/>
         <v>46179</v>
       </c>
-      <c r="AP5" s="130">
+      <c r="AP5" s="117">
         <f t="shared" si="0"/>
         <v>46180</v>
       </c>
-      <c r="AQ5" s="131">
+      <c r="AQ5" s="118">
         <f>AP5+1</f>
         <v>46181</v>
       </c>
-      <c r="AR5" s="129">
+      <c r="AR5" s="116">
         <f>AQ5+1</f>
         <v>46182</v>
       </c>
-      <c r="AS5" s="129">
+      <c r="AS5" s="116">
         <f t="shared" si="0"/>
         <v>46183</v>
       </c>
-      <c r="AT5" s="129">
+      <c r="AT5" s="116">
         <f t="shared" si="0"/>
         <v>46184</v>
       </c>
-      <c r="AU5" s="129">
+      <c r="AU5" s="116">
         <f t="shared" si="0"/>
         <v>46185</v>
       </c>
-      <c r="AV5" s="129">
+      <c r="AV5" s="116">
         <f t="shared" si="0"/>
         <v>46186</v>
       </c>
-      <c r="AW5" s="130">
+      <c r="AW5" s="117">
         <f t="shared" si="0"/>
         <v>46187</v>
       </c>
-      <c r="AX5" s="131">
+      <c r="AX5" s="118">
         <f>AW5+1</f>
         <v>46188</v>
       </c>
-      <c r="AY5" s="129">
+      <c r="AY5" s="116">
         <f>AX5+1</f>
         <v>46189</v>
       </c>
-      <c r="AZ5" s="129">
+      <c r="AZ5" s="116">
         <f t="shared" ref="AZ5:BD5" si="1">AY5+1</f>
         <v>46190</v>
       </c>
-      <c r="BA5" s="129">
+      <c r="BA5" s="116">
         <f t="shared" si="1"/>
         <v>46191</v>
       </c>
-      <c r="BB5" s="129">
+      <c r="BB5" s="116">
         <f t="shared" si="1"/>
         <v>46192</v>
       </c>
-      <c r="BC5" s="129">
+      <c r="BC5" s="116">
         <f t="shared" si="1"/>
         <v>46193</v>
       </c>
-      <c r="BD5" s="130">
+      <c r="BD5" s="117">
         <f t="shared" si="1"/>
         <v>46194</v>
       </c>
-      <c r="BE5" s="131">
+      <c r="BE5" s="118">
         <f>BD5+1</f>
         <v>46195</v>
       </c>
-      <c r="BF5" s="129">
+      <c r="BF5" s="116">
         <f>BE5+1</f>
         <v>46196</v>
       </c>
-      <c r="BG5" s="129">
+      <c r="BG5" s="116">
         <f t="shared" ref="BG5:BK5" si="2">BF5+1</f>
         <v>46197</v>
       </c>
-      <c r="BH5" s="129">
+      <c r="BH5" s="116">
         <f t="shared" si="2"/>
         <v>46198</v>
       </c>
-      <c r="BI5" s="129">
+      <c r="BI5" s="116">
         <f t="shared" si="2"/>
         <v>46199</v>
       </c>
-      <c r="BJ5" s="129">
+      <c r="BJ5" s="116">
         <f t="shared" si="2"/>
         <v>46200</v>
       </c>
-      <c r="BK5" s="129">
+      <c r="BK5" s="116">
         <f t="shared" si="2"/>
         <v>46201</v>
       </c>
-      <c r="BL5" s="131">
+      <c r="BL5" s="118">
         <f>BK5+1</f>
         <v>46202</v>
       </c>
-      <c r="BM5" s="129">
+      <c r="BM5" s="116">
         <f>BL5+1</f>
         <v>46203</v>
       </c>
-      <c r="BN5" s="129">
+      <c r="BN5" s="116">
         <f t="shared" ref="BN5" si="3">BM5+1</f>
         <v>46204</v>
       </c>
-      <c r="BO5" s="129">
+      <c r="BO5" s="116">
         <f t="shared" ref="BO5" si="4">BN5+1</f>
         <v>46205</v>
       </c>
-      <c r="BP5" s="129">
+      <c r="BP5" s="116">
         <f t="shared" ref="BP5" si="5">BO5+1</f>
         <v>46206</v>
       </c>
-      <c r="BQ5" s="129">
+      <c r="BQ5" s="116">
         <f t="shared" ref="BQ5" si="6">BP5+1</f>
         <v>46207</v>
       </c>
-      <c r="BR5" s="129">
+      <c r="BR5" s="116">
         <f t="shared" ref="BR5:BT5" si="7">BQ5+1</f>
         <v>46208</v>
       </c>
-      <c r="BS5" s="131">
+      <c r="BS5" s="118">
         <f t="shared" si="7"/>
         <v>46209</v>
       </c>
-      <c r="BT5" s="129">
+      <c r="BT5" s="116">
         <f t="shared" si="7"/>
         <v>46210</v>
       </c>
-      <c r="BU5" s="129">
+      <c r="BU5" s="116">
         <f t="shared" ref="BU5" si="8">BT5+1</f>
         <v>46211</v>
       </c>
-      <c r="BV5" s="129">
+      <c r="BV5" s="116">
         <f t="shared" ref="BV5" si="9">BU5+1</f>
         <v>46212</v>
       </c>
-      <c r="BW5" s="129">
+      <c r="BW5" s="116">
         <f t="shared" ref="BW5" si="10">BV5+1</f>
         <v>46213</v>
       </c>
-      <c r="BX5" s="129">
+      <c r="BX5" s="116">
         <f t="shared" ref="BX5" si="11">BW5+1</f>
         <v>46214</v>
       </c>
-      <c r="BY5" s="129">
+      <c r="BY5" s="116">
         <f t="shared" ref="BY5:CA5" si="12">BX5+1</f>
         <v>46215</v>
       </c>
-      <c r="BZ5" s="131">
+      <c r="BZ5" s="118">
         <f t="shared" si="12"/>
         <v>46216</v>
       </c>
-      <c r="CA5" s="129">
+      <c r="CA5" s="116">
         <f t="shared" si="12"/>
         <v>46217</v>
       </c>
-      <c r="CB5" s="129">
+      <c r="CB5" s="116">
         <f t="shared" ref="CB5" si="13">CA5+1</f>
         <v>46218</v>
       </c>
-      <c r="CC5" s="129">
+      <c r="CC5" s="116">
         <f t="shared" ref="CC5" si="14">CB5+1</f>
         <v>46219</v>
       </c>
-      <c r="CD5" s="129">
+      <c r="CD5" s="116">
         <f t="shared" ref="CD5" si="15">CC5+1</f>
         <v>46220</v>
       </c>
-      <c r="CE5" s="129">
+      <c r="CE5" s="116">
         <f t="shared" ref="CE5" si="16">CD5+1</f>
         <v>46221</v>
       </c>
-      <c r="CF5" s="129">
+      <c r="CF5" s="116">
         <f t="shared" ref="CF5:CH5" si="17">CE5+1</f>
         <v>46222</v>
       </c>
-      <c r="CG5" s="131">
+      <c r="CG5" s="118">
         <f t="shared" si="17"/>
         <v>46223</v>
       </c>
-      <c r="CH5" s="129">
+      <c r="CH5" s="116">
         <f t="shared" si="17"/>
         <v>46224</v>
       </c>
-      <c r="CI5" s="129">
+      <c r="CI5" s="116">
         <f t="shared" ref="CI5" si="18">CH5+1</f>
         <v>46225</v>
       </c>
-      <c r="CJ5" s="129">
+      <c r="CJ5" s="116">
         <f t="shared" ref="CJ5" si="19">CI5+1</f>
         <v>46226</v>
       </c>
-      <c r="CK5" s="129">
+      <c r="CK5" s="116">
         <f t="shared" ref="CK5" si="20">CJ5+1</f>
         <v>46227</v>
       </c>
-      <c r="CL5" s="129">
+      <c r="CL5" s="116">
         <f t="shared" ref="CL5" si="21">CK5+1</f>
         <v>46228</v>
       </c>
-      <c r="CM5" s="129">
+      <c r="CM5" s="116">
         <f t="shared" ref="CM5:CO5" si="22">CL5+1</f>
         <v>46229</v>
       </c>
-      <c r="CN5" s="131">
+      <c r="CN5" s="118">
         <f t="shared" si="22"/>
         <v>46230</v>
       </c>
-      <c r="CO5" s="129">
+      <c r="CO5" s="116">
         <f t="shared" si="22"/>
         <v>46231</v>
       </c>
-      <c r="CP5" s="129">
+      <c r="CP5" s="116">
         <f t="shared" ref="CP5" si="23">CO5+1</f>
         <v>46232</v>
       </c>
-      <c r="CQ5" s="129">
+      <c r="CQ5" s="116">
         <f t="shared" ref="CQ5" si="24">CP5+1</f>
         <v>46233</v>
       </c>
-      <c r="CR5" s="129">
+      <c r="CR5" s="116">
         <f t="shared" ref="CR5" si="25">CQ5+1</f>
         <v>46234</v>
       </c>
-      <c r="CS5" s="129">
+      <c r="CS5" s="116">
         <f t="shared" ref="CS5" si="26">CR5+1</f>
         <v>46235</v>
       </c>
-      <c r="CT5" s="129">
+      <c r="CT5" s="116">
         <f t="shared" ref="CT5:CV5" si="27">CS5+1</f>
         <v>46236</v>
       </c>
-      <c r="CU5" s="131">
+      <c r="CU5" s="118">
         <f t="shared" si="27"/>
         <v>46237</v>
       </c>
-      <c r="CV5" s="129">
+      <c r="CV5" s="116">
         <f t="shared" si="27"/>
         <v>46238</v>
       </c>
-      <c r="CW5" s="129">
+      <c r="CW5" s="116">
         <f t="shared" ref="CW5" si="28">CV5+1</f>
         <v>46239</v>
       </c>
-      <c r="CX5" s="129">
+      <c r="CX5" s="116">
         <f t="shared" ref="CX5" si="29">CW5+1</f>
         <v>46240</v>
       </c>
-      <c r="CY5" s="129">
+      <c r="CY5" s="116">
         <f t="shared" ref="CY5" si="30">CX5+1</f>
         <v>46241</v>
       </c>
-      <c r="CZ5" s="129">
+      <c r="CZ5" s="116">
         <f t="shared" ref="CZ5" si="31">CY5+1</f>
         <v>46242</v>
       </c>
-      <c r="DA5" s="129">
+      <c r="DA5" s="116">
         <f t="shared" ref="DA5:DC5" si="32">CZ5+1</f>
         <v>46243</v>
       </c>
-      <c r="DB5" s="131">
+      <c r="DB5" s="118">
         <f t="shared" si="32"/>
         <v>46244</v>
       </c>
-      <c r="DC5" s="129">
+      <c r="DC5" s="116">
         <f t="shared" si="32"/>
         <v>46245</v>
       </c>
-      <c r="DD5" s="129">
+      <c r="DD5" s="116">
         <f t="shared" ref="DD5" si="33">DC5+1</f>
         <v>46246</v>
       </c>
-      <c r="DE5" s="129">
+      <c r="DE5" s="116">
         <f t="shared" ref="DE5" si="34">DD5+1</f>
         <v>46247</v>
       </c>
-      <c r="DF5" s="129">
+      <c r="DF5" s="116">
         <f t="shared" ref="DF5" si="35">DE5+1</f>
         <v>46248</v>
       </c>
-      <c r="DG5" s="129">
+      <c r="DG5" s="116">
         <f t="shared" ref="DG5" si="36">DF5+1</f>
         <v>46249</v>
       </c>
-      <c r="DH5" s="129">
+      <c r="DH5" s="116">
         <f t="shared" ref="DH5:DJ5" si="37">DG5+1</f>
         <v>46250</v>
       </c>
-      <c r="DI5" s="131">
+      <c r="DI5" s="118">
         <f t="shared" si="37"/>
         <v>46251</v>
       </c>
-      <c r="DJ5" s="129">
+      <c r="DJ5" s="116">
         <f t="shared" si="37"/>
         <v>46252</v>
       </c>
-      <c r="DK5" s="129">
+      <c r="DK5" s="116">
         <f t="shared" ref="DK5" si="38">DJ5+1</f>
         <v>46253</v>
       </c>
-      <c r="DL5" s="129">
+      <c r="DL5" s="116">
         <f t="shared" ref="DL5" si="39">DK5+1</f>
         <v>46254</v>
       </c>
-      <c r="DM5" s="129">
+      <c r="DM5" s="116">
         <f t="shared" ref="DM5" si="40">DL5+1</f>
         <v>46255</v>
       </c>
-      <c r="DN5" s="129">
+      <c r="DN5" s="116">
         <f t="shared" ref="DN5" si="41">DM5+1</f>
         <v>46256</v>
       </c>
-      <c r="DO5" s="129">
+      <c r="DO5" s="116">
         <f t="shared" ref="DO5:DQ5" si="42">DN5+1</f>
         <v>46257</v>
       </c>
-      <c r="DP5" s="131">
+      <c r="DP5" s="118">
         <f t="shared" si="42"/>
         <v>46258</v>
       </c>
-      <c r="DQ5" s="129">
+      <c r="DQ5" s="116">
         <f t="shared" si="42"/>
         <v>46259</v>
       </c>
-      <c r="DR5" s="129">
+      <c r="DR5" s="116">
         <f t="shared" ref="DR5" si="43">DQ5+1</f>
         <v>46260</v>
       </c>
-      <c r="DS5" s="129">
+      <c r="DS5" s="116">
         <f t="shared" ref="DS5" si="44">DR5+1</f>
         <v>46261</v>
       </c>
-      <c r="DT5" s="129">
+      <c r="DT5" s="116">
         <f t="shared" ref="DT5" si="45">DS5+1</f>
         <v>46262</v>
       </c>
-      <c r="DU5" s="129">
+      <c r="DU5" s="116">
         <f t="shared" ref="DU5" si="46">DT5+1</f>
         <v>46263</v>
       </c>
-      <c r="DV5" s="129">
+      <c r="DV5" s="116">
         <f t="shared" ref="DV5:DX5" si="47">DU5+1</f>
         <v>46264</v>
       </c>
-      <c r="DW5" s="131">
+      <c r="DW5" s="118">
         <f t="shared" si="47"/>
         <v>46265</v>
       </c>
-      <c r="DX5" s="129">
+      <c r="DX5" s="116">
         <f t="shared" si="47"/>
         <v>46266</v>
       </c>
-      <c r="DY5" s="129">
+      <c r="DY5" s="116">
         <f t="shared" ref="DY5" si="48">DX5+1</f>
         <v>46267</v>
       </c>
-      <c r="DZ5" s="129">
+      <c r="DZ5" s="116">
         <f t="shared" ref="DZ5" si="49">DY5+1</f>
         <v>46268</v>
       </c>
-      <c r="EA5" s="129">
+      <c r="EA5" s="116">
         <f t="shared" ref="EA5" si="50">DZ5+1</f>
         <v>46269</v>
       </c>
-      <c r="EB5" s="129">
+      <c r="EB5" s="116">
         <f t="shared" ref="EB5" si="51">EA5+1</f>
         <v>46270</v>
       </c>
-      <c r="EC5" s="129">
+      <c r="EC5" s="116">
         <f t="shared" ref="EC5" si="52">EB5+1</f>
         <v>46271</v>
       </c>
-      <c r="ED5" s="131">
+      <c r="ED5" s="118">
         <f t="shared" ref="ED5" si="53">EC5+1</f>
         <v>46272</v>
       </c>
-      <c r="EE5" s="129">
+      <c r="EE5" s="116">
         <f t="shared" ref="EE5" si="54">ED5+1</f>
         <v>46273</v>
       </c>
-      <c r="EF5" s="129">
+      <c r="EF5" s="116">
         <f t="shared" ref="EF5" si="55">EE5+1</f>
         <v>46274</v>
       </c>
-      <c r="EG5" s="129">
+      <c r="EG5" s="116">
         <f t="shared" ref="EG5" si="56">EF5+1</f>
         <v>46275</v>
       </c>
-      <c r="EH5" s="129">
+      <c r="EH5" s="116">
         <f t="shared" ref="EH5" si="57">EG5+1</f>
         <v>46276</v>
       </c>
-      <c r="EI5" s="129">
+      <c r="EI5" s="116">
         <f t="shared" ref="EI5" si="58">EH5+1</f>
         <v>46277</v>
       </c>
-      <c r="EJ5" s="129">
+      <c r="EJ5" s="116">
         <f t="shared" ref="EJ5" si="59">EI5+1</f>
         <v>46278</v>
       </c>
     </row>
     <row r="6" spans="1:142" s="14" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="51"/>
-      <c r="B6" s="53"/>
-      <c r="C6" s="54"/>
-      <c r="D6" s="54"/>
-      <c r="E6" s="54"/>
+      <c r="A6" s="130"/>
+      <c r="B6" s="132"/>
+      <c r="C6" s="123"/>
+      <c r="D6" s="123"/>
+      <c r="E6" s="123"/>
       <c r="H6" s="19" t="str">
         <f t="shared" ref="H6:AM6" si="60">LEFT(TEXT(H5,"ddd"),1)</f>
         <v>M</v>
@@ -4037,11 +3955,11 @@
       <c r="C9" s="31">
         <v>0.1</v>
       </c>
-      <c r="D9" s="60">
+      <c r="D9" s="51">
         <f>Project_Start</f>
         <v>46148</v>
       </c>
-      <c r="E9" s="60">
+      <c r="E9" s="51">
         <v>46166</v>
       </c>
       <c r="F9" s="6"/>
@@ -4147,23 +4065,23 @@
       <c r="CY9" s="32"/>
       <c r="CZ9" s="32"/>
       <c r="DA9" s="32"/>
-      <c r="DB9" s="127" t="s">
+      <c r="DB9" s="119" t="s">
         <v>53</v>
       </c>
-      <c r="DC9" s="127"/>
-      <c r="DD9" s="127"/>
-      <c r="DE9" s="127"/>
-      <c r="DF9" s="127"/>
-      <c r="DG9" s="127"/>
-      <c r="DH9" s="127"/>
-      <c r="DI9" s="127"/>
-      <c r="DJ9" s="127"/>
-      <c r="DK9" s="127"/>
-      <c r="DL9" s="127"/>
-      <c r="DM9" s="127"/>
-      <c r="DN9" s="127"/>
-      <c r="DO9" s="128"/>
-      <c r="DP9" s="125"/>
+      <c r="DC9" s="119"/>
+      <c r="DD9" s="119"/>
+      <c r="DE9" s="119"/>
+      <c r="DF9" s="119"/>
+      <c r="DG9" s="119"/>
+      <c r="DH9" s="119"/>
+      <c r="DI9" s="119"/>
+      <c r="DJ9" s="119"/>
+      <c r="DK9" s="119"/>
+      <c r="DL9" s="119"/>
+      <c r="DM9" s="119"/>
+      <c r="DN9" s="119"/>
+      <c r="DO9" s="120"/>
+      <c r="DP9" s="114"/>
       <c r="DQ9" s="32"/>
       <c r="DR9" s="32"/>
       <c r="DS9" s="32"/>
@@ -4191,12 +4109,12 @@
         <v>49</v>
       </c>
       <c r="C10" s="31">
-        <v>0</v>
-      </c>
-      <c r="D10" s="60">
+        <v>1</v>
+      </c>
+      <c r="D10" s="51">
         <v>46152</v>
       </c>
-      <c r="E10" s="60">
+      <c r="E10" s="51">
         <v>46153</v>
       </c>
       <c r="F10" s="6"/>
@@ -4299,21 +4217,21 @@
       <c r="CY10" s="32"/>
       <c r="CZ10" s="32"/>
       <c r="DA10" s="32"/>
-      <c r="DB10" s="127"/>
-      <c r="DC10" s="127"/>
-      <c r="DD10" s="127"/>
-      <c r="DE10" s="127"/>
-      <c r="DF10" s="127"/>
-      <c r="DG10" s="127"/>
-      <c r="DH10" s="127"/>
-      <c r="DI10" s="127"/>
-      <c r="DJ10" s="127"/>
-      <c r="DK10" s="127"/>
-      <c r="DL10" s="127"/>
-      <c r="DM10" s="127"/>
-      <c r="DN10" s="127"/>
-      <c r="DO10" s="128"/>
-      <c r="DP10" s="125"/>
+      <c r="DB10" s="119"/>
+      <c r="DC10" s="119"/>
+      <c r="DD10" s="119"/>
+      <c r="DE10" s="119"/>
+      <c r="DF10" s="119"/>
+      <c r="DG10" s="119"/>
+      <c r="DH10" s="119"/>
+      <c r="DI10" s="119"/>
+      <c r="DJ10" s="119"/>
+      <c r="DK10" s="119"/>
+      <c r="DL10" s="119"/>
+      <c r="DM10" s="119"/>
+      <c r="DN10" s="119"/>
+      <c r="DO10" s="120"/>
+      <c r="DP10" s="114"/>
       <c r="DQ10" s="32"/>
       <c r="DR10" s="32"/>
       <c r="DS10" s="32"/>
@@ -4334,11 +4252,11 @@
       <c r="EH10" s="32"/>
       <c r="EI10" s="32"/>
       <c r="EJ10" s="32"/>
-      <c r="EK10" s="124">
+      <c r="EK10" s="113">
         <f>D11+7</f>
         <v>46174</v>
       </c>
-      <c r="EL10" s="124">
+      <c r="EL10" s="113">
         <f>E11+7</f>
         <v>46187</v>
       </c>
@@ -4351,10 +4269,10 @@
       <c r="C11" s="34">
         <v>0.05</v>
       </c>
-      <c r="D11" s="61">
+      <c r="D11" s="52">
         <v>46167</v>
       </c>
-      <c r="E11" s="61">
+      <c r="E11" s="52">
         <v>46180</v>
       </c>
       <c r="F11" s="6"/>
@@ -4460,21 +4378,21 @@
       <c r="CY11" s="32"/>
       <c r="CZ11" s="32"/>
       <c r="DA11" s="32"/>
-      <c r="DB11" s="127"/>
-      <c r="DC11" s="127"/>
-      <c r="DD11" s="127"/>
-      <c r="DE11" s="127"/>
-      <c r="DF11" s="127"/>
-      <c r="DG11" s="127"/>
-      <c r="DH11" s="127"/>
-      <c r="DI11" s="127"/>
-      <c r="DJ11" s="127"/>
-      <c r="DK11" s="127"/>
-      <c r="DL11" s="127"/>
-      <c r="DM11" s="127"/>
-      <c r="DN11" s="127"/>
-      <c r="DO11" s="128"/>
-      <c r="DP11" s="125"/>
+      <c r="DB11" s="119"/>
+      <c r="DC11" s="119"/>
+      <c r="DD11" s="119"/>
+      <c r="DE11" s="119"/>
+      <c r="DF11" s="119"/>
+      <c r="DG11" s="119"/>
+      <c r="DH11" s="119"/>
+      <c r="DI11" s="119"/>
+      <c r="DJ11" s="119"/>
+      <c r="DK11" s="119"/>
+      <c r="DL11" s="119"/>
+      <c r="DM11" s="119"/>
+      <c r="DN11" s="119"/>
+      <c r="DO11" s="120"/>
+      <c r="DP11" s="114"/>
       <c r="DQ11" s="32"/>
       <c r="DR11" s="32"/>
       <c r="DS11" s="32"/>
@@ -4495,12 +4413,12 @@
       <c r="EH11" s="32"/>
       <c r="EI11" s="32"/>
       <c r="EJ11" s="32"/>
-      <c r="EK11" s="124">
-        <f t="shared" ref="EK11:EK48" si="66">D12+7</f>
+      <c r="EK11" s="113">
+        <f t="shared" ref="EK11:EK13" si="66">D12+7</f>
         <v>46163</v>
       </c>
-      <c r="EL11" s="124">
-        <f t="shared" ref="EL11:EL48" si="67">E12+7</f>
+      <c r="EL11" s="113">
+        <f t="shared" ref="EL11:EL13" si="67">E12+7</f>
         <v>46188</v>
       </c>
     </row>
@@ -4512,10 +4430,10 @@
       <c r="C12" s="34">
         <v>0.05</v>
       </c>
-      <c r="D12" s="61">
+      <c r="D12" s="52">
         <v>46156</v>
       </c>
-      <c r="E12" s="61">
+      <c r="E12" s="52">
         <v>46181</v>
       </c>
       <c r="F12" s="6"/>
@@ -4621,21 +4539,21 @@
       <c r="CY12" s="32"/>
       <c r="CZ12" s="32"/>
       <c r="DA12" s="32"/>
-      <c r="DB12" s="127"/>
-      <c r="DC12" s="127"/>
-      <c r="DD12" s="127"/>
-      <c r="DE12" s="127"/>
-      <c r="DF12" s="127"/>
-      <c r="DG12" s="127"/>
-      <c r="DH12" s="127"/>
-      <c r="DI12" s="127"/>
-      <c r="DJ12" s="127"/>
-      <c r="DK12" s="127"/>
-      <c r="DL12" s="127"/>
-      <c r="DM12" s="127"/>
-      <c r="DN12" s="127"/>
-      <c r="DO12" s="128"/>
-      <c r="DP12" s="125"/>
+      <c r="DB12" s="119"/>
+      <c r="DC12" s="119"/>
+      <c r="DD12" s="119"/>
+      <c r="DE12" s="119"/>
+      <c r="DF12" s="119"/>
+      <c r="DG12" s="119"/>
+      <c r="DH12" s="119"/>
+      <c r="DI12" s="119"/>
+      <c r="DJ12" s="119"/>
+      <c r="DK12" s="119"/>
+      <c r="DL12" s="119"/>
+      <c r="DM12" s="119"/>
+      <c r="DN12" s="119"/>
+      <c r="DO12" s="120"/>
+      <c r="DP12" s="114"/>
       <c r="DQ12" s="32"/>
       <c r="DR12" s="32"/>
       <c r="DS12" s="32"/>
@@ -4656,27 +4574,27 @@
       <c r="EH12" s="32"/>
       <c r="EI12" s="32"/>
       <c r="EJ12" s="32"/>
-      <c r="EK12" s="124">
+      <c r="EK12" s="113">
         <f t="shared" si="66"/>
         <v>46163</v>
       </c>
-      <c r="EL12" s="124">
+      <c r="EL12" s="113">
         <f t="shared" si="67"/>
         <v>46188</v>
       </c>
     </row>
     <row r="13" spans="1:142" s="29" customFormat="1" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A13" s="4"/>
-      <c r="B13" s="73" t="s">
+      <c r="B13" s="62" t="s">
         <v>14</v>
       </c>
       <c r="C13" s="34">
         <v>0.05</v>
       </c>
-      <c r="D13" s="61">
+      <c r="D13" s="52">
         <v>46156</v>
       </c>
-      <c r="E13" s="61">
+      <c r="E13" s="52">
         <v>46181</v>
       </c>
       <c r="F13" s="6"/>
@@ -4779,21 +4697,21 @@
       <c r="CY13" s="32"/>
       <c r="CZ13" s="32"/>
       <c r="DA13" s="32"/>
-      <c r="DB13" s="127"/>
-      <c r="DC13" s="127"/>
-      <c r="DD13" s="127"/>
-      <c r="DE13" s="127"/>
-      <c r="DF13" s="127"/>
-      <c r="DG13" s="127"/>
-      <c r="DH13" s="127"/>
-      <c r="DI13" s="127"/>
-      <c r="DJ13" s="127"/>
-      <c r="DK13" s="127"/>
-      <c r="DL13" s="127"/>
-      <c r="DM13" s="127"/>
-      <c r="DN13" s="127"/>
-      <c r="DO13" s="128"/>
-      <c r="DP13" s="125"/>
+      <c r="DB13" s="119"/>
+      <c r="DC13" s="119"/>
+      <c r="DD13" s="119"/>
+      <c r="DE13" s="119"/>
+      <c r="DF13" s="119"/>
+      <c r="DG13" s="119"/>
+      <c r="DH13" s="119"/>
+      <c r="DI13" s="119"/>
+      <c r="DJ13" s="119"/>
+      <c r="DK13" s="119"/>
+      <c r="DL13" s="119"/>
+      <c r="DM13" s="119"/>
+      <c r="DN13" s="119"/>
+      <c r="DO13" s="120"/>
+      <c r="DP13" s="114"/>
       <c r="DQ13" s="32"/>
       <c r="DR13" s="32"/>
       <c r="DS13" s="32"/>
@@ -4814,11 +4732,11 @@
       <c r="EH13" s="32"/>
       <c r="EI13" s="32"/>
       <c r="EJ13" s="32"/>
-      <c r="EK13" s="124">
+      <c r="EK13" s="113">
         <f t="shared" si="66"/>
         <v>46189</v>
       </c>
-      <c r="EL13" s="124">
+      <c r="EL13" s="113">
         <f t="shared" si="67"/>
         <v>46190</v>
       </c>
@@ -4831,10 +4749,10 @@
       <c r="C14" s="34">
         <v>0</v>
       </c>
-      <c r="D14" s="61">
+      <c r="D14" s="52">
         <v>46182</v>
       </c>
-      <c r="E14" s="61">
+      <c r="E14" s="52">
         <v>46183</v>
       </c>
       <c r="F14" s="6"/>
@@ -4940,21 +4858,21 @@
       <c r="CY14" s="32"/>
       <c r="CZ14" s="32"/>
       <c r="DA14" s="32"/>
-      <c r="DB14" s="127"/>
-      <c r="DC14" s="127"/>
-      <c r="DD14" s="127"/>
-      <c r="DE14" s="127"/>
-      <c r="DF14" s="127"/>
-      <c r="DG14" s="127"/>
-      <c r="DH14" s="127"/>
-      <c r="DI14" s="127"/>
-      <c r="DJ14" s="127"/>
-      <c r="DK14" s="127"/>
-      <c r="DL14" s="127"/>
-      <c r="DM14" s="127"/>
-      <c r="DN14" s="127"/>
-      <c r="DO14" s="128"/>
-      <c r="DP14" s="125"/>
+      <c r="DB14" s="119"/>
+      <c r="DC14" s="119"/>
+      <c r="DD14" s="119"/>
+      <c r="DE14" s="119"/>
+      <c r="DF14" s="119"/>
+      <c r="DG14" s="119"/>
+      <c r="DH14" s="119"/>
+      <c r="DI14" s="119"/>
+      <c r="DJ14" s="119"/>
+      <c r="DK14" s="119"/>
+      <c r="DL14" s="119"/>
+      <c r="DM14" s="119"/>
+      <c r="DN14" s="119"/>
+      <c r="DO14" s="120"/>
+      <c r="DP14" s="114"/>
       <c r="DQ14" s="32"/>
       <c r="DR14" s="32"/>
       <c r="DS14" s="32"/>
@@ -4975,11 +4893,11 @@
       <c r="EH14" s="32"/>
       <c r="EI14" s="32"/>
       <c r="EJ14" s="32"/>
-      <c r="EK14" s="124">
+      <c r="EK14" s="113">
         <f>D14-10</f>
         <v>46172</v>
       </c>
-      <c r="EL14" s="124">
+      <c r="EL14" s="113">
         <f>E14-10</f>
         <v>46173</v>
       </c>
@@ -4992,10 +4910,10 @@
       <c r="C15" s="34">
         <v>0</v>
       </c>
-      <c r="D15" s="61">
+      <c r="D15" s="52">
         <v>46183</v>
       </c>
-      <c r="E15" s="61">
+      <c r="E15" s="52">
         <v>46183</v>
       </c>
       <c r="F15" s="6"/>
@@ -5101,21 +5019,21 @@
       <c r="CY15" s="32"/>
       <c r="CZ15" s="32"/>
       <c r="DA15" s="32"/>
-      <c r="DB15" s="127"/>
-      <c r="DC15" s="127"/>
-      <c r="DD15" s="127"/>
-      <c r="DE15" s="127"/>
-      <c r="DF15" s="127"/>
-      <c r="DG15" s="127"/>
-      <c r="DH15" s="127"/>
-      <c r="DI15" s="127"/>
-      <c r="DJ15" s="127"/>
-      <c r="DK15" s="127"/>
-      <c r="DL15" s="127"/>
-      <c r="DM15" s="127"/>
-      <c r="DN15" s="127"/>
-      <c r="DO15" s="128"/>
-      <c r="DP15" s="125"/>
+      <c r="DB15" s="119"/>
+      <c r="DC15" s="119"/>
+      <c r="DD15" s="119"/>
+      <c r="DE15" s="119"/>
+      <c r="DF15" s="119"/>
+      <c r="DG15" s="119"/>
+      <c r="DH15" s="119"/>
+      <c r="DI15" s="119"/>
+      <c r="DJ15" s="119"/>
+      <c r="DK15" s="119"/>
+      <c r="DL15" s="119"/>
+      <c r="DM15" s="119"/>
+      <c r="DN15" s="119"/>
+      <c r="DO15" s="120"/>
+      <c r="DP15" s="114"/>
       <c r="DQ15" s="32"/>
       <c r="DR15" s="32"/>
       <c r="DS15" s="32"/>
@@ -5136,27 +5054,27 @@
       <c r="EH15" s="32"/>
       <c r="EI15" s="32"/>
       <c r="EJ15" s="32"/>
-      <c r="EK15" s="124">
-        <f t="shared" ref="EK15:EK35" si="68">D15-10</f>
+      <c r="EK15" s="113">
+        <f t="shared" ref="EK15:EK17" si="68">D15-10</f>
         <v>46173</v>
       </c>
-      <c r="EL15" s="124">
-        <f t="shared" ref="EL15:EL35" si="69">E15-10</f>
+      <c r="EL15" s="113">
+        <f t="shared" ref="EL15:EL18" si="69">E15-10</f>
         <v>46173</v>
       </c>
     </row>
     <row r="16" spans="1:142" s="29" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A16" s="4"/>
-      <c r="B16" s="73" t="s">
+      <c r="B16" s="62" t="s">
         <v>18</v>
       </c>
       <c r="C16" s="34">
         <v>0</v>
       </c>
-      <c r="D16" s="61">
+      <c r="D16" s="52">
         <v>46183</v>
       </c>
-      <c r="E16" s="61">
+      <c r="E16" s="52">
         <v>46183</v>
       </c>
       <c r="F16" s="6"/>
@@ -5262,21 +5180,21 @@
       <c r="CY16" s="32"/>
       <c r="CZ16" s="32"/>
       <c r="DA16" s="32"/>
-      <c r="DB16" s="127"/>
-      <c r="DC16" s="127"/>
-      <c r="DD16" s="127"/>
-      <c r="DE16" s="127"/>
-      <c r="DF16" s="127"/>
-      <c r="DG16" s="127"/>
-      <c r="DH16" s="127"/>
-      <c r="DI16" s="127"/>
-      <c r="DJ16" s="127"/>
-      <c r="DK16" s="127"/>
-      <c r="DL16" s="127"/>
-      <c r="DM16" s="127"/>
-      <c r="DN16" s="127"/>
-      <c r="DO16" s="128"/>
-      <c r="DP16" s="125"/>
+      <c r="DB16" s="119"/>
+      <c r="DC16" s="119"/>
+      <c r="DD16" s="119"/>
+      <c r="DE16" s="119"/>
+      <c r="DF16" s="119"/>
+      <c r="DG16" s="119"/>
+      <c r="DH16" s="119"/>
+      <c r="DI16" s="119"/>
+      <c r="DJ16" s="119"/>
+      <c r="DK16" s="119"/>
+      <c r="DL16" s="119"/>
+      <c r="DM16" s="119"/>
+      <c r="DN16" s="119"/>
+      <c r="DO16" s="120"/>
+      <c r="DP16" s="114"/>
       <c r="DQ16" s="32"/>
       <c r="DR16" s="32"/>
       <c r="DS16" s="32"/>
@@ -5297,11 +5215,11 @@
       <c r="EH16" s="32"/>
       <c r="EI16" s="32"/>
       <c r="EJ16" s="32"/>
-      <c r="EK16" s="124">
+      <c r="EK16" s="113">
         <f t="shared" si="68"/>
         <v>46173</v>
       </c>
-      <c r="EL16" s="124">
+      <c r="EL16" s="113">
         <f t="shared" si="69"/>
         <v>46173</v>
       </c>
@@ -5312,48 +5230,48 @@
         <v>15</v>
       </c>
       <c r="C17" s="37"/>
-      <c r="D17" s="62"/>
-      <c r="E17" s="63"/>
+      <c r="D17" s="53"/>
+      <c r="E17" s="54"/>
       <c r="F17" s="6"/>
       <c r="G17" s="3" t="str">
         <f t="shared" si="65"/>
         <v/>
       </c>
-      <c r="DB17" s="127"/>
-      <c r="DC17" s="127"/>
-      <c r="DD17" s="127"/>
-      <c r="DE17" s="127"/>
-      <c r="DF17" s="127"/>
-      <c r="DG17" s="127"/>
-      <c r="DH17" s="127"/>
-      <c r="DI17" s="127"/>
-      <c r="DJ17" s="127"/>
-      <c r="DK17" s="127"/>
-      <c r="DL17" s="127"/>
-      <c r="DM17" s="127"/>
-      <c r="DN17" s="127"/>
-      <c r="DO17" s="128"/>
-      <c r="EK17" s="124">
+      <c r="DB17" s="119"/>
+      <c r="DC17" s="119"/>
+      <c r="DD17" s="119"/>
+      <c r="DE17" s="119"/>
+      <c r="DF17" s="119"/>
+      <c r="DG17" s="119"/>
+      <c r="DH17" s="119"/>
+      <c r="DI17" s="119"/>
+      <c r="DJ17" s="119"/>
+      <c r="DK17" s="119"/>
+      <c r="DL17" s="119"/>
+      <c r="DM17" s="119"/>
+      <c r="DN17" s="119"/>
+      <c r="DO17" s="120"/>
+      <c r="EK17" s="113">
         <f t="shared" si="68"/>
         <v>-10</v>
       </c>
-      <c r="EL17" s="124">
+      <c r="EL17" s="113">
         <f t="shared" si="69"/>
         <v>-10</v>
       </c>
     </row>
     <row r="18" spans="1:142" s="29" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A18" s="5"/>
-      <c r="B18" s="74" t="s">
+      <c r="B18" s="63" t="s">
         <v>19</v>
       </c>
       <c r="C18" s="39">
         <v>0</v>
       </c>
-      <c r="D18" s="64">
+      <c r="D18" s="55">
         <v>46184</v>
       </c>
-      <c r="E18" s="64">
+      <c r="E18" s="55">
         <v>46185</v>
       </c>
       <c r="F18" s="6"/>
@@ -5459,21 +5377,21 @@
       <c r="CY18" s="32"/>
       <c r="CZ18" s="32"/>
       <c r="DA18" s="32"/>
-      <c r="DB18" s="127"/>
-      <c r="DC18" s="127"/>
-      <c r="DD18" s="127"/>
-      <c r="DE18" s="127"/>
-      <c r="DF18" s="127"/>
-      <c r="DG18" s="127"/>
-      <c r="DH18" s="127"/>
-      <c r="DI18" s="127"/>
-      <c r="DJ18" s="127"/>
-      <c r="DK18" s="127"/>
-      <c r="DL18" s="127"/>
-      <c r="DM18" s="127"/>
-      <c r="DN18" s="127"/>
-      <c r="DO18" s="128"/>
-      <c r="DP18" s="125"/>
+      <c r="DB18" s="119"/>
+      <c r="DC18" s="119"/>
+      <c r="DD18" s="119"/>
+      <c r="DE18" s="119"/>
+      <c r="DF18" s="119"/>
+      <c r="DG18" s="119"/>
+      <c r="DH18" s="119"/>
+      <c r="DI18" s="119"/>
+      <c r="DJ18" s="119"/>
+      <c r="DK18" s="119"/>
+      <c r="DL18" s="119"/>
+      <c r="DM18" s="119"/>
+      <c r="DN18" s="119"/>
+      <c r="DO18" s="120"/>
+      <c r="DP18" s="114"/>
       <c r="DQ18" s="32"/>
       <c r="DR18" s="32"/>
       <c r="DS18" s="32"/>
@@ -5494,11 +5412,11 @@
       <c r="EH18" s="32"/>
       <c r="EI18" s="32"/>
       <c r="EJ18" s="32"/>
-      <c r="EK18" s="124">
+      <c r="EK18" s="113">
         <f>D18-10</f>
         <v>46174</v>
       </c>
-      <c r="EL18" s="124">
+      <c r="EL18" s="113">
         <f t="shared" si="69"/>
         <v>46175</v>
       </c>
@@ -5511,10 +5429,10 @@
       <c r="C19" s="39">
         <v>0</v>
       </c>
-      <c r="D19" s="64">
+      <c r="D19" s="55">
         <v>46186</v>
       </c>
-      <c r="E19" s="64">
+      <c r="E19" s="55">
         <v>46186</v>
       </c>
       <c r="F19" s="6"/>
@@ -5620,21 +5538,21 @@
       <c r="CY19" s="32"/>
       <c r="CZ19" s="32"/>
       <c r="DA19" s="32"/>
-      <c r="DB19" s="127"/>
-      <c r="DC19" s="127"/>
-      <c r="DD19" s="127"/>
-      <c r="DE19" s="127"/>
-      <c r="DF19" s="127"/>
-      <c r="DG19" s="127"/>
-      <c r="DH19" s="127"/>
-      <c r="DI19" s="127"/>
-      <c r="DJ19" s="127"/>
-      <c r="DK19" s="127"/>
-      <c r="DL19" s="127"/>
-      <c r="DM19" s="127"/>
-      <c r="DN19" s="127"/>
-      <c r="DO19" s="128"/>
-      <c r="DP19" s="125"/>
+      <c r="DB19" s="119"/>
+      <c r="DC19" s="119"/>
+      <c r="DD19" s="119"/>
+      <c r="DE19" s="119"/>
+      <c r="DF19" s="119"/>
+      <c r="DG19" s="119"/>
+      <c r="DH19" s="119"/>
+      <c r="DI19" s="119"/>
+      <c r="DJ19" s="119"/>
+      <c r="DK19" s="119"/>
+      <c r="DL19" s="119"/>
+      <c r="DM19" s="119"/>
+      <c r="DN19" s="119"/>
+      <c r="DO19" s="120"/>
+      <c r="DP19" s="114"/>
       <c r="DQ19" s="32"/>
       <c r="DR19" s="32"/>
       <c r="DS19" s="32"/>
@@ -5655,11 +5573,11 @@
       <c r="EH19" s="32"/>
       <c r="EI19" s="32"/>
       <c r="EJ19" s="32"/>
-      <c r="EK19" s="124">
+      <c r="EK19" s="113">
         <f>D19-1</f>
         <v>46185</v>
       </c>
-      <c r="EL19" s="124">
+      <c r="EL19" s="113">
         <f>E19-1</f>
         <v>46185</v>
       </c>
@@ -5672,10 +5590,10 @@
       <c r="C20" s="39">
         <v>0</v>
       </c>
-      <c r="D20" s="64">
+      <c r="D20" s="55">
         <v>46186</v>
       </c>
-      <c r="E20" s="64">
+      <c r="E20" s="55">
         <v>46186</v>
       </c>
       <c r="F20" s="6"/>
@@ -5778,21 +5696,21 @@
       <c r="CY20" s="32"/>
       <c r="CZ20" s="32"/>
       <c r="DA20" s="32"/>
-      <c r="DB20" s="127"/>
-      <c r="DC20" s="127"/>
-      <c r="DD20" s="127"/>
-      <c r="DE20" s="127"/>
-      <c r="DF20" s="127"/>
-      <c r="DG20" s="127"/>
-      <c r="DH20" s="127"/>
-      <c r="DI20" s="127"/>
-      <c r="DJ20" s="127"/>
-      <c r="DK20" s="127"/>
-      <c r="DL20" s="127"/>
-      <c r="DM20" s="127"/>
-      <c r="DN20" s="127"/>
-      <c r="DO20" s="128"/>
-      <c r="DP20" s="125"/>
+      <c r="DB20" s="119"/>
+      <c r="DC20" s="119"/>
+      <c r="DD20" s="119"/>
+      <c r="DE20" s="119"/>
+      <c r="DF20" s="119"/>
+      <c r="DG20" s="119"/>
+      <c r="DH20" s="119"/>
+      <c r="DI20" s="119"/>
+      <c r="DJ20" s="119"/>
+      <c r="DK20" s="119"/>
+      <c r="DL20" s="119"/>
+      <c r="DM20" s="119"/>
+      <c r="DN20" s="119"/>
+      <c r="DO20" s="120"/>
+      <c r="DP20" s="114"/>
       <c r="DQ20" s="32"/>
       <c r="DR20" s="32"/>
       <c r="DS20" s="32"/>
@@ -5813,12 +5731,12 @@
       <c r="EH20" s="32"/>
       <c r="EI20" s="32"/>
       <c r="EJ20" s="32"/>
-      <c r="EK20" s="124">
-        <f t="shared" ref="EK20:EK48" si="70">D20-1</f>
+      <c r="EK20" s="113">
+        <f t="shared" ref="EK20:EK40" si="70">D20-1</f>
         <v>46185</v>
       </c>
-      <c r="EL20" s="124">
-        <f t="shared" ref="EL20:EL48" si="71">E20-1</f>
+      <c r="EL20" s="113">
+        <f t="shared" ref="EL20:EL40" si="71">E20-1</f>
         <v>46185</v>
       </c>
     </row>
@@ -5828,8 +5746,8 @@
         <v>17</v>
       </c>
       <c r="C21" s="41"/>
-      <c r="D21" s="65"/>
-      <c r="E21" s="66"/>
+      <c r="D21" s="56"/>
+      <c r="E21" s="57"/>
       <c r="F21" s="6"/>
       <c r="G21" s="3" t="str">
         <f t="shared" si="65"/>
@@ -5933,20 +5851,20 @@
       <c r="CY21" s="42"/>
       <c r="CZ21" s="42"/>
       <c r="DA21" s="42"/>
-      <c r="DB21" s="127"/>
-      <c r="DC21" s="127"/>
-      <c r="DD21" s="127"/>
-      <c r="DE21" s="127"/>
-      <c r="DF21" s="127"/>
-      <c r="DG21" s="127"/>
-      <c r="DH21" s="127"/>
-      <c r="DI21" s="127"/>
-      <c r="DJ21" s="127"/>
-      <c r="DK21" s="127"/>
-      <c r="DL21" s="127"/>
-      <c r="DM21" s="127"/>
-      <c r="DN21" s="127"/>
-      <c r="DO21" s="128"/>
+      <c r="DB21" s="119"/>
+      <c r="DC21" s="119"/>
+      <c r="DD21" s="119"/>
+      <c r="DE21" s="119"/>
+      <c r="DF21" s="119"/>
+      <c r="DG21" s="119"/>
+      <c r="DH21" s="119"/>
+      <c r="DI21" s="119"/>
+      <c r="DJ21" s="119"/>
+      <c r="DK21" s="119"/>
+      <c r="DL21" s="119"/>
+      <c r="DM21" s="119"/>
+      <c r="DN21" s="119"/>
+      <c r="DO21" s="120"/>
       <c r="DP21" s="42"/>
       <c r="DQ21" s="42"/>
       <c r="DR21" s="42"/>
@@ -5968,11 +5886,11 @@
       <c r="EH21" s="42"/>
       <c r="EI21" s="42"/>
       <c r="EJ21" s="42"/>
-      <c r="EK21" s="124">
+      <c r="EK21" s="113">
         <f t="shared" si="70"/>
         <v>-1</v>
       </c>
-      <c r="EL21" s="124">
+      <c r="EL21" s="113">
         <f t="shared" si="71"/>
         <v>-1</v>
       </c>
@@ -5985,10 +5903,10 @@
       <c r="C22" s="44">
         <v>0</v>
       </c>
-      <c r="D22" s="67">
+      <c r="D22" s="58">
         <v>46187</v>
       </c>
-      <c r="E22" s="67">
+      <c r="E22" s="58">
         <v>46189</v>
       </c>
       <c r="F22" s="6"/>
@@ -6094,21 +6012,21 @@
       <c r="CY22" s="32"/>
       <c r="CZ22" s="32"/>
       <c r="DA22" s="32"/>
-      <c r="DB22" s="127"/>
-      <c r="DC22" s="127"/>
-      <c r="DD22" s="127"/>
-      <c r="DE22" s="127"/>
-      <c r="DF22" s="127"/>
-      <c r="DG22" s="127"/>
-      <c r="DH22" s="127"/>
-      <c r="DI22" s="127"/>
-      <c r="DJ22" s="127"/>
-      <c r="DK22" s="127"/>
-      <c r="DL22" s="127"/>
-      <c r="DM22" s="127"/>
-      <c r="DN22" s="127"/>
-      <c r="DO22" s="128"/>
-      <c r="DP22" s="125"/>
+      <c r="DB22" s="119"/>
+      <c r="DC22" s="119"/>
+      <c r="DD22" s="119"/>
+      <c r="DE22" s="119"/>
+      <c r="DF22" s="119"/>
+      <c r="DG22" s="119"/>
+      <c r="DH22" s="119"/>
+      <c r="DI22" s="119"/>
+      <c r="DJ22" s="119"/>
+      <c r="DK22" s="119"/>
+      <c r="DL22" s="119"/>
+      <c r="DM22" s="119"/>
+      <c r="DN22" s="119"/>
+      <c r="DO22" s="120"/>
+      <c r="DP22" s="114"/>
       <c r="DQ22" s="32"/>
       <c r="DR22" s="32"/>
       <c r="DS22" s="32"/>
@@ -6129,27 +6047,27 @@
       <c r="EH22" s="32"/>
       <c r="EI22" s="32"/>
       <c r="EJ22" s="32"/>
-      <c r="EK22" s="124">
+      <c r="EK22" s="113">
         <f t="shared" si="70"/>
         <v>46186</v>
       </c>
-      <c r="EL22" s="124">
+      <c r="EL22" s="113">
         <f t="shared" si="71"/>
         <v>46188</v>
       </c>
     </row>
     <row r="23" spans="1:142" s="29" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A23" s="4"/>
-      <c r="B23" s="75" t="s">
+      <c r="B23" s="64" t="s">
         <v>21</v>
       </c>
       <c r="C23" s="44">
         <v>0</v>
       </c>
-      <c r="D23" s="67">
+      <c r="D23" s="58">
         <v>46190</v>
       </c>
-      <c r="E23" s="67">
+      <c r="E23" s="58">
         <v>46190</v>
       </c>
       <c r="F23" s="6"/>
@@ -6255,21 +6173,21 @@
       <c r="CY23" s="32"/>
       <c r="CZ23" s="32"/>
       <c r="DA23" s="32"/>
-      <c r="DB23" s="127"/>
-      <c r="DC23" s="127"/>
-      <c r="DD23" s="127"/>
-      <c r="DE23" s="127"/>
-      <c r="DF23" s="127"/>
-      <c r="DG23" s="127"/>
-      <c r="DH23" s="127"/>
-      <c r="DI23" s="127"/>
-      <c r="DJ23" s="127"/>
-      <c r="DK23" s="127"/>
-      <c r="DL23" s="127"/>
-      <c r="DM23" s="127"/>
-      <c r="DN23" s="127"/>
-      <c r="DO23" s="128"/>
-      <c r="DP23" s="125"/>
+      <c r="DB23" s="119"/>
+      <c r="DC23" s="119"/>
+      <c r="DD23" s="119"/>
+      <c r="DE23" s="119"/>
+      <c r="DF23" s="119"/>
+      <c r="DG23" s="119"/>
+      <c r="DH23" s="119"/>
+      <c r="DI23" s="119"/>
+      <c r="DJ23" s="119"/>
+      <c r="DK23" s="119"/>
+      <c r="DL23" s="119"/>
+      <c r="DM23" s="119"/>
+      <c r="DN23" s="119"/>
+      <c r="DO23" s="120"/>
+      <c r="DP23" s="114"/>
       <c r="DQ23" s="32"/>
       <c r="DR23" s="32"/>
       <c r="DS23" s="32"/>
@@ -6290,11 +6208,11 @@
       <c r="EH23" s="32"/>
       <c r="EI23" s="32"/>
       <c r="EJ23" s="32"/>
-      <c r="EK23" s="124">
+      <c r="EK23" s="113">
         <f t="shared" si="70"/>
         <v>46189</v>
       </c>
-      <c r="EL23" s="124">
+      <c r="EL23" s="113">
         <f t="shared" si="71"/>
         <v>46189</v>
       </c>
@@ -6305,8 +6223,8 @@
         <v>22</v>
       </c>
       <c r="C24" s="46"/>
-      <c r="D24" s="68"/>
-      <c r="E24" s="69"/>
+      <c r="D24" s="59"/>
+      <c r="E24" s="60"/>
       <c r="F24" s="6"/>
       <c r="G24" s="3" t="str">
         <f t="shared" si="65"/>
@@ -6410,20 +6328,20 @@
       <c r="CY24" s="47"/>
       <c r="CZ24" s="47"/>
       <c r="DA24" s="47"/>
-      <c r="DB24" s="127"/>
-      <c r="DC24" s="127"/>
-      <c r="DD24" s="127"/>
-      <c r="DE24" s="127"/>
-      <c r="DF24" s="127"/>
-      <c r="DG24" s="127"/>
-      <c r="DH24" s="127"/>
-      <c r="DI24" s="127"/>
-      <c r="DJ24" s="127"/>
-      <c r="DK24" s="127"/>
-      <c r="DL24" s="127"/>
-      <c r="DM24" s="127"/>
-      <c r="DN24" s="127"/>
-      <c r="DO24" s="128"/>
+      <c r="DB24" s="119"/>
+      <c r="DC24" s="119"/>
+      <c r="DD24" s="119"/>
+      <c r="DE24" s="119"/>
+      <c r="DF24" s="119"/>
+      <c r="DG24" s="119"/>
+      <c r="DH24" s="119"/>
+      <c r="DI24" s="119"/>
+      <c r="DJ24" s="119"/>
+      <c r="DK24" s="119"/>
+      <c r="DL24" s="119"/>
+      <c r="DM24" s="119"/>
+      <c r="DN24" s="119"/>
+      <c r="DO24" s="120"/>
       <c r="DP24" s="47"/>
       <c r="DQ24" s="47"/>
       <c r="DR24" s="47"/>
@@ -6445,11 +6363,11 @@
       <c r="EH24" s="47"/>
       <c r="EI24" s="47"/>
       <c r="EJ24" s="47"/>
-      <c r="EK24" s="124">
+      <c r="EK24" s="113">
         <f t="shared" si="70"/>
         <v>-1</v>
       </c>
-      <c r="EL24" s="124">
+      <c r="EL24" s="113">
         <f t="shared" si="71"/>
         <v>-1</v>
       </c>
@@ -6462,10 +6380,10 @@
       <c r="C25" s="49">
         <v>0</v>
       </c>
-      <c r="D25" s="70">
+      <c r="D25" s="61">
         <v>46191</v>
       </c>
-      <c r="E25" s="70">
+      <c r="E25" s="61">
         <v>46192</v>
       </c>
       <c r="F25" s="6"/>
@@ -6571,21 +6489,21 @@
       <c r="CY25" s="32"/>
       <c r="CZ25" s="32"/>
       <c r="DA25" s="32"/>
-      <c r="DB25" s="127"/>
-      <c r="DC25" s="127"/>
-      <c r="DD25" s="127"/>
-      <c r="DE25" s="127"/>
-      <c r="DF25" s="127"/>
-      <c r="DG25" s="127"/>
-      <c r="DH25" s="127"/>
-      <c r="DI25" s="127"/>
-      <c r="DJ25" s="127"/>
-      <c r="DK25" s="127"/>
-      <c r="DL25" s="127"/>
-      <c r="DM25" s="127"/>
-      <c r="DN25" s="127"/>
-      <c r="DO25" s="128"/>
-      <c r="DP25" s="125"/>
+      <c r="DB25" s="119"/>
+      <c r="DC25" s="119"/>
+      <c r="DD25" s="119"/>
+      <c r="DE25" s="119"/>
+      <c r="DF25" s="119"/>
+      <c r="DG25" s="119"/>
+      <c r="DH25" s="119"/>
+      <c r="DI25" s="119"/>
+      <c r="DJ25" s="119"/>
+      <c r="DK25" s="119"/>
+      <c r="DL25" s="119"/>
+      <c r="DM25" s="119"/>
+      <c r="DN25" s="119"/>
+      <c r="DO25" s="120"/>
+      <c r="DP25" s="114"/>
       <c r="DQ25" s="32"/>
       <c r="DR25" s="32"/>
       <c r="DS25" s="32"/>
@@ -6606,27 +6524,27 @@
       <c r="EH25" s="32"/>
       <c r="EI25" s="32"/>
       <c r="EJ25" s="32"/>
-      <c r="EK25" s="124">
+      <c r="EK25" s="113">
         <f t="shared" si="70"/>
         <v>46190</v>
       </c>
-      <c r="EL25" s="124">
+      <c r="EL25" s="113">
         <f t="shared" si="71"/>
         <v>46191</v>
       </c>
     </row>
     <row r="26" spans="1:142" s="29" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A26" s="4"/>
-      <c r="B26" s="76" t="s">
+      <c r="B26" s="65" t="s">
         <v>23</v>
       </c>
       <c r="C26" s="49">
         <v>0</v>
       </c>
-      <c r="D26" s="70">
+      <c r="D26" s="61">
         <v>46192</v>
       </c>
-      <c r="E26" s="70">
+      <c r="E26" s="61">
         <v>46195</v>
       </c>
       <c r="F26" s="6"/>
@@ -6732,21 +6650,21 @@
       <c r="CY26" s="32"/>
       <c r="CZ26" s="32"/>
       <c r="DA26" s="32"/>
-      <c r="DB26" s="127"/>
-      <c r="DC26" s="127"/>
-      <c r="DD26" s="127"/>
-      <c r="DE26" s="127"/>
-      <c r="DF26" s="127"/>
-      <c r="DG26" s="127"/>
-      <c r="DH26" s="127"/>
-      <c r="DI26" s="127"/>
-      <c r="DJ26" s="127"/>
-      <c r="DK26" s="127"/>
-      <c r="DL26" s="127"/>
-      <c r="DM26" s="127"/>
-      <c r="DN26" s="127"/>
-      <c r="DO26" s="128"/>
-      <c r="DP26" s="125"/>
+      <c r="DB26" s="119"/>
+      <c r="DC26" s="119"/>
+      <c r="DD26" s="119"/>
+      <c r="DE26" s="119"/>
+      <c r="DF26" s="119"/>
+      <c r="DG26" s="119"/>
+      <c r="DH26" s="119"/>
+      <c r="DI26" s="119"/>
+      <c r="DJ26" s="119"/>
+      <c r="DK26" s="119"/>
+      <c r="DL26" s="119"/>
+      <c r="DM26" s="119"/>
+      <c r="DN26" s="119"/>
+      <c r="DO26" s="120"/>
+      <c r="DP26" s="114"/>
       <c r="DQ26" s="32"/>
       <c r="DR26" s="32"/>
       <c r="DS26" s="32"/>
@@ -6767,27 +6685,27 @@
       <c r="EH26" s="32"/>
       <c r="EI26" s="32"/>
       <c r="EJ26" s="32"/>
-      <c r="EK26" s="124">
+      <c r="EK26" s="113">
         <f t="shared" si="70"/>
         <v>46191</v>
       </c>
-      <c r="EL26" s="124">
+      <c r="EL26" s="113">
         <f t="shared" si="71"/>
         <v>46194</v>
       </c>
     </row>
     <row r="27" spans="1:142" s="29" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A27" s="4"/>
-      <c r="B27" s="76" t="s">
+      <c r="B27" s="65" t="s">
         <v>30</v>
       </c>
       <c r="C27" s="49">
         <v>0</v>
       </c>
-      <c r="D27" s="70">
+      <c r="D27" s="61">
         <v>46196</v>
       </c>
-      <c r="E27" s="70">
+      <c r="E27" s="61">
         <v>46199</v>
       </c>
       <c r="F27" s="6"/>
@@ -6893,21 +6811,21 @@
       <c r="CY27" s="32"/>
       <c r="CZ27" s="32"/>
       <c r="DA27" s="32"/>
-      <c r="DB27" s="127"/>
-      <c r="DC27" s="127"/>
-      <c r="DD27" s="127"/>
-      <c r="DE27" s="127"/>
-      <c r="DF27" s="127"/>
-      <c r="DG27" s="127"/>
-      <c r="DH27" s="127"/>
-      <c r="DI27" s="127"/>
-      <c r="DJ27" s="127"/>
-      <c r="DK27" s="127"/>
-      <c r="DL27" s="127"/>
-      <c r="DM27" s="127"/>
-      <c r="DN27" s="127"/>
-      <c r="DO27" s="128"/>
-      <c r="DP27" s="125"/>
+      <c r="DB27" s="119"/>
+      <c r="DC27" s="119"/>
+      <c r="DD27" s="119"/>
+      <c r="DE27" s="119"/>
+      <c r="DF27" s="119"/>
+      <c r="DG27" s="119"/>
+      <c r="DH27" s="119"/>
+      <c r="DI27" s="119"/>
+      <c r="DJ27" s="119"/>
+      <c r="DK27" s="119"/>
+      <c r="DL27" s="119"/>
+      <c r="DM27" s="119"/>
+      <c r="DN27" s="119"/>
+      <c r="DO27" s="120"/>
+      <c r="DP27" s="114"/>
       <c r="DQ27" s="32"/>
       <c r="DR27" s="32"/>
       <c r="DS27" s="32"/>
@@ -6928,27 +6846,27 @@
       <c r="EH27" s="32"/>
       <c r="EI27" s="32"/>
       <c r="EJ27" s="32"/>
-      <c r="EK27" s="124">
+      <c r="EK27" s="113">
         <f t="shared" si="70"/>
         <v>46195</v>
       </c>
-      <c r="EL27" s="124">
+      <c r="EL27" s="113">
         <f t="shared" si="71"/>
         <v>46198</v>
       </c>
     </row>
     <row r="28" spans="1:142" s="29" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A28" s="4"/>
-      <c r="B28" s="81" t="s">
+      <c r="B28" s="70" t="s">
         <v>25</v>
       </c>
-      <c r="C28" s="82">
+      <c r="C28" s="71">
         <v>0</v>
       </c>
-      <c r="D28" s="83">
+      <c r="D28" s="72">
         <v>46199</v>
       </c>
-      <c r="E28" s="83">
+      <c r="E28" s="72">
         <v>46199</v>
       </c>
       <c r="F28" s="6"/>
@@ -7054,21 +6972,21 @@
       <c r="CY28" s="32"/>
       <c r="CZ28" s="32"/>
       <c r="DA28" s="32"/>
-      <c r="DB28" s="127"/>
-      <c r="DC28" s="127"/>
-      <c r="DD28" s="127"/>
-      <c r="DE28" s="127"/>
-      <c r="DF28" s="127"/>
-      <c r="DG28" s="127"/>
-      <c r="DH28" s="127"/>
-      <c r="DI28" s="127"/>
-      <c r="DJ28" s="127"/>
-      <c r="DK28" s="127"/>
-      <c r="DL28" s="127"/>
-      <c r="DM28" s="127"/>
-      <c r="DN28" s="127"/>
-      <c r="DO28" s="128"/>
-      <c r="DP28" s="125"/>
+      <c r="DB28" s="119"/>
+      <c r="DC28" s="119"/>
+      <c r="DD28" s="119"/>
+      <c r="DE28" s="119"/>
+      <c r="DF28" s="119"/>
+      <c r="DG28" s="119"/>
+      <c r="DH28" s="119"/>
+      <c r="DI28" s="119"/>
+      <c r="DJ28" s="119"/>
+      <c r="DK28" s="119"/>
+      <c r="DL28" s="119"/>
+      <c r="DM28" s="119"/>
+      <c r="DN28" s="119"/>
+      <c r="DO28" s="120"/>
+      <c r="DP28" s="114"/>
       <c r="DQ28" s="32"/>
       <c r="DR28" s="32"/>
       <c r="DS28" s="32"/>
@@ -7089,23 +7007,23 @@
       <c r="EH28" s="32"/>
       <c r="EI28" s="32"/>
       <c r="EJ28" s="32"/>
-      <c r="EK28" s="124">
+      <c r="EK28" s="113">
         <f t="shared" si="70"/>
         <v>46198</v>
       </c>
-      <c r="EL28" s="124">
+      <c r="EL28" s="113">
         <f t="shared" si="71"/>
         <v>46198</v>
       </c>
     </row>
     <row r="29" spans="1:142" s="29" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A29" s="4"/>
-      <c r="B29" s="84" t="s">
+      <c r="B29" s="73" t="s">
         <v>27</v>
       </c>
-      <c r="C29" s="85"/>
-      <c r="D29" s="86"/>
-      <c r="E29" s="87"/>
+      <c r="C29" s="74"/>
+      <c r="D29" s="75"/>
+      <c r="E29" s="76"/>
       <c r="F29" s="6"/>
       <c r="G29" s="3" t="str">
         <f t="shared" si="65"/>
@@ -7209,20 +7127,20 @@
       <c r="CY29" s="47"/>
       <c r="CZ29" s="47"/>
       <c r="DA29" s="47"/>
-      <c r="DB29" s="127"/>
-      <c r="DC29" s="127"/>
-      <c r="DD29" s="127"/>
-      <c r="DE29" s="127"/>
-      <c r="DF29" s="127"/>
-      <c r="DG29" s="127"/>
-      <c r="DH29" s="127"/>
-      <c r="DI29" s="127"/>
-      <c r="DJ29" s="127"/>
-      <c r="DK29" s="127"/>
-      <c r="DL29" s="127"/>
-      <c r="DM29" s="127"/>
-      <c r="DN29" s="127"/>
-      <c r="DO29" s="128"/>
+      <c r="DB29" s="119"/>
+      <c r="DC29" s="119"/>
+      <c r="DD29" s="119"/>
+      <c r="DE29" s="119"/>
+      <c r="DF29" s="119"/>
+      <c r="DG29" s="119"/>
+      <c r="DH29" s="119"/>
+      <c r="DI29" s="119"/>
+      <c r="DJ29" s="119"/>
+      <c r="DK29" s="119"/>
+      <c r="DL29" s="119"/>
+      <c r="DM29" s="119"/>
+      <c r="DN29" s="119"/>
+      <c r="DO29" s="120"/>
       <c r="DP29" s="47"/>
       <c r="DQ29" s="47"/>
       <c r="DR29" s="47"/>
@@ -7244,27 +7162,27 @@
       <c r="EH29" s="47"/>
       <c r="EI29" s="47"/>
       <c r="EJ29" s="47"/>
-      <c r="EK29" s="124">
+      <c r="EK29" s="113">
         <f t="shared" si="70"/>
         <v>-1</v>
       </c>
-      <c r="EL29" s="124">
+      <c r="EL29" s="113">
         <f t="shared" si="71"/>
         <v>-1</v>
       </c>
     </row>
     <row r="30" spans="1:142" s="29" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A30" s="4"/>
-      <c r="B30" s="100" t="s">
+      <c r="B30" s="89" t="s">
         <v>28</v>
       </c>
-      <c r="C30" s="93">
+      <c r="C30" s="82">
         <v>0</v>
       </c>
-      <c r="D30" s="94">
+      <c r="D30" s="83">
         <v>46200</v>
       </c>
-      <c r="E30" s="95">
+      <c r="E30" s="84">
         <v>46204</v>
       </c>
       <c r="F30" s="6"/>
@@ -7370,21 +7288,21 @@
       <c r="CY30" s="32"/>
       <c r="CZ30" s="32"/>
       <c r="DA30" s="32"/>
-      <c r="DB30" s="127"/>
-      <c r="DC30" s="127"/>
-      <c r="DD30" s="127"/>
-      <c r="DE30" s="127"/>
-      <c r="DF30" s="127"/>
-      <c r="DG30" s="127"/>
-      <c r="DH30" s="127"/>
-      <c r="DI30" s="127"/>
-      <c r="DJ30" s="127"/>
-      <c r="DK30" s="127"/>
-      <c r="DL30" s="127"/>
-      <c r="DM30" s="127"/>
-      <c r="DN30" s="127"/>
-      <c r="DO30" s="128"/>
-      <c r="DP30" s="125"/>
+      <c r="DB30" s="119"/>
+      <c r="DC30" s="119"/>
+      <c r="DD30" s="119"/>
+      <c r="DE30" s="119"/>
+      <c r="DF30" s="119"/>
+      <c r="DG30" s="119"/>
+      <c r="DH30" s="119"/>
+      <c r="DI30" s="119"/>
+      <c r="DJ30" s="119"/>
+      <c r="DK30" s="119"/>
+      <c r="DL30" s="119"/>
+      <c r="DM30" s="119"/>
+      <c r="DN30" s="119"/>
+      <c r="DO30" s="120"/>
+      <c r="DP30" s="114"/>
       <c r="DQ30" s="32"/>
       <c r="DR30" s="32"/>
       <c r="DS30" s="32"/>
@@ -7405,27 +7323,27 @@
       <c r="EH30" s="32"/>
       <c r="EI30" s="32"/>
       <c r="EJ30" s="32"/>
-      <c r="EK30" s="124">
+      <c r="EK30" s="113">
         <f t="shared" si="70"/>
         <v>46199</v>
       </c>
-      <c r="EL30" s="124">
+      <c r="EL30" s="113">
         <f t="shared" si="71"/>
         <v>46203</v>
       </c>
     </row>
     <row r="31" spans="1:142" s="29" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A31" s="4"/>
-      <c r="B31" s="96" t="s">
+      <c r="B31" s="85" t="s">
         <v>29</v>
       </c>
-      <c r="C31" s="97">
+      <c r="C31" s="86">
         <v>0</v>
       </c>
-      <c r="D31" s="98">
+      <c r="D31" s="87">
         <v>46205</v>
       </c>
-      <c r="E31" s="99">
+      <c r="E31" s="88">
         <v>46207</v>
       </c>
       <c r="F31" s="6"/>
@@ -7531,21 +7449,21 @@
       <c r="CY31" s="32"/>
       <c r="CZ31" s="32"/>
       <c r="DA31" s="32"/>
-      <c r="DB31" s="127"/>
-      <c r="DC31" s="127"/>
-      <c r="DD31" s="127"/>
-      <c r="DE31" s="127"/>
-      <c r="DF31" s="127"/>
-      <c r="DG31" s="127"/>
-      <c r="DH31" s="127"/>
-      <c r="DI31" s="127"/>
-      <c r="DJ31" s="127"/>
-      <c r="DK31" s="127"/>
-      <c r="DL31" s="127"/>
-      <c r="DM31" s="127"/>
-      <c r="DN31" s="127"/>
-      <c r="DO31" s="128"/>
-      <c r="DP31" s="125"/>
+      <c r="DB31" s="119"/>
+      <c r="DC31" s="119"/>
+      <c r="DD31" s="119"/>
+      <c r="DE31" s="119"/>
+      <c r="DF31" s="119"/>
+      <c r="DG31" s="119"/>
+      <c r="DH31" s="119"/>
+      <c r="DI31" s="119"/>
+      <c r="DJ31" s="119"/>
+      <c r="DK31" s="119"/>
+      <c r="DL31" s="119"/>
+      <c r="DM31" s="119"/>
+      <c r="DN31" s="119"/>
+      <c r="DO31" s="120"/>
+      <c r="DP31" s="114"/>
       <c r="DQ31" s="32"/>
       <c r="DR31" s="32"/>
       <c r="DS31" s="32"/>
@@ -7566,27 +7484,27 @@
       <c r="EH31" s="32"/>
       <c r="EI31" s="32"/>
       <c r="EJ31" s="32"/>
-      <c r="EK31" s="124">
+      <c r="EK31" s="113">
         <f t="shared" si="70"/>
         <v>46204</v>
       </c>
-      <c r="EL31" s="124">
+      <c r="EL31" s="113">
         <f t="shared" si="71"/>
         <v>46206</v>
       </c>
     </row>
     <row r="32" spans="1:142" s="29" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A32" s="4"/>
-      <c r="B32" s="92" t="s">
+      <c r="B32" s="81" t="s">
         <v>30</v>
       </c>
-      <c r="C32" s="93">
+      <c r="C32" s="82">
         <v>0</v>
       </c>
-      <c r="D32" s="94">
+      <c r="D32" s="83">
         <v>46208</v>
       </c>
-      <c r="E32" s="95">
+      <c r="E32" s="84">
         <v>46211</v>
       </c>
       <c r="F32" s="6"/>
@@ -7692,21 +7610,21 @@
       <c r="CY32" s="32"/>
       <c r="CZ32" s="32"/>
       <c r="DA32" s="32"/>
-      <c r="DB32" s="127"/>
-      <c r="DC32" s="127"/>
-      <c r="DD32" s="127"/>
-      <c r="DE32" s="127"/>
-      <c r="DF32" s="127"/>
-      <c r="DG32" s="127"/>
-      <c r="DH32" s="127"/>
-      <c r="DI32" s="127"/>
-      <c r="DJ32" s="127"/>
-      <c r="DK32" s="127"/>
-      <c r="DL32" s="127"/>
-      <c r="DM32" s="127"/>
-      <c r="DN32" s="127"/>
-      <c r="DO32" s="128"/>
-      <c r="DP32" s="125"/>
+      <c r="DB32" s="119"/>
+      <c r="DC32" s="119"/>
+      <c r="DD32" s="119"/>
+      <c r="DE32" s="119"/>
+      <c r="DF32" s="119"/>
+      <c r="DG32" s="119"/>
+      <c r="DH32" s="119"/>
+      <c r="DI32" s="119"/>
+      <c r="DJ32" s="119"/>
+      <c r="DK32" s="119"/>
+      <c r="DL32" s="119"/>
+      <c r="DM32" s="119"/>
+      <c r="DN32" s="119"/>
+      <c r="DO32" s="120"/>
+      <c r="DP32" s="114"/>
       <c r="DQ32" s="32"/>
       <c r="DR32" s="32"/>
       <c r="DS32" s="32"/>
@@ -7727,27 +7645,27 @@
       <c r="EH32" s="32"/>
       <c r="EI32" s="32"/>
       <c r="EJ32" s="32"/>
-      <c r="EK32" s="124">
+      <c r="EK32" s="113">
         <f t="shared" si="70"/>
         <v>46207</v>
       </c>
-      <c r="EL32" s="124">
+      <c r="EL32" s="113">
         <f t="shared" si="71"/>
         <v>46210</v>
       </c>
     </row>
     <row r="33" spans="1:142" s="29" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A33" s="4"/>
-      <c r="B33" s="88" t="s">
+      <c r="B33" s="77" t="s">
         <v>31</v>
       </c>
-      <c r="C33" s="89">
+      <c r="C33" s="78">
         <v>0</v>
       </c>
-      <c r="D33" s="90">
+      <c r="D33" s="79">
         <v>46212</v>
       </c>
-      <c r="E33" s="91">
+      <c r="E33" s="80">
         <v>46212</v>
       </c>
       <c r="F33" s="6"/>
@@ -7853,21 +7771,21 @@
       <c r="CY33" s="32"/>
       <c r="CZ33" s="32"/>
       <c r="DA33" s="32"/>
-      <c r="DB33" s="127"/>
-      <c r="DC33" s="127"/>
-      <c r="DD33" s="127"/>
-      <c r="DE33" s="127"/>
-      <c r="DF33" s="127"/>
-      <c r="DG33" s="127"/>
-      <c r="DH33" s="127"/>
-      <c r="DI33" s="127"/>
-      <c r="DJ33" s="127"/>
-      <c r="DK33" s="127"/>
-      <c r="DL33" s="127"/>
-      <c r="DM33" s="127"/>
-      <c r="DN33" s="127"/>
-      <c r="DO33" s="128"/>
-      <c r="DP33" s="125"/>
+      <c r="DB33" s="119"/>
+      <c r="DC33" s="119"/>
+      <c r="DD33" s="119"/>
+      <c r="DE33" s="119"/>
+      <c r="DF33" s="119"/>
+      <c r="DG33" s="119"/>
+      <c r="DH33" s="119"/>
+      <c r="DI33" s="119"/>
+      <c r="DJ33" s="119"/>
+      <c r="DK33" s="119"/>
+      <c r="DL33" s="119"/>
+      <c r="DM33" s="119"/>
+      <c r="DN33" s="119"/>
+      <c r="DO33" s="120"/>
+      <c r="DP33" s="114"/>
       <c r="DQ33" s="32"/>
       <c r="DR33" s="32"/>
       <c r="DS33" s="32"/>
@@ -7888,23 +7806,23 @@
       <c r="EH33" s="32"/>
       <c r="EI33" s="32"/>
       <c r="EJ33" s="32"/>
-      <c r="EK33" s="124">
+      <c r="EK33" s="113">
         <f t="shared" si="70"/>
         <v>46211</v>
       </c>
-      <c r="EL33" s="124">
+      <c r="EL33" s="113">
         <f t="shared" si="71"/>
         <v>46211</v>
       </c>
     </row>
     <row r="34" spans="1:142" s="29" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A34" s="4"/>
-      <c r="B34" s="77" t="s">
+      <c r="B34" s="66" t="s">
         <v>32</v>
       </c>
-      <c r="C34" s="78"/>
-      <c r="D34" s="79"/>
-      <c r="E34" s="80"/>
+      <c r="C34" s="67"/>
+      <c r="D34" s="68"/>
+      <c r="E34" s="69"/>
       <c r="F34" s="6"/>
       <c r="G34" s="3" t="str">
         <f t="shared" si="65"/>
@@ -8008,20 +7926,20 @@
       <c r="CY34" s="47"/>
       <c r="CZ34" s="47"/>
       <c r="DA34" s="47"/>
-      <c r="DB34" s="127"/>
-      <c r="DC34" s="127"/>
-      <c r="DD34" s="127"/>
-      <c r="DE34" s="127"/>
-      <c r="DF34" s="127"/>
-      <c r="DG34" s="127"/>
-      <c r="DH34" s="127"/>
-      <c r="DI34" s="127"/>
-      <c r="DJ34" s="127"/>
-      <c r="DK34" s="127"/>
-      <c r="DL34" s="127"/>
-      <c r="DM34" s="127"/>
-      <c r="DN34" s="127"/>
-      <c r="DO34" s="128"/>
+      <c r="DB34" s="119"/>
+      <c r="DC34" s="119"/>
+      <c r="DD34" s="119"/>
+      <c r="DE34" s="119"/>
+      <c r="DF34" s="119"/>
+      <c r="DG34" s="119"/>
+      <c r="DH34" s="119"/>
+      <c r="DI34" s="119"/>
+      <c r="DJ34" s="119"/>
+      <c r="DK34" s="119"/>
+      <c r="DL34" s="119"/>
+      <c r="DM34" s="119"/>
+      <c r="DN34" s="119"/>
+      <c r="DO34" s="120"/>
       <c r="DP34" s="47"/>
       <c r="DQ34" s="47"/>
       <c r="DR34" s="47"/>
@@ -8043,27 +7961,27 @@
       <c r="EH34" s="47"/>
       <c r="EI34" s="47"/>
       <c r="EJ34" s="47"/>
-      <c r="EK34" s="124">
+      <c r="EK34" s="113">
         <f t="shared" si="70"/>
         <v>-1</v>
       </c>
-      <c r="EL34" s="124">
+      <c r="EL34" s="113">
         <f t="shared" si="71"/>
         <v>-1</v>
       </c>
     </row>
     <row r="35" spans="1:142" s="29" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A35" s="4"/>
-      <c r="B35" s="105" t="s">
+      <c r="B35" s="94" t="s">
         <v>33</v>
       </c>
-      <c r="C35" s="106">
+      <c r="C35" s="95">
         <v>0</v>
       </c>
-      <c r="D35" s="107">
+      <c r="D35" s="96">
         <v>46213</v>
       </c>
-      <c r="E35" s="108">
+      <c r="E35" s="97">
         <v>46217</v>
       </c>
       <c r="F35" s="6"/>
@@ -8169,21 +8087,21 @@
       <c r="CY35" s="32"/>
       <c r="CZ35" s="32"/>
       <c r="DA35" s="32"/>
-      <c r="DB35" s="127"/>
-      <c r="DC35" s="127"/>
-      <c r="DD35" s="127"/>
-      <c r="DE35" s="127"/>
-      <c r="DF35" s="127"/>
-      <c r="DG35" s="127"/>
-      <c r="DH35" s="127"/>
-      <c r="DI35" s="127"/>
-      <c r="DJ35" s="127"/>
-      <c r="DK35" s="127"/>
-      <c r="DL35" s="127"/>
-      <c r="DM35" s="127"/>
-      <c r="DN35" s="127"/>
-      <c r="DO35" s="128"/>
-      <c r="DP35" s="125"/>
+      <c r="DB35" s="119"/>
+      <c r="DC35" s="119"/>
+      <c r="DD35" s="119"/>
+      <c r="DE35" s="119"/>
+      <c r="DF35" s="119"/>
+      <c r="DG35" s="119"/>
+      <c r="DH35" s="119"/>
+      <c r="DI35" s="119"/>
+      <c r="DJ35" s="119"/>
+      <c r="DK35" s="119"/>
+      <c r="DL35" s="119"/>
+      <c r="DM35" s="119"/>
+      <c r="DN35" s="119"/>
+      <c r="DO35" s="120"/>
+      <c r="DP35" s="114"/>
       <c r="DQ35" s="32"/>
       <c r="DR35" s="32"/>
       <c r="DS35" s="32"/>
@@ -8204,27 +8122,27 @@
       <c r="EH35" s="32"/>
       <c r="EI35" s="32"/>
       <c r="EJ35" s="32"/>
-      <c r="EK35" s="124">
+      <c r="EK35" s="113">
         <f t="shared" si="70"/>
         <v>46212</v>
       </c>
-      <c r="EL35" s="124">
+      <c r="EL35" s="113">
         <f t="shared" si="71"/>
         <v>46216</v>
       </c>
     </row>
     <row r="36" spans="1:142" s="29" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A36" s="4"/>
-      <c r="B36" s="109" t="s">
+      <c r="B36" s="98" t="s">
         <v>34</v>
       </c>
-      <c r="C36" s="110">
+      <c r="C36" s="99">
         <v>0</v>
       </c>
-      <c r="D36" s="111">
+      <c r="D36" s="100">
         <v>46218</v>
       </c>
-      <c r="E36" s="112">
+      <c r="E36" s="101">
         <v>46219</v>
       </c>
       <c r="F36" s="6"/>
@@ -8330,21 +8248,21 @@
       <c r="CY36" s="32"/>
       <c r="CZ36" s="32"/>
       <c r="DA36" s="32"/>
-      <c r="DB36" s="127"/>
-      <c r="DC36" s="127"/>
-      <c r="DD36" s="127"/>
-      <c r="DE36" s="127"/>
-      <c r="DF36" s="127"/>
-      <c r="DG36" s="127"/>
-      <c r="DH36" s="127"/>
-      <c r="DI36" s="127"/>
-      <c r="DJ36" s="127"/>
-      <c r="DK36" s="127"/>
-      <c r="DL36" s="127"/>
-      <c r="DM36" s="127"/>
-      <c r="DN36" s="127"/>
-      <c r="DO36" s="128"/>
-      <c r="DP36" s="125"/>
+      <c r="DB36" s="119"/>
+      <c r="DC36" s="119"/>
+      <c r="DD36" s="119"/>
+      <c r="DE36" s="119"/>
+      <c r="DF36" s="119"/>
+      <c r="DG36" s="119"/>
+      <c r="DH36" s="119"/>
+      <c r="DI36" s="119"/>
+      <c r="DJ36" s="119"/>
+      <c r="DK36" s="119"/>
+      <c r="DL36" s="119"/>
+      <c r="DM36" s="119"/>
+      <c r="DN36" s="119"/>
+      <c r="DO36" s="120"/>
+      <c r="DP36" s="114"/>
       <c r="DQ36" s="32"/>
       <c r="DR36" s="32"/>
       <c r="DS36" s="32"/>
@@ -8365,27 +8283,27 @@
       <c r="EH36" s="32"/>
       <c r="EI36" s="32"/>
       <c r="EJ36" s="32"/>
-      <c r="EK36" s="124">
+      <c r="EK36" s="113">
         <f t="shared" si="70"/>
         <v>46217</v>
       </c>
-      <c r="EL36" s="124">
+      <c r="EL36" s="113">
         <f t="shared" si="71"/>
         <v>46218</v>
       </c>
     </row>
     <row r="37" spans="1:142" s="29" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A37" s="4"/>
-      <c r="B37" s="113" t="s">
+      <c r="B37" s="102" t="s">
         <v>35</v>
       </c>
-      <c r="C37" s="110">
+      <c r="C37" s="99">
         <v>0</v>
       </c>
-      <c r="D37" s="111">
+      <c r="D37" s="100">
         <v>46220</v>
       </c>
-      <c r="E37" s="114">
+      <c r="E37" s="103">
         <v>46222</v>
       </c>
       <c r="F37" s="6"/>
@@ -8491,21 +8409,21 @@
       <c r="CY37" s="32"/>
       <c r="CZ37" s="32"/>
       <c r="DA37" s="32"/>
-      <c r="DB37" s="127"/>
-      <c r="DC37" s="127"/>
-      <c r="DD37" s="127"/>
-      <c r="DE37" s="127"/>
-      <c r="DF37" s="127"/>
-      <c r="DG37" s="127"/>
-      <c r="DH37" s="127"/>
-      <c r="DI37" s="127"/>
-      <c r="DJ37" s="127"/>
-      <c r="DK37" s="127"/>
-      <c r="DL37" s="127"/>
-      <c r="DM37" s="127"/>
-      <c r="DN37" s="127"/>
-      <c r="DO37" s="128"/>
-      <c r="DP37" s="125"/>
+      <c r="DB37" s="119"/>
+      <c r="DC37" s="119"/>
+      <c r="DD37" s="119"/>
+      <c r="DE37" s="119"/>
+      <c r="DF37" s="119"/>
+      <c r="DG37" s="119"/>
+      <c r="DH37" s="119"/>
+      <c r="DI37" s="119"/>
+      <c r="DJ37" s="119"/>
+      <c r="DK37" s="119"/>
+      <c r="DL37" s="119"/>
+      <c r="DM37" s="119"/>
+      <c r="DN37" s="119"/>
+      <c r="DO37" s="120"/>
+      <c r="DP37" s="114"/>
       <c r="DQ37" s="32"/>
       <c r="DR37" s="32"/>
       <c r="DS37" s="32"/>
@@ -8526,27 +8444,27 @@
       <c r="EH37" s="32"/>
       <c r="EI37" s="32"/>
       <c r="EJ37" s="32"/>
-      <c r="EK37" s="124">
+      <c r="EK37" s="113">
         <f t="shared" si="70"/>
         <v>46219</v>
       </c>
-      <c r="EL37" s="124">
+      <c r="EL37" s="113">
         <f t="shared" si="71"/>
         <v>46221</v>
       </c>
     </row>
     <row r="38" spans="1:142" s="29" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A38" s="4"/>
-      <c r="B38" s="113" t="s">
+      <c r="B38" s="102" t="s">
         <v>36</v>
       </c>
-      <c r="C38" s="115">
+      <c r="C38" s="104">
         <v>0</v>
       </c>
-      <c r="D38" s="111">
+      <c r="D38" s="100">
         <v>46221</v>
       </c>
-      <c r="E38" s="114">
+      <c r="E38" s="103">
         <v>46223</v>
       </c>
       <c r="F38" s="6"/>
@@ -8652,21 +8570,21 @@
       <c r="CY38" s="32"/>
       <c r="CZ38" s="32"/>
       <c r="DA38" s="32"/>
-      <c r="DB38" s="127"/>
-      <c r="DC38" s="127"/>
-      <c r="DD38" s="127"/>
-      <c r="DE38" s="127"/>
-      <c r="DF38" s="127"/>
-      <c r="DG38" s="127"/>
-      <c r="DH38" s="127"/>
-      <c r="DI38" s="127"/>
-      <c r="DJ38" s="127"/>
-      <c r="DK38" s="127"/>
-      <c r="DL38" s="127"/>
-      <c r="DM38" s="127"/>
-      <c r="DN38" s="127"/>
-      <c r="DO38" s="128"/>
-      <c r="DP38" s="125"/>
+      <c r="DB38" s="119"/>
+      <c r="DC38" s="119"/>
+      <c r="DD38" s="119"/>
+      <c r="DE38" s="119"/>
+      <c r="DF38" s="119"/>
+      <c r="DG38" s="119"/>
+      <c r="DH38" s="119"/>
+      <c r="DI38" s="119"/>
+      <c r="DJ38" s="119"/>
+      <c r="DK38" s="119"/>
+      <c r="DL38" s="119"/>
+      <c r="DM38" s="119"/>
+      <c r="DN38" s="119"/>
+      <c r="DO38" s="120"/>
+      <c r="DP38" s="114"/>
       <c r="DQ38" s="32"/>
       <c r="DR38" s="32"/>
       <c r="DS38" s="32"/>
@@ -8687,27 +8605,27 @@
       <c r="EH38" s="32"/>
       <c r="EI38" s="32"/>
       <c r="EJ38" s="32"/>
-      <c r="EK38" s="124">
+      <c r="EK38" s="113">
         <f t="shared" si="70"/>
         <v>46220</v>
       </c>
-      <c r="EL38" s="124">
+      <c r="EL38" s="113">
         <f t="shared" si="71"/>
         <v>46222</v>
       </c>
     </row>
     <row r="39" spans="1:142" s="29" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A39" s="4"/>
-      <c r="B39" s="104" t="s">
+      <c r="B39" s="93" t="s">
         <v>37</v>
       </c>
-      <c r="C39" s="101">
+      <c r="C39" s="90">
         <v>0</v>
       </c>
-      <c r="D39" s="102">
+      <c r="D39" s="91">
         <v>46224</v>
       </c>
-      <c r="E39" s="103">
+      <c r="E39" s="92">
         <v>46226</v>
       </c>
       <c r="F39" s="6"/>
@@ -8813,21 +8731,21 @@
       <c r="CY39" s="32"/>
       <c r="CZ39" s="32"/>
       <c r="DA39" s="32"/>
-      <c r="DB39" s="127"/>
-      <c r="DC39" s="127"/>
-      <c r="DD39" s="127"/>
-      <c r="DE39" s="127"/>
-      <c r="DF39" s="127"/>
-      <c r="DG39" s="127"/>
-      <c r="DH39" s="127"/>
-      <c r="DI39" s="127"/>
-      <c r="DJ39" s="127"/>
-      <c r="DK39" s="127"/>
-      <c r="DL39" s="127"/>
-      <c r="DM39" s="127"/>
-      <c r="DN39" s="127"/>
-      <c r="DO39" s="128"/>
-      <c r="DP39" s="125"/>
+      <c r="DB39" s="119"/>
+      <c r="DC39" s="119"/>
+      <c r="DD39" s="119"/>
+      <c r="DE39" s="119"/>
+      <c r="DF39" s="119"/>
+      <c r="DG39" s="119"/>
+      <c r="DH39" s="119"/>
+      <c r="DI39" s="119"/>
+      <c r="DJ39" s="119"/>
+      <c r="DK39" s="119"/>
+      <c r="DL39" s="119"/>
+      <c r="DM39" s="119"/>
+      <c r="DN39" s="119"/>
+      <c r="DO39" s="120"/>
+      <c r="DP39" s="114"/>
       <c r="DQ39" s="32"/>
       <c r="DR39" s="32"/>
       <c r="DS39" s="32"/>
@@ -8848,11 +8766,11 @@
       <c r="EH39" s="32"/>
       <c r="EI39" s="32"/>
       <c r="EJ39" s="32"/>
-      <c r="EK39" s="124">
+      <c r="EK39" s="113">
         <f t="shared" si="70"/>
         <v>46223</v>
       </c>
-      <c r="EL39" s="124">
+      <c r="EL39" s="113">
         <f t="shared" si="71"/>
         <v>46225</v>
       </c>
@@ -8968,20 +8886,20 @@
       <c r="CY40" s="28"/>
       <c r="CZ40" s="28"/>
       <c r="DA40" s="28"/>
-      <c r="DB40" s="127"/>
-      <c r="DC40" s="127"/>
-      <c r="DD40" s="127"/>
-      <c r="DE40" s="127"/>
-      <c r="DF40" s="127"/>
-      <c r="DG40" s="127"/>
-      <c r="DH40" s="127"/>
-      <c r="DI40" s="127"/>
-      <c r="DJ40" s="127"/>
-      <c r="DK40" s="127"/>
-      <c r="DL40" s="127"/>
-      <c r="DM40" s="127"/>
-      <c r="DN40" s="127"/>
-      <c r="DO40" s="128"/>
+      <c r="DB40" s="119"/>
+      <c r="DC40" s="119"/>
+      <c r="DD40" s="119"/>
+      <c r="DE40" s="119"/>
+      <c r="DF40" s="119"/>
+      <c r="DG40" s="119"/>
+      <c r="DH40" s="119"/>
+      <c r="DI40" s="119"/>
+      <c r="DJ40" s="119"/>
+      <c r="DK40" s="119"/>
+      <c r="DL40" s="119"/>
+      <c r="DM40" s="119"/>
+      <c r="DN40" s="119"/>
+      <c r="DO40" s="120"/>
       <c r="DP40" s="28"/>
       <c r="DQ40" s="28"/>
       <c r="DR40" s="28"/>
@@ -9003,27 +8921,27 @@
       <c r="EH40" s="28"/>
       <c r="EI40" s="28"/>
       <c r="EJ40" s="28"/>
-      <c r="EK40" s="124">
+      <c r="EK40" s="113">
         <f t="shared" si="70"/>
         <v>-1</v>
       </c>
-      <c r="EL40" s="124">
+      <c r="EL40" s="113">
         <f t="shared" si="71"/>
         <v>-1</v>
       </c>
     </row>
     <row r="41" spans="1:142" s="29" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A41" s="5"/>
-      <c r="B41" s="116" t="s">
+      <c r="B41" s="105" t="s">
         <v>38</v>
       </c>
       <c r="C41" s="31">
         <v>0</v>
       </c>
-      <c r="D41" s="60">
+      <c r="D41" s="51">
         <v>46226</v>
       </c>
-      <c r="E41" s="60">
+      <c r="E41" s="51">
         <v>46227</v>
       </c>
       <c r="F41" s="6"/>
@@ -9129,21 +9047,21 @@
       <c r="CY41" s="32"/>
       <c r="CZ41" s="32"/>
       <c r="DA41" s="32"/>
-      <c r="DB41" s="127"/>
-      <c r="DC41" s="127"/>
-      <c r="DD41" s="127"/>
-      <c r="DE41" s="127"/>
-      <c r="DF41" s="127"/>
-      <c r="DG41" s="127"/>
-      <c r="DH41" s="127"/>
-      <c r="DI41" s="127"/>
-      <c r="DJ41" s="127"/>
-      <c r="DK41" s="127"/>
-      <c r="DL41" s="127"/>
-      <c r="DM41" s="127"/>
-      <c r="DN41" s="127"/>
-      <c r="DO41" s="128"/>
-      <c r="DP41" s="125"/>
+      <c r="DB41" s="119"/>
+      <c r="DC41" s="119"/>
+      <c r="DD41" s="119"/>
+      <c r="DE41" s="119"/>
+      <c r="DF41" s="119"/>
+      <c r="DG41" s="119"/>
+      <c r="DH41" s="119"/>
+      <c r="DI41" s="119"/>
+      <c r="DJ41" s="119"/>
+      <c r="DK41" s="119"/>
+      <c r="DL41" s="119"/>
+      <c r="DM41" s="119"/>
+      <c r="DN41" s="119"/>
+      <c r="DO41" s="120"/>
+      <c r="DP41" s="114"/>
       <c r="DQ41" s="32"/>
       <c r="DR41" s="32"/>
       <c r="DS41" s="32"/>
@@ -9164,27 +9082,27 @@
       <c r="EH41" s="32"/>
       <c r="EI41" s="32"/>
       <c r="EJ41" s="32"/>
-      <c r="EK41" s="124">
+      <c r="EK41" s="113">
         <f>D41+2</f>
         <v>46228</v>
       </c>
-      <c r="EL41" s="124">
+      <c r="EL41" s="113">
         <f>E41+2</f>
         <v>46229</v>
       </c>
     </row>
     <row r="42" spans="1:142" s="29" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A42" s="5"/>
-      <c r="B42" s="73" t="s">
+      <c r="B42" s="62" t="s">
         <v>39</v>
       </c>
       <c r="C42" s="34">
         <v>0</v>
       </c>
-      <c r="D42" s="61">
+      <c r="D42" s="52">
         <v>46227</v>
       </c>
-      <c r="E42" s="61">
+      <c r="E42" s="52">
         <v>46229</v>
       </c>
       <c r="F42" s="6"/>
@@ -9290,21 +9208,21 @@
       <c r="CY42" s="32"/>
       <c r="CZ42" s="32"/>
       <c r="DA42" s="32"/>
-      <c r="DB42" s="127"/>
-      <c r="DC42" s="127"/>
-      <c r="DD42" s="127"/>
-      <c r="DE42" s="127"/>
-      <c r="DF42" s="127"/>
-      <c r="DG42" s="127"/>
-      <c r="DH42" s="127"/>
-      <c r="DI42" s="127"/>
-      <c r="DJ42" s="127"/>
-      <c r="DK42" s="127"/>
-      <c r="DL42" s="127"/>
-      <c r="DM42" s="127"/>
-      <c r="DN42" s="127"/>
-      <c r="DO42" s="128"/>
-      <c r="DP42" s="125"/>
+      <c r="DB42" s="119"/>
+      <c r="DC42" s="119"/>
+      <c r="DD42" s="119"/>
+      <c r="DE42" s="119"/>
+      <c r="DF42" s="119"/>
+      <c r="DG42" s="119"/>
+      <c r="DH42" s="119"/>
+      <c r="DI42" s="119"/>
+      <c r="DJ42" s="119"/>
+      <c r="DK42" s="119"/>
+      <c r="DL42" s="119"/>
+      <c r="DM42" s="119"/>
+      <c r="DN42" s="119"/>
+      <c r="DO42" s="120"/>
+      <c r="DP42" s="114"/>
       <c r="DQ42" s="32"/>
       <c r="DR42" s="32"/>
       <c r="DS42" s="32"/>
@@ -9325,11 +9243,11 @@
       <c r="EH42" s="32"/>
       <c r="EI42" s="32"/>
       <c r="EJ42" s="32"/>
-      <c r="EK42" s="124">
+      <c r="EK42" s="113">
         <f t="shared" ref="EK42:EK52" si="72">D42+2</f>
         <v>46229</v>
       </c>
-      <c r="EL42" s="124">
+      <c r="EL42" s="113">
         <f t="shared" ref="EL42:EL52" si="73">E42+2</f>
         <v>46231</v>
       </c>
@@ -9342,10 +9260,10 @@
       <c r="C43" s="34">
         <v>0</v>
       </c>
-      <c r="D43" s="61">
+      <c r="D43" s="52">
         <v>46230</v>
       </c>
-      <c r="E43" s="61">
+      <c r="E43" s="52">
         <v>46230</v>
       </c>
       <c r="F43" s="6"/>
@@ -9451,21 +9369,21 @@
       <c r="CY43" s="32"/>
       <c r="CZ43" s="32"/>
       <c r="DA43" s="32"/>
-      <c r="DB43" s="127"/>
-      <c r="DC43" s="127"/>
-      <c r="DD43" s="127"/>
-      <c r="DE43" s="127"/>
-      <c r="DF43" s="127"/>
-      <c r="DG43" s="127"/>
-      <c r="DH43" s="127"/>
-      <c r="DI43" s="127"/>
-      <c r="DJ43" s="127"/>
-      <c r="DK43" s="127"/>
-      <c r="DL43" s="127"/>
-      <c r="DM43" s="127"/>
-      <c r="DN43" s="127"/>
-      <c r="DO43" s="128"/>
-      <c r="DP43" s="125"/>
+      <c r="DB43" s="119"/>
+      <c r="DC43" s="119"/>
+      <c r="DD43" s="119"/>
+      <c r="DE43" s="119"/>
+      <c r="DF43" s="119"/>
+      <c r="DG43" s="119"/>
+      <c r="DH43" s="119"/>
+      <c r="DI43" s="119"/>
+      <c r="DJ43" s="119"/>
+      <c r="DK43" s="119"/>
+      <c r="DL43" s="119"/>
+      <c r="DM43" s="119"/>
+      <c r="DN43" s="119"/>
+      <c r="DO43" s="120"/>
+      <c r="DP43" s="114"/>
       <c r="DQ43" s="32"/>
       <c r="DR43" s="32"/>
       <c r="DS43" s="32"/>
@@ -9486,27 +9404,27 @@
       <c r="EH43" s="32"/>
       <c r="EI43" s="32"/>
       <c r="EJ43" s="32"/>
-      <c r="EK43" s="124">
+      <c r="EK43" s="113">
         <f t="shared" si="72"/>
         <v>46232</v>
       </c>
-      <c r="EL43" s="124">
+      <c r="EL43" s="113">
         <f t="shared" si="73"/>
         <v>46232</v>
       </c>
     </row>
     <row r="44" spans="1:142" s="29" customFormat="1" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A44" s="4"/>
-      <c r="B44" s="73" t="s">
+      <c r="B44" s="62" t="s">
         <v>41</v>
       </c>
       <c r="C44" s="34">
         <v>0</v>
       </c>
-      <c r="D44" s="61">
+      <c r="D44" s="52">
         <v>46230</v>
       </c>
-      <c r="E44" s="61">
+      <c r="E44" s="52">
         <v>46230</v>
       </c>
       <c r="F44" s="6"/>
@@ -9609,21 +9527,21 @@
       <c r="CY44" s="32"/>
       <c r="CZ44" s="32"/>
       <c r="DA44" s="32"/>
-      <c r="DB44" s="127"/>
-      <c r="DC44" s="127"/>
-      <c r="DD44" s="127"/>
-      <c r="DE44" s="127"/>
-      <c r="DF44" s="127"/>
-      <c r="DG44" s="127"/>
-      <c r="DH44" s="127"/>
-      <c r="DI44" s="127"/>
-      <c r="DJ44" s="127"/>
-      <c r="DK44" s="127"/>
-      <c r="DL44" s="127"/>
-      <c r="DM44" s="127"/>
-      <c r="DN44" s="127"/>
-      <c r="DO44" s="128"/>
-      <c r="DP44" s="125"/>
+      <c r="DB44" s="119"/>
+      <c r="DC44" s="119"/>
+      <c r="DD44" s="119"/>
+      <c r="DE44" s="119"/>
+      <c r="DF44" s="119"/>
+      <c r="DG44" s="119"/>
+      <c r="DH44" s="119"/>
+      <c r="DI44" s="119"/>
+      <c r="DJ44" s="119"/>
+      <c r="DK44" s="119"/>
+      <c r="DL44" s="119"/>
+      <c r="DM44" s="119"/>
+      <c r="DN44" s="119"/>
+      <c r="DO44" s="120"/>
+      <c r="DP44" s="114"/>
       <c r="DQ44" s="32"/>
       <c r="DR44" s="32"/>
       <c r="DS44" s="32"/>
@@ -9644,11 +9562,11 @@
       <c r="EH44" s="32"/>
       <c r="EI44" s="32"/>
       <c r="EJ44" s="32"/>
-      <c r="EK44" s="124">
+      <c r="EK44" s="113">
         <f t="shared" si="72"/>
         <v>46232</v>
       </c>
-      <c r="EL44" s="124">
+      <c r="EL44" s="113">
         <f t="shared" si="73"/>
         <v>46232</v>
       </c>
@@ -9659,48 +9577,48 @@
         <v>42</v>
       </c>
       <c r="C45" s="37"/>
-      <c r="D45" s="62"/>
-      <c r="E45" s="63"/>
+      <c r="D45" s="53"/>
+      <c r="E45" s="54"/>
       <c r="F45" s="6"/>
       <c r="G45" s="3" t="str">
         <f t="shared" si="65"/>
         <v/>
       </c>
-      <c r="DB45" s="127"/>
-      <c r="DC45" s="127"/>
-      <c r="DD45" s="127"/>
-      <c r="DE45" s="127"/>
-      <c r="DF45" s="127"/>
-      <c r="DG45" s="127"/>
-      <c r="DH45" s="127"/>
-      <c r="DI45" s="127"/>
-      <c r="DJ45" s="127"/>
-      <c r="DK45" s="127"/>
-      <c r="DL45" s="127"/>
-      <c r="DM45" s="127"/>
-      <c r="DN45" s="127"/>
-      <c r="DO45" s="128"/>
-      <c r="EK45" s="124">
+      <c r="DB45" s="119"/>
+      <c r="DC45" s="119"/>
+      <c r="DD45" s="119"/>
+      <c r="DE45" s="119"/>
+      <c r="DF45" s="119"/>
+      <c r="DG45" s="119"/>
+      <c r="DH45" s="119"/>
+      <c r="DI45" s="119"/>
+      <c r="DJ45" s="119"/>
+      <c r="DK45" s="119"/>
+      <c r="DL45" s="119"/>
+      <c r="DM45" s="119"/>
+      <c r="DN45" s="119"/>
+      <c r="DO45" s="120"/>
+      <c r="EK45" s="113">
         <f t="shared" si="72"/>
         <v>2</v>
       </c>
-      <c r="EL45" s="124">
+      <c r="EL45" s="113">
         <f t="shared" si="73"/>
         <v>2</v>
       </c>
     </row>
     <row r="46" spans="1:142" s="29" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A46" s="5"/>
-      <c r="B46" s="74" t="s">
+      <c r="B46" s="63" t="s">
         <v>45</v>
       </c>
       <c r="C46" s="39">
         <v>0</v>
       </c>
-      <c r="D46" s="64">
+      <c r="D46" s="55">
         <v>46169</v>
       </c>
-      <c r="E46" s="64">
+      <c r="E46" s="55">
         <v>46234</v>
       </c>
       <c r="F46" s="6"/>
@@ -9806,21 +9724,21 @@
       <c r="CY46" s="32"/>
       <c r="CZ46" s="32"/>
       <c r="DA46" s="32"/>
-      <c r="DB46" s="127"/>
-      <c r="DC46" s="127"/>
-      <c r="DD46" s="127"/>
-      <c r="DE46" s="127"/>
-      <c r="DF46" s="127"/>
-      <c r="DG46" s="127"/>
-      <c r="DH46" s="127"/>
-      <c r="DI46" s="127"/>
-      <c r="DJ46" s="127"/>
-      <c r="DK46" s="127"/>
-      <c r="DL46" s="127"/>
-      <c r="DM46" s="127"/>
-      <c r="DN46" s="127"/>
-      <c r="DO46" s="128"/>
-      <c r="DP46" s="125"/>
+      <c r="DB46" s="119"/>
+      <c r="DC46" s="119"/>
+      <c r="DD46" s="119"/>
+      <c r="DE46" s="119"/>
+      <c r="DF46" s="119"/>
+      <c r="DG46" s="119"/>
+      <c r="DH46" s="119"/>
+      <c r="DI46" s="119"/>
+      <c r="DJ46" s="119"/>
+      <c r="DK46" s="119"/>
+      <c r="DL46" s="119"/>
+      <c r="DM46" s="119"/>
+      <c r="DN46" s="119"/>
+      <c r="DO46" s="120"/>
+      <c r="DP46" s="114"/>
       <c r="DQ46" s="32"/>
       <c r="DR46" s="32"/>
       <c r="DS46" s="32"/>
@@ -9841,11 +9759,11 @@
       <c r="EH46" s="32"/>
       <c r="EI46" s="32"/>
       <c r="EJ46" s="32"/>
-      <c r="EK46" s="124">
+      <c r="EK46" s="113">
         <f t="shared" si="72"/>
         <v>46171</v>
       </c>
-      <c r="EL46" s="124">
+      <c r="EL46" s="113">
         <f t="shared" si="73"/>
         <v>46236</v>
       </c>
@@ -9858,10 +9776,10 @@
       <c r="C47" s="39">
         <v>0</v>
       </c>
-      <c r="D47" s="64">
+      <c r="D47" s="55">
         <v>46188</v>
       </c>
-      <c r="E47" s="64">
+      <c r="E47" s="55">
         <v>46234</v>
       </c>
       <c r="F47" s="6"/>
@@ -9967,21 +9885,21 @@
       <c r="CY47" s="32"/>
       <c r="CZ47" s="32"/>
       <c r="DA47" s="32"/>
-      <c r="DB47" s="127"/>
-      <c r="DC47" s="127"/>
-      <c r="DD47" s="127"/>
-      <c r="DE47" s="127"/>
-      <c r="DF47" s="127"/>
-      <c r="DG47" s="127"/>
-      <c r="DH47" s="127"/>
-      <c r="DI47" s="127"/>
-      <c r="DJ47" s="127"/>
-      <c r="DK47" s="127"/>
-      <c r="DL47" s="127"/>
-      <c r="DM47" s="127"/>
-      <c r="DN47" s="127"/>
-      <c r="DO47" s="128"/>
-      <c r="DP47" s="125"/>
+      <c r="DB47" s="119"/>
+      <c r="DC47" s="119"/>
+      <c r="DD47" s="119"/>
+      <c r="DE47" s="119"/>
+      <c r="DF47" s="119"/>
+      <c r="DG47" s="119"/>
+      <c r="DH47" s="119"/>
+      <c r="DI47" s="119"/>
+      <c r="DJ47" s="119"/>
+      <c r="DK47" s="119"/>
+      <c r="DL47" s="119"/>
+      <c r="DM47" s="119"/>
+      <c r="DN47" s="119"/>
+      <c r="DO47" s="120"/>
+      <c r="DP47" s="114"/>
       <c r="DQ47" s="32"/>
       <c r="DR47" s="32"/>
       <c r="DS47" s="32"/>
@@ -10002,11 +9920,11 @@
       <c r="EH47" s="32"/>
       <c r="EI47" s="32"/>
       <c r="EJ47" s="32"/>
-      <c r="EK47" s="124">
+      <c r="EK47" s="113">
         <f t="shared" si="72"/>
         <v>46190</v>
       </c>
-      <c r="EL47" s="124">
+      <c r="EL47" s="113">
         <f t="shared" si="73"/>
         <v>46236</v>
       </c>
@@ -10017,10 +9935,10 @@
         <v>43</v>
       </c>
       <c r="C48" s="39"/>
-      <c r="D48" s="64">
+      <c r="D48" s="55">
         <v>46231</v>
       </c>
-      <c r="E48" s="64">
+      <c r="E48" s="55">
         <v>46233</v>
       </c>
       <c r="F48" s="6"/>
@@ -10123,21 +10041,21 @@
       <c r="CY48" s="32"/>
       <c r="CZ48" s="32"/>
       <c r="DA48" s="32"/>
-      <c r="DB48" s="127"/>
-      <c r="DC48" s="127"/>
-      <c r="DD48" s="127"/>
-      <c r="DE48" s="127"/>
-      <c r="DF48" s="127"/>
-      <c r="DG48" s="127"/>
-      <c r="DH48" s="127"/>
-      <c r="DI48" s="127"/>
-      <c r="DJ48" s="127"/>
-      <c r="DK48" s="127"/>
-      <c r="DL48" s="127"/>
-      <c r="DM48" s="127"/>
-      <c r="DN48" s="127"/>
-      <c r="DO48" s="128"/>
-      <c r="DP48" s="125"/>
+      <c r="DB48" s="119"/>
+      <c r="DC48" s="119"/>
+      <c r="DD48" s="119"/>
+      <c r="DE48" s="119"/>
+      <c r="DF48" s="119"/>
+      <c r="DG48" s="119"/>
+      <c r="DH48" s="119"/>
+      <c r="DI48" s="119"/>
+      <c r="DJ48" s="119"/>
+      <c r="DK48" s="119"/>
+      <c r="DL48" s="119"/>
+      <c r="DM48" s="119"/>
+      <c r="DN48" s="119"/>
+      <c r="DO48" s="120"/>
+      <c r="DP48" s="114"/>
       <c r="DQ48" s="32"/>
       <c r="DR48" s="32"/>
       <c r="DS48" s="32"/>
@@ -10158,11 +10076,11 @@
       <c r="EH48" s="32"/>
       <c r="EI48" s="32"/>
       <c r="EJ48" s="32"/>
-      <c r="EK48" s="124">
+      <c r="EK48" s="113">
         <f t="shared" si="72"/>
         <v>46233</v>
       </c>
-      <c r="EL48" s="124">
+      <c r="EL48" s="113">
         <f t="shared" si="73"/>
         <v>46235</v>
       </c>
@@ -10173,10 +10091,10 @@
         <v>44</v>
       </c>
       <c r="C49" s="39"/>
-      <c r="D49" s="64">
+      <c r="D49" s="55">
         <v>46234</v>
       </c>
-      <c r="E49" s="64">
+      <c r="E49" s="55">
         <v>46236</v>
       </c>
       <c r="F49" s="6"/>
@@ -10279,21 +10197,21 @@
       <c r="CY49" s="32"/>
       <c r="CZ49" s="32"/>
       <c r="DA49" s="32"/>
-      <c r="DB49" s="127"/>
-      <c r="DC49" s="127"/>
-      <c r="DD49" s="127"/>
-      <c r="DE49" s="127"/>
-      <c r="DF49" s="127"/>
-      <c r="DG49" s="127"/>
-      <c r="DH49" s="127"/>
-      <c r="DI49" s="127"/>
-      <c r="DJ49" s="127"/>
-      <c r="DK49" s="127"/>
-      <c r="DL49" s="127"/>
-      <c r="DM49" s="127"/>
-      <c r="DN49" s="127"/>
-      <c r="DO49" s="128"/>
-      <c r="DP49" s="125"/>
+      <c r="DB49" s="119"/>
+      <c r="DC49" s="119"/>
+      <c r="DD49" s="119"/>
+      <c r="DE49" s="119"/>
+      <c r="DF49" s="119"/>
+      <c r="DG49" s="119"/>
+      <c r="DH49" s="119"/>
+      <c r="DI49" s="119"/>
+      <c r="DJ49" s="119"/>
+      <c r="DK49" s="119"/>
+      <c r="DL49" s="119"/>
+      <c r="DM49" s="119"/>
+      <c r="DN49" s="119"/>
+      <c r="DO49" s="120"/>
+      <c r="DP49" s="114"/>
       <c r="DQ49" s="32"/>
       <c r="DR49" s="32"/>
       <c r="DS49" s="32"/>
@@ -10314,11 +10232,11 @@
       <c r="EH49" s="32"/>
       <c r="EI49" s="32"/>
       <c r="EJ49" s="32"/>
-      <c r="EK49" s="124">
+      <c r="EK49" s="113">
         <f t="shared" si="72"/>
         <v>46236</v>
       </c>
-      <c r="EL49" s="124">
+      <c r="EL49" s="113">
         <f t="shared" si="73"/>
         <v>46238</v>
       </c>
@@ -10329,10 +10247,10 @@
         <v>51</v>
       </c>
       <c r="C50" s="39"/>
-      <c r="D50" s="64">
+      <c r="D50" s="55">
         <v>46237</v>
       </c>
-      <c r="E50" s="64">
+      <c r="E50" s="55">
         <v>46238</v>
       </c>
       <c r="F50" s="6"/>
@@ -10435,21 +10353,21 @@
       <c r="CY50" s="32"/>
       <c r="CZ50" s="32"/>
       <c r="DA50" s="32"/>
-      <c r="DB50" s="127"/>
-      <c r="DC50" s="127"/>
-      <c r="DD50" s="127"/>
-      <c r="DE50" s="127"/>
-      <c r="DF50" s="127"/>
-      <c r="DG50" s="127"/>
-      <c r="DH50" s="127"/>
-      <c r="DI50" s="127"/>
-      <c r="DJ50" s="127"/>
-      <c r="DK50" s="127"/>
-      <c r="DL50" s="127"/>
-      <c r="DM50" s="127"/>
-      <c r="DN50" s="127"/>
-      <c r="DO50" s="128"/>
-      <c r="DP50" s="125"/>
+      <c r="DB50" s="119"/>
+      <c r="DC50" s="119"/>
+      <c r="DD50" s="119"/>
+      <c r="DE50" s="119"/>
+      <c r="DF50" s="119"/>
+      <c r="DG50" s="119"/>
+      <c r="DH50" s="119"/>
+      <c r="DI50" s="119"/>
+      <c r="DJ50" s="119"/>
+      <c r="DK50" s="119"/>
+      <c r="DL50" s="119"/>
+      <c r="DM50" s="119"/>
+      <c r="DN50" s="119"/>
+      <c r="DO50" s="120"/>
+      <c r="DP50" s="114"/>
       <c r="DQ50" s="32"/>
       <c r="DR50" s="32"/>
       <c r="DS50" s="32"/>
@@ -10470,11 +10388,11 @@
       <c r="EH50" s="32"/>
       <c r="EI50" s="32"/>
       <c r="EJ50" s="32"/>
-      <c r="EK50" s="124">
+      <c r="EK50" s="113">
         <f t="shared" si="72"/>
         <v>46239</v>
       </c>
-      <c r="EL50" s="124">
+      <c r="EL50" s="113">
         <f t="shared" si="73"/>
         <v>46240</v>
       </c>
@@ -10485,10 +10403,10 @@
         <v>47</v>
       </c>
       <c r="C51" s="39"/>
-      <c r="D51" s="64">
+      <c r="D51" s="55">
         <v>46239</v>
       </c>
-      <c r="E51" s="64">
+      <c r="E51" s="55">
         <v>46240</v>
       </c>
       <c r="F51" s="6"/>
@@ -10591,21 +10509,21 @@
       <c r="CY51" s="32"/>
       <c r="CZ51" s="32"/>
       <c r="DA51" s="32"/>
-      <c r="DB51" s="127"/>
-      <c r="DC51" s="127"/>
-      <c r="DD51" s="127"/>
-      <c r="DE51" s="127"/>
-      <c r="DF51" s="127"/>
-      <c r="DG51" s="127"/>
-      <c r="DH51" s="127"/>
-      <c r="DI51" s="127"/>
-      <c r="DJ51" s="127"/>
-      <c r="DK51" s="127"/>
-      <c r="DL51" s="127"/>
-      <c r="DM51" s="127"/>
-      <c r="DN51" s="127"/>
-      <c r="DO51" s="128"/>
-      <c r="DP51" s="125"/>
+      <c r="DB51" s="119"/>
+      <c r="DC51" s="119"/>
+      <c r="DD51" s="119"/>
+      <c r="DE51" s="119"/>
+      <c r="DF51" s="119"/>
+      <c r="DG51" s="119"/>
+      <c r="DH51" s="119"/>
+      <c r="DI51" s="119"/>
+      <c r="DJ51" s="119"/>
+      <c r="DK51" s="119"/>
+      <c r="DL51" s="119"/>
+      <c r="DM51" s="119"/>
+      <c r="DN51" s="119"/>
+      <c r="DO51" s="120"/>
+      <c r="DP51" s="114"/>
       <c r="DQ51" s="32"/>
       <c r="DR51" s="32"/>
       <c r="DS51" s="32"/>
@@ -10626,11 +10544,11 @@
       <c r="EH51" s="32"/>
       <c r="EI51" s="32"/>
       <c r="EJ51" s="32"/>
-      <c r="EK51" s="124">
+      <c r="EK51" s="113">
         <f t="shared" si="72"/>
         <v>46241</v>
       </c>
-      <c r="EL51" s="124">
+      <c r="EL51" s="113">
         <f t="shared" si="73"/>
         <v>46242</v>
       </c>
@@ -10641,10 +10559,10 @@
         <v>48</v>
       </c>
       <c r="C52" s="39"/>
-      <c r="D52" s="64">
+      <c r="D52" s="55">
         <v>46241</v>
       </c>
-      <c r="E52" s="64">
+      <c r="E52" s="55">
         <v>46243</v>
       </c>
       <c r="F52" s="6"/>
@@ -10747,21 +10665,21 @@
       <c r="CY52" s="32"/>
       <c r="CZ52" s="32"/>
       <c r="DA52" s="32"/>
-      <c r="DB52" s="127"/>
-      <c r="DC52" s="127"/>
-      <c r="DD52" s="127"/>
-      <c r="DE52" s="127"/>
-      <c r="DF52" s="127"/>
-      <c r="DG52" s="127"/>
-      <c r="DH52" s="127"/>
-      <c r="DI52" s="127"/>
-      <c r="DJ52" s="127"/>
-      <c r="DK52" s="127"/>
-      <c r="DL52" s="127"/>
-      <c r="DM52" s="127"/>
-      <c r="DN52" s="127"/>
-      <c r="DO52" s="128"/>
-      <c r="DP52" s="125"/>
+      <c r="DB52" s="119"/>
+      <c r="DC52" s="119"/>
+      <c r="DD52" s="119"/>
+      <c r="DE52" s="119"/>
+      <c r="DF52" s="119"/>
+      <c r="DG52" s="119"/>
+      <c r="DH52" s="119"/>
+      <c r="DI52" s="119"/>
+      <c r="DJ52" s="119"/>
+      <c r="DK52" s="119"/>
+      <c r="DL52" s="119"/>
+      <c r="DM52" s="119"/>
+      <c r="DN52" s="119"/>
+      <c r="DO52" s="120"/>
+      <c r="DP52" s="114"/>
       <c r="DQ52" s="32"/>
       <c r="DR52" s="32"/>
       <c r="DS52" s="32"/>
@@ -10782,25 +10700,25 @@
       <c r="EH52" s="32"/>
       <c r="EI52" s="32"/>
       <c r="EJ52" s="32"/>
-      <c r="EK52" s="124">
+      <c r="EK52" s="113">
         <f t="shared" si="72"/>
         <v>46243</v>
       </c>
-      <c r="EL52" s="124">
+      <c r="EL52" s="113">
         <f t="shared" si="73"/>
         <v>46245</v>
       </c>
     </row>
     <row r="53" spans="1:142" s="29" customFormat="1" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A53" s="4"/>
-      <c r="B53" s="119" t="s">
+      <c r="B53" s="108" t="s">
         <v>50</v>
       </c>
-      <c r="C53" s="117"/>
-      <c r="D53" s="118">
+      <c r="C53" s="106"/>
+      <c r="D53" s="107">
         <v>46258</v>
       </c>
-      <c r="E53" s="118">
+      <c r="E53" s="107">
         <v>46275</v>
       </c>
       <c r="F53" s="6"/>
@@ -10903,21 +10821,21 @@
       <c r="CY53" s="32"/>
       <c r="CZ53" s="32"/>
       <c r="DA53" s="32"/>
-      <c r="DB53" s="127"/>
-      <c r="DC53" s="127"/>
-      <c r="DD53" s="127"/>
-      <c r="DE53" s="127"/>
-      <c r="DF53" s="127"/>
-      <c r="DG53" s="127"/>
-      <c r="DH53" s="127"/>
-      <c r="DI53" s="127"/>
-      <c r="DJ53" s="127"/>
-      <c r="DK53" s="127"/>
-      <c r="DL53" s="127"/>
-      <c r="DM53" s="127"/>
-      <c r="DN53" s="127"/>
-      <c r="DO53" s="128"/>
-      <c r="DP53" s="125"/>
+      <c r="DB53" s="119"/>
+      <c r="DC53" s="119"/>
+      <c r="DD53" s="119"/>
+      <c r="DE53" s="119"/>
+      <c r="DF53" s="119"/>
+      <c r="DG53" s="119"/>
+      <c r="DH53" s="119"/>
+      <c r="DI53" s="119"/>
+      <c r="DJ53" s="119"/>
+      <c r="DK53" s="119"/>
+      <c r="DL53" s="119"/>
+      <c r="DM53" s="119"/>
+      <c r="DN53" s="119"/>
+      <c r="DO53" s="120"/>
+      <c r="DP53" s="114"/>
       <c r="DQ53" s="32"/>
       <c r="DR53" s="32"/>
       <c r="DS53" s="32"/>
@@ -10941,14 +10859,14 @@
     </row>
     <row r="54" spans="1:142" s="29" customFormat="1" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A54" s="4"/>
-      <c r="B54" s="120" t="s">
+      <c r="B54" s="109" t="s">
         <v>52</v>
       </c>
-      <c r="C54" s="121"/>
-      <c r="D54" s="122">
+      <c r="C54" s="110"/>
+      <c r="D54" s="111">
         <v>46276</v>
       </c>
-      <c r="E54" s="122">
+      <c r="E54" s="111">
         <v>46276</v>
       </c>
       <c r="F54" s="6"/>
@@ -11051,21 +10969,21 @@
       <c r="CY54" s="32"/>
       <c r="CZ54" s="32"/>
       <c r="DA54" s="32"/>
-      <c r="DB54" s="127"/>
-      <c r="DC54" s="127"/>
-      <c r="DD54" s="127"/>
-      <c r="DE54" s="127"/>
-      <c r="DF54" s="127"/>
-      <c r="DG54" s="127"/>
-      <c r="DH54" s="127"/>
-      <c r="DI54" s="127"/>
-      <c r="DJ54" s="127"/>
-      <c r="DK54" s="127"/>
-      <c r="DL54" s="127"/>
-      <c r="DM54" s="127"/>
-      <c r="DN54" s="127"/>
-      <c r="DO54" s="128"/>
-      <c r="DP54" s="125"/>
+      <c r="DB54" s="119"/>
+      <c r="DC54" s="119"/>
+      <c r="DD54" s="119"/>
+      <c r="DE54" s="119"/>
+      <c r="DF54" s="119"/>
+      <c r="DG54" s="119"/>
+      <c r="DH54" s="119"/>
+      <c r="DI54" s="119"/>
+      <c r="DJ54" s="119"/>
+      <c r="DK54" s="119"/>
+      <c r="DL54" s="119"/>
+      <c r="DM54" s="119"/>
+      <c r="DN54" s="119"/>
+      <c r="DO54" s="120"/>
+      <c r="DP54" s="114"/>
       <c r="DQ54" s="32"/>
       <c r="DR54" s="32"/>
       <c r="DS54" s="32"/>
@@ -11088,25 +11006,25 @@
       <c r="EJ54" s="32"/>
     </row>
     <row r="55" spans="1:142" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="DF55" s="126"/>
+      <c r="DF55" s="115"/>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="DB9:DO54"/>
-    <mergeCell ref="H4:AI4"/>
-    <mergeCell ref="AJ4:BM4"/>
-    <mergeCell ref="BN4:CR4"/>
-    <mergeCell ref="CS4:DW4"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
     <mergeCell ref="DX4:EJ4"/>
     <mergeCell ref="E5:E6"/>
     <mergeCell ref="P2:Y2"/>
     <mergeCell ref="P1:Y1"/>
     <mergeCell ref="H1:N1"/>
     <mergeCell ref="H2:N2"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="DB9:DO54"/>
+    <mergeCell ref="H4:AI4"/>
+    <mergeCell ref="AJ4:BM4"/>
+    <mergeCell ref="BN4:CR4"/>
+    <mergeCell ref="CS4:DW4"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C54">
     <cfRule type="dataBar" priority="61">
@@ -11122,150 +11040,135 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H41:DA44 ED9:EI16 ED41:EI44 H9:DA16 DP41:EB44 DP9:EB16">
-    <cfRule type="expression" dxfId="35" priority="44">
-      <formula>AND(task_start&lt;=H$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=H$5)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="34" priority="45" stopIfTrue="1">
+  <conditionalFormatting sqref="H9:DA16 DP9:EB16 ED9:EI16 H41:DA44 DP41:EB44 ED41:EI44">
+    <cfRule type="expression" dxfId="26" priority="45" stopIfTrue="1">
       <formula>AND(task_end&gt;=H$5,task_start&lt;I$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H18:DA20 H46:DA52 ED18:EI20 ED46:EI52 DP46:EB52 DP18:EB20">
-    <cfRule type="expression" dxfId="33" priority="42">
+  <conditionalFormatting sqref="H9:DA16 DP9:EJ16 H41:DA44 DP41:EJ44">
+    <cfRule type="expression" dxfId="25" priority="44">
       <formula>AND(task_start&lt;=H$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=H$5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="32" priority="43" stopIfTrue="1">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H18:DA20 DP18:EB20 ED18:EI20 H46:DA52 DP46:EB52 ED46:EI52">
+    <cfRule type="expression" dxfId="24" priority="43" stopIfTrue="1">
       <formula>AND(task_end&gt;=H$5,task_start&lt;I$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H22:DA23 ED22:EI23 DP22:EB23">
-    <cfRule type="expression" dxfId="31" priority="40">
+  <conditionalFormatting sqref="H18:DA20 DP18:EJ20 H46:DA52 DP46:EJ52">
+    <cfRule type="expression" dxfId="23" priority="42">
       <formula>AND(task_start&lt;=H$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=H$5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="30" priority="41" stopIfTrue="1">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H22:DA23 DP22:EB23 ED22:EI23">
+    <cfRule type="expression" dxfId="22" priority="41" stopIfTrue="1">
       <formula>AND(task_end&gt;=H$5,task_start&lt;I$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H25:DA28 ED25:EI28 DP25:EB28">
-    <cfRule type="expression" dxfId="29" priority="74">
+  <conditionalFormatting sqref="H22:DA23 DP22:EJ23">
+    <cfRule type="expression" dxfId="21" priority="40">
       <formula>AND(task_start&lt;=H$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=H$5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="28" priority="75" stopIfTrue="1">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H25:DA28 DP25:EB28 ED25:EI28">
+    <cfRule type="expression" dxfId="20" priority="75" stopIfTrue="1">
       <formula>AND(task_end&gt;=H$5,task_start&lt;I$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EC9:EC16 EC41:EC44 EJ9:EJ16 EJ41:EJ44">
-    <cfRule type="expression" dxfId="27" priority="80">
-      <formula>AND(task_start&lt;=EC$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=EC$5)</formula>
+  <conditionalFormatting sqref="H25:DA28 DP25:EJ28">
+    <cfRule type="expression" dxfId="19" priority="74">
+      <formula>AND(task_start&lt;=H$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=H$5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="26" priority="81" stopIfTrue="1">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H30:DA33 DP30:EB33 ED30:EI33">
+    <cfRule type="expression" dxfId="18" priority="36" stopIfTrue="1">
+      <formula>AND(task_end&gt;=H$5,task_start&lt;I$5)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H30:DA33 DP30:EJ33">
+    <cfRule type="expression" dxfId="17" priority="35">
+      <formula>AND(task_start&lt;=H$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=H$5)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H35:DA39 DP35:EB39 ED35:EI39">
+    <cfRule type="expression" dxfId="16" priority="31" stopIfTrue="1">
+      <formula>AND(task_end&gt;=H$5,task_start&lt;I$5)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H35:DA39 DP35:EJ39">
+    <cfRule type="expression" dxfId="15" priority="30">
+      <formula>AND(task_start&lt;=H$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=H$5)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H53:DA53 DP53:EI53">
+    <cfRule type="expression" dxfId="14" priority="7" stopIfTrue="1">
+      <formula>AND(task_end&gt;=H$5,task_start&lt;I$5)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H53:DA54 DP53:EJ54">
+    <cfRule type="expression" dxfId="13" priority="3">
+      <formula>AND(task_start&lt;=H$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=H$5)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H54:DA54 DP54:EB54 ED54:EI54">
+    <cfRule type="expression" dxfId="12" priority="4" stopIfTrue="1">
+      <formula>AND(task_end&gt;=H$5,task_start&lt;I$5)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="DB9">
+    <cfRule type="expression" dxfId="11" priority="155">
+      <formula>AND(task_start&lt;=DF$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=DF$5)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="10" priority="156" stopIfTrue="1">
+      <formula>AND(task_end&gt;=DF$5,task_start&lt;DG$5)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="9" priority="152">
+      <formula>AND(TODAY()&gt;=DF$5, TODAY()&lt;DG$5)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="EC9:EC16 EJ9:EJ16 EC41:EC44 EJ41:EJ44">
+    <cfRule type="expression" dxfId="8" priority="81" stopIfTrue="1">
       <formula>AND(task_end&gt;=EC$5,task_start&lt;#REF!)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EC18:EC20 EC46:EC52 EJ18:EJ20 EJ46:EJ52">
-    <cfRule type="expression" dxfId="25" priority="84">
-      <formula>AND(task_start&lt;=EC$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=EC$5)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="24" priority="85" stopIfTrue="1">
+  <conditionalFormatting sqref="EC18:EC20 EJ18:EJ20 EC46:EC52 EJ46:EJ52">
+    <cfRule type="expression" dxfId="7" priority="85" stopIfTrue="1">
       <formula>AND(task_end&gt;=EC$5,task_start&lt;#REF!)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EC22:EC23 EJ22:EJ23">
-    <cfRule type="expression" dxfId="23" priority="88">
-      <formula>AND(task_start&lt;=EC$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=EC$5)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="22" priority="89" stopIfTrue="1">
+    <cfRule type="expression" dxfId="6" priority="89" stopIfTrue="1">
       <formula>AND(task_end&gt;=EC$5,task_start&lt;#REF!)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EC25:EC28 EJ25:EJ28">
-    <cfRule type="expression" dxfId="21" priority="92">
-      <formula>AND(task_start&lt;=EC$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=EC$5)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="20" priority="93" stopIfTrue="1">
+    <cfRule type="expression" dxfId="5" priority="93" stopIfTrue="1">
       <formula>AND(task_end&gt;=EC$5,task_start&lt;#REF!)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H30:DA33 ED30:EI33 DP30:EB33">
-    <cfRule type="expression" dxfId="19" priority="35">
-      <formula>AND(task_start&lt;=H$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=H$5)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="18" priority="36" stopIfTrue="1">
-      <formula>AND(task_end&gt;=H$5,task_start&lt;I$5)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H35:DA39 ED35:EI39 DP35:EB39">
-    <cfRule type="expression" dxfId="17" priority="30">
-      <formula>AND(task_start&lt;=H$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=H$5)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="16" priority="31" stopIfTrue="1">
-      <formula>AND(task_end&gt;=H$5,task_start&lt;I$5)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H53:DA53 DP53:EI53">
-    <cfRule type="expression" dxfId="15" priority="6">
-      <formula>AND(task_start&lt;=H$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=H$5)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="14" priority="7" stopIfTrue="1">
-      <formula>AND(task_end&gt;=H$5,task_start&lt;I$5)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H54:DA54 ED54:EI54 DP54:EB54">
-    <cfRule type="expression" dxfId="13" priority="3">
-      <formula>AND(task_start&lt;=H$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=H$5)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="12" priority="4" stopIfTrue="1">
-      <formula>AND(task_end&gt;=H$5,task_start&lt;I$5)</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="EC30:EC33 EJ30:EJ33">
-    <cfRule type="expression" dxfId="11" priority="116">
-      <formula>AND(task_start&lt;=EC$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=EC$5)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="10" priority="117" stopIfTrue="1">
+    <cfRule type="expression" dxfId="4" priority="117" stopIfTrue="1">
       <formula>AND(task_end&gt;=EC$5,task_start&lt;#REF!)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EC35:EC39 EJ35:EJ39">
-    <cfRule type="expression" dxfId="9" priority="122">
-      <formula>AND(task_start&lt;=EC$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=EC$5)</formula>
+    <cfRule type="expression" dxfId="3" priority="123" stopIfTrue="1">
+      <formula>AND(task_end&gt;=EC$5,task_start&lt;#REF!)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="123" stopIfTrue="1">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="EC53">
+    <cfRule type="expression" dxfId="2" priority="1">
+      <formula>AND(TODAY()&gt;=EC$5, TODAY()&lt;ED$5)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="EC54 EJ54">
+    <cfRule type="expression" dxfId="1" priority="150" stopIfTrue="1">
       <formula>AND(task_end&gt;=EC$5,task_start&lt;#REF!)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EJ53">
-    <cfRule type="expression" dxfId="7" priority="140">
-      <formula>AND(task_start&lt;=EJ$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=EJ$5)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="6" priority="141" stopIfTrue="1">
+    <cfRule type="expression" dxfId="0" priority="141" stopIfTrue="1">
       <formula>AND(task_end&gt;=EJ$5,task_start&lt;#REF!)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="EC54 EJ54">
-    <cfRule type="expression" dxfId="5" priority="149">
-      <formula>AND(task_start&lt;=EC$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=EC$5)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="4" priority="150" stopIfTrue="1">
-      <formula>AND(task_end&gt;=EC$5,task_start&lt;#REF!)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="EC53">
-    <cfRule type="expression" dxfId="3" priority="1">
-      <formula>AND(TODAY()&gt;=EC$5, TODAY()&lt;ED$5)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="DB9">
-    <cfRule type="expression" dxfId="2" priority="152">
-      <formula>AND(TODAY()&gt;=DF$5, TODAY()&lt;DG$5)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="DB9">
-    <cfRule type="expression" dxfId="1" priority="155">
-      <formula>AND(task_start&lt;=DF$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=DF$5)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="0" priority="156" stopIfTrue="1">
-      <formula>AND(task_end&gt;=DF$5,task_start&lt;DG$5)</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations disablePrompts="1" count="12">
@@ -11320,7 +11223,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="17.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.15">
@@ -11367,6 +11270,13 @@
     <row r="5" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
         <v>63</v>
+      </c>
+      <c r="C5" t="s">
+        <v>77</v>
+      </c>
+      <c r="D5" t="e">
+        <f>SUM([1]Sessions_data!$B$2:$B$1048576)</f>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.15">
@@ -11425,6 +11335,35 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Url xsi:nil="true"/>
+      <Description xsi:nil="true"/>
+    </Image>
+    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
+    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ImageTagsTaxHTField>
+    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
+    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010079F111ED35F8CC479449609E8A0923A6" ma:contentTypeVersion="28" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="60f5a4f2d2b0abadcf532d48ebf9cb71">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xmlns:ns3="16c05727-aa75-4e4a-9b5f-8a80a1165891" xmlns:ns4="230e9df3-be65-4c73-a93b-d1236ebd677e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7dd78129e6a1811f84807ad11c651531" ns1:_="" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -11736,52 +11675,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Url xsi:nil="true"/>
-      <Description xsi:nil="true"/>
-    </Image>
-    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
-    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ImageTagsTaxHTField>
-    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
-    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A09426A3-87E9-4865-8A6C-3456B026AE03}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97245281-08F3-4104-84BD-39F3D8CFB195}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
-    <ds:schemaRef ds:uri="16c05727-aa75-4e4a-9b5f-8a80a1165891"/>
-    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -11806,9 +11703,22 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97245281-08F3-4104-84BD-39F3D8CFB195}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A09426A3-87E9-4865-8A6C-3456B026AE03}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
+    <ds:schemaRef ds:uri="16c05727-aa75-4e4a-9b5f-8a80a1165891"/>
+    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/Progress Tracker.xlsx
+++ b/Progress Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/will/Desktop/Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB923163-FCB4-A04C-92F7-E7C4937C89C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DB6B788-BAF3-0D4F-AE6C-2BBB8BB4F949}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Project schedule" sheetId="11" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="98">
   <si>
     <t>PROGRESS</t>
   </si>
@@ -284,6 +284,66 @@
   <si>
     <t>Actual no. Sessions</t>
   </si>
+  <si>
+    <t>Katie Mckenna</t>
+  </si>
+  <si>
+    <t>Ben Menges</t>
+  </si>
+  <si>
+    <t>Helen Menges</t>
+  </si>
+  <si>
+    <t>Tom Menges</t>
+  </si>
+  <si>
+    <t>Louise McKenna</t>
+  </si>
+  <si>
+    <t>Received Data</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Folder Number</t>
+  </si>
+  <si>
+    <t>Number of Sessions</t>
+  </si>
+  <si>
+    <t>Josie Collings</t>
+  </si>
+  <si>
+    <t>Kamila Turczewski</t>
+  </si>
+  <si>
+    <t>Email Address</t>
+  </si>
+  <si>
+    <t>aravindkokkranikal@gmail.com</t>
+  </si>
+  <si>
+    <t>wmcken01@student.bbk.ac.uk</t>
+  </si>
+  <si>
+    <t>defuzuner@gmail.com</t>
+  </si>
+  <si>
+    <t>mckbigfish@googlemail.com</t>
+  </si>
+  <si>
+    <t>Adrian Turcana</t>
+  </si>
+  <si>
+    <t>Madhu</t>
+  </si>
+  <si>
+    <t>Hugo Smith</t>
+  </si>
 </sst>
 </file>
 
@@ -296,7 +356,7 @@
     <numFmt numFmtId="166" formatCode="mmm\ d\,\ yyyy"/>
     <numFmt numFmtId="167" formatCode="d"/>
   </numFmts>
-  <fonts count="24" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -464,6 +524,12 @@
       <sz val="72"/>
       <color theme="0"/>
       <name val="Arial (Body)"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF5E5E5E"/>
+      <name val="Helvetica"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="20">
@@ -1142,7 +1208,7 @@
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="133">
+  <cellXfs count="135">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1482,19 +1548,22 @@
     <xf numFmtId="167" fontId="15" fillId="12" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180"/>
-    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="22" fillId="2" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1507,15 +1576,14 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="3" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="13">
     <cellStyle name="Comma" xfId="4" builtinId="3" customBuiltin="1"/>
@@ -1664,18 +1732,6 @@
       </border>
     </dxf>
     <dxf>
-      <border>
-        <left style="thin">
-          <color theme="5"/>
-        </left>
-        <right style="thin">
-          <color theme="5"/>
-        </right>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="4" tint="0.39994506668294322"/>
@@ -1705,6 +1761,18 @@
         <bottom style="thin">
           <color theme="0" tint="-4.9989318521683403E-2"/>
         </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="5"/>
+        </left>
+        <right style="thin">
+          <color theme="5"/>
+        </right>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -2362,57 +2430,57 @@
       <c r="D1" s="8"/>
       <c r="E1" s="9"/>
       <c r="G1" s="1"/>
-      <c r="H1" s="128" t="s">
+      <c r="H1" s="129" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="129"/>
-      <c r="J1" s="129"/>
-      <c r="K1" s="129"/>
-      <c r="L1" s="129"/>
-      <c r="M1" s="129"/>
-      <c r="N1" s="129"/>
+      <c r="I1" s="130"/>
+      <c r="J1" s="130"/>
+      <c r="K1" s="130"/>
+      <c r="L1" s="130"/>
+      <c r="M1" s="130"/>
+      <c r="N1" s="130"/>
       <c r="O1" s="12"/>
-      <c r="P1" s="126">
+      <c r="P1" s="127">
         <f>DATE(2026,5,6)</f>
         <v>46148</v>
       </c>
-      <c r="Q1" s="127"/>
-      <c r="R1" s="127"/>
-      <c r="S1" s="127"/>
-      <c r="T1" s="127"/>
-      <c r="U1" s="127"/>
-      <c r="V1" s="127"/>
-      <c r="W1" s="127"/>
-      <c r="X1" s="127"/>
-      <c r="Y1" s="127"/>
+      <c r="Q1" s="128"/>
+      <c r="R1" s="128"/>
+      <c r="S1" s="128"/>
+      <c r="T1" s="128"/>
+      <c r="U1" s="128"/>
+      <c r="V1" s="128"/>
+      <c r="W1" s="128"/>
+      <c r="X1" s="128"/>
+      <c r="Y1" s="128"/>
     </row>
     <row r="2" spans="1:142" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="50"/>
       <c r="C2" s="10"/>
       <c r="D2" s="11"/>
       <c r="E2" s="10"/>
-      <c r="H2" s="128" t="s">
+      <c r="H2" s="129" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="129"/>
-      <c r="J2" s="129"/>
-      <c r="K2" s="129"/>
-      <c r="L2" s="129"/>
-      <c r="M2" s="129"/>
-      <c r="N2" s="129"/>
+      <c r="I2" s="130"/>
+      <c r="J2" s="130"/>
+      <c r="K2" s="130"/>
+      <c r="L2" s="130"/>
+      <c r="M2" s="130"/>
+      <c r="N2" s="130"/>
       <c r="O2" s="12"/>
-      <c r="P2" s="124">
+      <c r="P2" s="125">
         <v>1</v>
       </c>
-      <c r="Q2" s="125"/>
-      <c r="R2" s="125"/>
-      <c r="S2" s="125"/>
-      <c r="T2" s="125"/>
-      <c r="U2" s="125"/>
-      <c r="V2" s="125"/>
-      <c r="W2" s="125"/>
-      <c r="X2" s="125"/>
-      <c r="Y2" s="125"/>
+      <c r="Q2" s="126"/>
+      <c r="R2" s="126"/>
+      <c r="S2" s="126"/>
+      <c r="T2" s="126"/>
+      <c r="U2" s="126"/>
+      <c r="V2" s="126"/>
+      <c r="W2" s="126"/>
+      <c r="X2" s="126"/>
+      <c r="Y2" s="126"/>
     </row>
     <row r="3" spans="1:142" s="14" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="4"/>
@@ -2424,153 +2492,153 @@
       <c r="A4" s="5"/>
       <c r="B4" s="17"/>
       <c r="D4" s="18"/>
-      <c r="H4" s="121" t="s">
+      <c r="H4" s="124" t="s">
         <v>54</v>
       </c>
-      <c r="I4" s="121"/>
-      <c r="J4" s="121"/>
-      <c r="K4" s="121"/>
-      <c r="L4" s="121"/>
-      <c r="M4" s="121"/>
-      <c r="N4" s="121"/>
-      <c r="O4" s="121"/>
-      <c r="P4" s="121"/>
-      <c r="Q4" s="121"/>
-      <c r="R4" s="121"/>
-      <c r="S4" s="121"/>
-      <c r="T4" s="121"/>
-      <c r="U4" s="121"/>
-      <c r="V4" s="121"/>
-      <c r="W4" s="121"/>
-      <c r="X4" s="121"/>
-      <c r="Y4" s="121"/>
-      <c r="Z4" s="121"/>
-      <c r="AA4" s="121"/>
-      <c r="AB4" s="121"/>
-      <c r="AC4" s="121"/>
-      <c r="AD4" s="121"/>
-      <c r="AE4" s="121"/>
-      <c r="AF4" s="121"/>
-      <c r="AG4" s="121"/>
-      <c r="AH4" s="121"/>
-      <c r="AI4" s="121"/>
-      <c r="AJ4" s="121" t="s">
+      <c r="I4" s="124"/>
+      <c r="J4" s="124"/>
+      <c r="K4" s="124"/>
+      <c r="L4" s="124"/>
+      <c r="M4" s="124"/>
+      <c r="N4" s="124"/>
+      <c r="O4" s="124"/>
+      <c r="P4" s="124"/>
+      <c r="Q4" s="124"/>
+      <c r="R4" s="124"/>
+      <c r="S4" s="124"/>
+      <c r="T4" s="124"/>
+      <c r="U4" s="124"/>
+      <c r="V4" s="124"/>
+      <c r="W4" s="124"/>
+      <c r="X4" s="124"/>
+      <c r="Y4" s="124"/>
+      <c r="Z4" s="124"/>
+      <c r="AA4" s="124"/>
+      <c r="AB4" s="124"/>
+      <c r="AC4" s="124"/>
+      <c r="AD4" s="124"/>
+      <c r="AE4" s="124"/>
+      <c r="AF4" s="124"/>
+      <c r="AG4" s="124"/>
+      <c r="AH4" s="124"/>
+      <c r="AI4" s="124"/>
+      <c r="AJ4" s="124" t="s">
         <v>55</v>
       </c>
-      <c r="AK4" s="121"/>
-      <c r="AL4" s="121"/>
-      <c r="AM4" s="121"/>
-      <c r="AN4" s="121"/>
-      <c r="AO4" s="121"/>
-      <c r="AP4" s="121"/>
-      <c r="AQ4" s="121"/>
-      <c r="AR4" s="121"/>
-      <c r="AS4" s="121"/>
-      <c r="AT4" s="121"/>
-      <c r="AU4" s="121"/>
-      <c r="AV4" s="121"/>
-      <c r="AW4" s="121"/>
-      <c r="AX4" s="121"/>
-      <c r="AY4" s="121"/>
-      <c r="AZ4" s="121"/>
-      <c r="BA4" s="121"/>
-      <c r="BB4" s="121"/>
-      <c r="BC4" s="121"/>
-      <c r="BD4" s="121"/>
-      <c r="BE4" s="121"/>
-      <c r="BF4" s="121"/>
-      <c r="BG4" s="121"/>
-      <c r="BH4" s="121"/>
-      <c r="BI4" s="121"/>
-      <c r="BJ4" s="121"/>
-      <c r="BK4" s="121"/>
-      <c r="BL4" s="121"/>
-      <c r="BM4" s="121"/>
-      <c r="BN4" s="121" t="s">
+      <c r="AK4" s="124"/>
+      <c r="AL4" s="124"/>
+      <c r="AM4" s="124"/>
+      <c r="AN4" s="124"/>
+      <c r="AO4" s="124"/>
+      <c r="AP4" s="124"/>
+      <c r="AQ4" s="124"/>
+      <c r="AR4" s="124"/>
+      <c r="AS4" s="124"/>
+      <c r="AT4" s="124"/>
+      <c r="AU4" s="124"/>
+      <c r="AV4" s="124"/>
+      <c r="AW4" s="124"/>
+      <c r="AX4" s="124"/>
+      <c r="AY4" s="124"/>
+      <c r="AZ4" s="124"/>
+      <c r="BA4" s="124"/>
+      <c r="BB4" s="124"/>
+      <c r="BC4" s="124"/>
+      <c r="BD4" s="124"/>
+      <c r="BE4" s="124"/>
+      <c r="BF4" s="124"/>
+      <c r="BG4" s="124"/>
+      <c r="BH4" s="124"/>
+      <c r="BI4" s="124"/>
+      <c r="BJ4" s="124"/>
+      <c r="BK4" s="124"/>
+      <c r="BL4" s="124"/>
+      <c r="BM4" s="124"/>
+      <c r="BN4" s="124" t="s">
         <v>56</v>
       </c>
-      <c r="BO4" s="121"/>
-      <c r="BP4" s="121"/>
-      <c r="BQ4" s="121"/>
-      <c r="BR4" s="121"/>
-      <c r="BS4" s="121"/>
-      <c r="BT4" s="121"/>
-      <c r="BU4" s="121"/>
-      <c r="BV4" s="121"/>
-      <c r="BW4" s="121"/>
-      <c r="BX4" s="121"/>
-      <c r="BY4" s="121"/>
-      <c r="BZ4" s="121"/>
-      <c r="CA4" s="121"/>
-      <c r="CB4" s="121"/>
-      <c r="CC4" s="121"/>
-      <c r="CD4" s="121"/>
-      <c r="CE4" s="121"/>
-      <c r="CF4" s="121"/>
-      <c r="CG4" s="121"/>
-      <c r="CH4" s="121"/>
-      <c r="CI4" s="121"/>
-      <c r="CJ4" s="121"/>
-      <c r="CK4" s="121"/>
-      <c r="CL4" s="121"/>
-      <c r="CM4" s="121"/>
-      <c r="CN4" s="121"/>
-      <c r="CO4" s="121"/>
-      <c r="CP4" s="121"/>
-      <c r="CQ4" s="121"/>
-      <c r="CR4" s="121"/>
-      <c r="CS4" s="121" t="s">
+      <c r="BO4" s="124"/>
+      <c r="BP4" s="124"/>
+      <c r="BQ4" s="124"/>
+      <c r="BR4" s="124"/>
+      <c r="BS4" s="124"/>
+      <c r="BT4" s="124"/>
+      <c r="BU4" s="124"/>
+      <c r="BV4" s="124"/>
+      <c r="BW4" s="124"/>
+      <c r="BX4" s="124"/>
+      <c r="BY4" s="124"/>
+      <c r="BZ4" s="124"/>
+      <c r="CA4" s="124"/>
+      <c r="CB4" s="124"/>
+      <c r="CC4" s="124"/>
+      <c r="CD4" s="124"/>
+      <c r="CE4" s="124"/>
+      <c r="CF4" s="124"/>
+      <c r="CG4" s="124"/>
+      <c r="CH4" s="124"/>
+      <c r="CI4" s="124"/>
+      <c r="CJ4" s="124"/>
+      <c r="CK4" s="124"/>
+      <c r="CL4" s="124"/>
+      <c r="CM4" s="124"/>
+      <c r="CN4" s="124"/>
+      <c r="CO4" s="124"/>
+      <c r="CP4" s="124"/>
+      <c r="CQ4" s="124"/>
+      <c r="CR4" s="124"/>
+      <c r="CS4" s="124" t="s">
         <v>57</v>
       </c>
-      <c r="CT4" s="121"/>
-      <c r="CU4" s="121"/>
-      <c r="CV4" s="121"/>
-      <c r="CW4" s="121"/>
-      <c r="CX4" s="121"/>
-      <c r="CY4" s="121"/>
-      <c r="CZ4" s="121"/>
-      <c r="DA4" s="121"/>
-      <c r="DB4" s="121"/>
-      <c r="DC4" s="121"/>
-      <c r="DD4" s="121"/>
-      <c r="DE4" s="121"/>
-      <c r="DF4" s="121"/>
-      <c r="DG4" s="121"/>
-      <c r="DH4" s="121"/>
-      <c r="DI4" s="121"/>
-      <c r="DJ4" s="121"/>
-      <c r="DK4" s="121"/>
-      <c r="DL4" s="121"/>
-      <c r="DM4" s="121"/>
-      <c r="DN4" s="121"/>
-      <c r="DO4" s="121"/>
-      <c r="DP4" s="121"/>
-      <c r="DQ4" s="121"/>
-      <c r="DR4" s="121"/>
-      <c r="DS4" s="121"/>
-      <c r="DT4" s="121"/>
-      <c r="DU4" s="121"/>
-      <c r="DV4" s="121"/>
-      <c r="DW4" s="121"/>
-      <c r="DX4" s="121" t="s">
+      <c r="CT4" s="124"/>
+      <c r="CU4" s="124"/>
+      <c r="CV4" s="124"/>
+      <c r="CW4" s="124"/>
+      <c r="CX4" s="124"/>
+      <c r="CY4" s="124"/>
+      <c r="CZ4" s="124"/>
+      <c r="DA4" s="124"/>
+      <c r="DB4" s="124"/>
+      <c r="DC4" s="124"/>
+      <c r="DD4" s="124"/>
+      <c r="DE4" s="124"/>
+      <c r="DF4" s="124"/>
+      <c r="DG4" s="124"/>
+      <c r="DH4" s="124"/>
+      <c r="DI4" s="124"/>
+      <c r="DJ4" s="124"/>
+      <c r="DK4" s="124"/>
+      <c r="DL4" s="124"/>
+      <c r="DM4" s="124"/>
+      <c r="DN4" s="124"/>
+      <c r="DO4" s="124"/>
+      <c r="DP4" s="124"/>
+      <c r="DQ4" s="124"/>
+      <c r="DR4" s="124"/>
+      <c r="DS4" s="124"/>
+      <c r="DT4" s="124"/>
+      <c r="DU4" s="124"/>
+      <c r="DV4" s="124"/>
+      <c r="DW4" s="124"/>
+      <c r="DX4" s="124" t="s">
         <v>58</v>
       </c>
-      <c r="DY4" s="121"/>
-      <c r="DZ4" s="121"/>
-      <c r="EA4" s="121"/>
-      <c r="EB4" s="121"/>
-      <c r="EC4" s="121"/>
-      <c r="ED4" s="121"/>
-      <c r="EE4" s="121"/>
-      <c r="EF4" s="121"/>
-      <c r="EG4" s="121"/>
-      <c r="EH4" s="121"/>
-      <c r="EI4" s="121"/>
-      <c r="EJ4" s="121"/>
+      <c r="DY4" s="124"/>
+      <c r="DZ4" s="124"/>
+      <c r="EA4" s="124"/>
+      <c r="EB4" s="124"/>
+      <c r="EC4" s="124"/>
+      <c r="ED4" s="124"/>
+      <c r="EE4" s="124"/>
+      <c r="EF4" s="124"/>
+      <c r="EG4" s="124"/>
+      <c r="EH4" s="124"/>
+      <c r="EI4" s="124"/>
+      <c r="EJ4" s="124"/>
     </row>
     <row r="5" spans="1:142" s="14" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="130"/>
-      <c r="B5" s="131" t="s">
+      <c r="A5" s="119"/>
+      <c r="B5" s="120" t="s">
         <v>3</v>
       </c>
       <c r="C5" s="122" t="s">
@@ -3116,8 +3184,8 @@
       </c>
     </row>
     <row r="6" spans="1:142" s="14" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="130"/>
-      <c r="B6" s="132"/>
+      <c r="A6" s="119"/>
+      <c r="B6" s="121"/>
       <c r="C6" s="123"/>
       <c r="D6" s="123"/>
       <c r="E6" s="123"/>
@@ -3953,7 +4021,7 @@
         <v>9</v>
       </c>
       <c r="C9" s="31">
-        <v>0.1</v>
+        <v>0.66</v>
       </c>
       <c r="D9" s="51">
         <f>Project_Start</f>
@@ -4065,22 +4133,22 @@
       <c r="CY9" s="32"/>
       <c r="CZ9" s="32"/>
       <c r="DA9" s="32"/>
-      <c r="DB9" s="119" t="s">
+      <c r="DB9" s="131" t="s">
         <v>53</v>
       </c>
-      <c r="DC9" s="119"/>
-      <c r="DD9" s="119"/>
-      <c r="DE9" s="119"/>
-      <c r="DF9" s="119"/>
-      <c r="DG9" s="119"/>
-      <c r="DH9" s="119"/>
-      <c r="DI9" s="119"/>
-      <c r="DJ9" s="119"/>
-      <c r="DK9" s="119"/>
-      <c r="DL9" s="119"/>
-      <c r="DM9" s="119"/>
-      <c r="DN9" s="119"/>
-      <c r="DO9" s="120"/>
+      <c r="DC9" s="131"/>
+      <c r="DD9" s="131"/>
+      <c r="DE9" s="131"/>
+      <c r="DF9" s="131"/>
+      <c r="DG9" s="131"/>
+      <c r="DH9" s="131"/>
+      <c r="DI9" s="131"/>
+      <c r="DJ9" s="131"/>
+      <c r="DK9" s="131"/>
+      <c r="DL9" s="131"/>
+      <c r="DM9" s="131"/>
+      <c r="DN9" s="131"/>
+      <c r="DO9" s="132"/>
       <c r="DP9" s="114"/>
       <c r="DQ9" s="32"/>
       <c r="DR9" s="32"/>
@@ -4217,20 +4285,20 @@
       <c r="CY10" s="32"/>
       <c r="CZ10" s="32"/>
       <c r="DA10" s="32"/>
-      <c r="DB10" s="119"/>
-      <c r="DC10" s="119"/>
-      <c r="DD10" s="119"/>
-      <c r="DE10" s="119"/>
-      <c r="DF10" s="119"/>
-      <c r="DG10" s="119"/>
-      <c r="DH10" s="119"/>
-      <c r="DI10" s="119"/>
-      <c r="DJ10" s="119"/>
-      <c r="DK10" s="119"/>
-      <c r="DL10" s="119"/>
-      <c r="DM10" s="119"/>
-      <c r="DN10" s="119"/>
-      <c r="DO10" s="120"/>
+      <c r="DB10" s="131"/>
+      <c r="DC10" s="131"/>
+      <c r="DD10" s="131"/>
+      <c r="DE10" s="131"/>
+      <c r="DF10" s="131"/>
+      <c r="DG10" s="131"/>
+      <c r="DH10" s="131"/>
+      <c r="DI10" s="131"/>
+      <c r="DJ10" s="131"/>
+      <c r="DK10" s="131"/>
+      <c r="DL10" s="131"/>
+      <c r="DM10" s="131"/>
+      <c r="DN10" s="131"/>
+      <c r="DO10" s="132"/>
       <c r="DP10" s="114"/>
       <c r="DQ10" s="32"/>
       <c r="DR10" s="32"/>
@@ -4267,7 +4335,7 @@
         <v>12</v>
       </c>
       <c r="C11" s="34">
-        <v>0.05</v>
+        <v>0.12</v>
       </c>
       <c r="D11" s="52">
         <v>46167</v>
@@ -4378,20 +4446,20 @@
       <c r="CY11" s="32"/>
       <c r="CZ11" s="32"/>
       <c r="DA11" s="32"/>
-      <c r="DB11" s="119"/>
-      <c r="DC11" s="119"/>
-      <c r="DD11" s="119"/>
-      <c r="DE11" s="119"/>
-      <c r="DF11" s="119"/>
-      <c r="DG11" s="119"/>
-      <c r="DH11" s="119"/>
-      <c r="DI11" s="119"/>
-      <c r="DJ11" s="119"/>
-      <c r="DK11" s="119"/>
-      <c r="DL11" s="119"/>
-      <c r="DM11" s="119"/>
-      <c r="DN11" s="119"/>
-      <c r="DO11" s="120"/>
+      <c r="DB11" s="131"/>
+      <c r="DC11" s="131"/>
+      <c r="DD11" s="131"/>
+      <c r="DE11" s="131"/>
+      <c r="DF11" s="131"/>
+      <c r="DG11" s="131"/>
+      <c r="DH11" s="131"/>
+      <c r="DI11" s="131"/>
+      <c r="DJ11" s="131"/>
+      <c r="DK11" s="131"/>
+      <c r="DL11" s="131"/>
+      <c r="DM11" s="131"/>
+      <c r="DN11" s="131"/>
+      <c r="DO11" s="132"/>
       <c r="DP11" s="114"/>
       <c r="DQ11" s="32"/>
       <c r="DR11" s="32"/>
@@ -4539,20 +4607,20 @@
       <c r="CY12" s="32"/>
       <c r="CZ12" s="32"/>
       <c r="DA12" s="32"/>
-      <c r="DB12" s="119"/>
-      <c r="DC12" s="119"/>
-      <c r="DD12" s="119"/>
-      <c r="DE12" s="119"/>
-      <c r="DF12" s="119"/>
-      <c r="DG12" s="119"/>
-      <c r="DH12" s="119"/>
-      <c r="DI12" s="119"/>
-      <c r="DJ12" s="119"/>
-      <c r="DK12" s="119"/>
-      <c r="DL12" s="119"/>
-      <c r="DM12" s="119"/>
-      <c r="DN12" s="119"/>
-      <c r="DO12" s="120"/>
+      <c r="DB12" s="131"/>
+      <c r="DC12" s="131"/>
+      <c r="DD12" s="131"/>
+      <c r="DE12" s="131"/>
+      <c r="DF12" s="131"/>
+      <c r="DG12" s="131"/>
+      <c r="DH12" s="131"/>
+      <c r="DI12" s="131"/>
+      <c r="DJ12" s="131"/>
+      <c r="DK12" s="131"/>
+      <c r="DL12" s="131"/>
+      <c r="DM12" s="131"/>
+      <c r="DN12" s="131"/>
+      <c r="DO12" s="132"/>
       <c r="DP12" s="114"/>
       <c r="DQ12" s="32"/>
       <c r="DR12" s="32"/>
@@ -4697,20 +4765,20 @@
       <c r="CY13" s="32"/>
       <c r="CZ13" s="32"/>
       <c r="DA13" s="32"/>
-      <c r="DB13" s="119"/>
-      <c r="DC13" s="119"/>
-      <c r="DD13" s="119"/>
-      <c r="DE13" s="119"/>
-      <c r="DF13" s="119"/>
-      <c r="DG13" s="119"/>
-      <c r="DH13" s="119"/>
-      <c r="DI13" s="119"/>
-      <c r="DJ13" s="119"/>
-      <c r="DK13" s="119"/>
-      <c r="DL13" s="119"/>
-      <c r="DM13" s="119"/>
-      <c r="DN13" s="119"/>
-      <c r="DO13" s="120"/>
+      <c r="DB13" s="131"/>
+      <c r="DC13" s="131"/>
+      <c r="DD13" s="131"/>
+      <c r="DE13" s="131"/>
+      <c r="DF13" s="131"/>
+      <c r="DG13" s="131"/>
+      <c r="DH13" s="131"/>
+      <c r="DI13" s="131"/>
+      <c r="DJ13" s="131"/>
+      <c r="DK13" s="131"/>
+      <c r="DL13" s="131"/>
+      <c r="DM13" s="131"/>
+      <c r="DN13" s="131"/>
+      <c r="DO13" s="132"/>
       <c r="DP13" s="114"/>
       <c r="DQ13" s="32"/>
       <c r="DR13" s="32"/>
@@ -4747,7 +4815,7 @@
         <v>11</v>
       </c>
       <c r="C14" s="34">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="D14" s="52">
         <v>46182</v>
@@ -4858,20 +4926,20 @@
       <c r="CY14" s="32"/>
       <c r="CZ14" s="32"/>
       <c r="DA14" s="32"/>
-      <c r="DB14" s="119"/>
-      <c r="DC14" s="119"/>
-      <c r="DD14" s="119"/>
-      <c r="DE14" s="119"/>
-      <c r="DF14" s="119"/>
-      <c r="DG14" s="119"/>
-      <c r="DH14" s="119"/>
-      <c r="DI14" s="119"/>
-      <c r="DJ14" s="119"/>
-      <c r="DK14" s="119"/>
-      <c r="DL14" s="119"/>
-      <c r="DM14" s="119"/>
-      <c r="DN14" s="119"/>
-      <c r="DO14" s="120"/>
+      <c r="DB14" s="131"/>
+      <c r="DC14" s="131"/>
+      <c r="DD14" s="131"/>
+      <c r="DE14" s="131"/>
+      <c r="DF14" s="131"/>
+      <c r="DG14" s="131"/>
+      <c r="DH14" s="131"/>
+      <c r="DI14" s="131"/>
+      <c r="DJ14" s="131"/>
+      <c r="DK14" s="131"/>
+      <c r="DL14" s="131"/>
+      <c r="DM14" s="131"/>
+      <c r="DN14" s="131"/>
+      <c r="DO14" s="132"/>
       <c r="DP14" s="114"/>
       <c r="DQ14" s="32"/>
       <c r="DR14" s="32"/>
@@ -4908,7 +4976,7 @@
         <v>13</v>
       </c>
       <c r="C15" s="34">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="D15" s="52">
         <v>46183</v>
@@ -5019,20 +5087,20 @@
       <c r="CY15" s="32"/>
       <c r="CZ15" s="32"/>
       <c r="DA15" s="32"/>
-      <c r="DB15" s="119"/>
-      <c r="DC15" s="119"/>
-      <c r="DD15" s="119"/>
-      <c r="DE15" s="119"/>
-      <c r="DF15" s="119"/>
-      <c r="DG15" s="119"/>
-      <c r="DH15" s="119"/>
-      <c r="DI15" s="119"/>
-      <c r="DJ15" s="119"/>
-      <c r="DK15" s="119"/>
-      <c r="DL15" s="119"/>
-      <c r="DM15" s="119"/>
-      <c r="DN15" s="119"/>
-      <c r="DO15" s="120"/>
+      <c r="DB15" s="131"/>
+      <c r="DC15" s="131"/>
+      <c r="DD15" s="131"/>
+      <c r="DE15" s="131"/>
+      <c r="DF15" s="131"/>
+      <c r="DG15" s="131"/>
+      <c r="DH15" s="131"/>
+      <c r="DI15" s="131"/>
+      <c r="DJ15" s="131"/>
+      <c r="DK15" s="131"/>
+      <c r="DL15" s="131"/>
+      <c r="DM15" s="131"/>
+      <c r="DN15" s="131"/>
+      <c r="DO15" s="132"/>
       <c r="DP15" s="114"/>
       <c r="DQ15" s="32"/>
       <c r="DR15" s="32"/>
@@ -5180,20 +5248,20 @@
       <c r="CY16" s="32"/>
       <c r="CZ16" s="32"/>
       <c r="DA16" s="32"/>
-      <c r="DB16" s="119"/>
-      <c r="DC16" s="119"/>
-      <c r="DD16" s="119"/>
-      <c r="DE16" s="119"/>
-      <c r="DF16" s="119"/>
-      <c r="DG16" s="119"/>
-      <c r="DH16" s="119"/>
-      <c r="DI16" s="119"/>
-      <c r="DJ16" s="119"/>
-      <c r="DK16" s="119"/>
-      <c r="DL16" s="119"/>
-      <c r="DM16" s="119"/>
-      <c r="DN16" s="119"/>
-      <c r="DO16" s="120"/>
+      <c r="DB16" s="131"/>
+      <c r="DC16" s="131"/>
+      <c r="DD16" s="131"/>
+      <c r="DE16" s="131"/>
+      <c r="DF16" s="131"/>
+      <c r="DG16" s="131"/>
+      <c r="DH16" s="131"/>
+      <c r="DI16" s="131"/>
+      <c r="DJ16" s="131"/>
+      <c r="DK16" s="131"/>
+      <c r="DL16" s="131"/>
+      <c r="DM16" s="131"/>
+      <c r="DN16" s="131"/>
+      <c r="DO16" s="132"/>
       <c r="DP16" s="114"/>
       <c r="DQ16" s="32"/>
       <c r="DR16" s="32"/>
@@ -5237,20 +5305,20 @@
         <f t="shared" si="65"/>
         <v/>
       </c>
-      <c r="DB17" s="119"/>
-      <c r="DC17" s="119"/>
-      <c r="DD17" s="119"/>
-      <c r="DE17" s="119"/>
-      <c r="DF17" s="119"/>
-      <c r="DG17" s="119"/>
-      <c r="DH17" s="119"/>
-      <c r="DI17" s="119"/>
-      <c r="DJ17" s="119"/>
-      <c r="DK17" s="119"/>
-      <c r="DL17" s="119"/>
-      <c r="DM17" s="119"/>
-      <c r="DN17" s="119"/>
-      <c r="DO17" s="120"/>
+      <c r="DB17" s="131"/>
+      <c r="DC17" s="131"/>
+      <c r="DD17" s="131"/>
+      <c r="DE17" s="131"/>
+      <c r="DF17" s="131"/>
+      <c r="DG17" s="131"/>
+      <c r="DH17" s="131"/>
+      <c r="DI17" s="131"/>
+      <c r="DJ17" s="131"/>
+      <c r="DK17" s="131"/>
+      <c r="DL17" s="131"/>
+      <c r="DM17" s="131"/>
+      <c r="DN17" s="131"/>
+      <c r="DO17" s="132"/>
       <c r="EK17" s="113">
         <f t="shared" si="68"/>
         <v>-10</v>
@@ -5377,20 +5445,20 @@
       <c r="CY18" s="32"/>
       <c r="CZ18" s="32"/>
       <c r="DA18" s="32"/>
-      <c r="DB18" s="119"/>
-      <c r="DC18" s="119"/>
-      <c r="DD18" s="119"/>
-      <c r="DE18" s="119"/>
-      <c r="DF18" s="119"/>
-      <c r="DG18" s="119"/>
-      <c r="DH18" s="119"/>
-      <c r="DI18" s="119"/>
-      <c r="DJ18" s="119"/>
-      <c r="DK18" s="119"/>
-      <c r="DL18" s="119"/>
-      <c r="DM18" s="119"/>
-      <c r="DN18" s="119"/>
-      <c r="DO18" s="120"/>
+      <c r="DB18" s="131"/>
+      <c r="DC18" s="131"/>
+      <c r="DD18" s="131"/>
+      <c r="DE18" s="131"/>
+      <c r="DF18" s="131"/>
+      <c r="DG18" s="131"/>
+      <c r="DH18" s="131"/>
+      <c r="DI18" s="131"/>
+      <c r="DJ18" s="131"/>
+      <c r="DK18" s="131"/>
+      <c r="DL18" s="131"/>
+      <c r="DM18" s="131"/>
+      <c r="DN18" s="131"/>
+      <c r="DO18" s="132"/>
       <c r="DP18" s="114"/>
       <c r="DQ18" s="32"/>
       <c r="DR18" s="32"/>
@@ -5538,20 +5606,20 @@
       <c r="CY19" s="32"/>
       <c r="CZ19" s="32"/>
       <c r="DA19" s="32"/>
-      <c r="DB19" s="119"/>
-      <c r="DC19" s="119"/>
-      <c r="DD19" s="119"/>
-      <c r="DE19" s="119"/>
-      <c r="DF19" s="119"/>
-      <c r="DG19" s="119"/>
-      <c r="DH19" s="119"/>
-      <c r="DI19" s="119"/>
-      <c r="DJ19" s="119"/>
-      <c r="DK19" s="119"/>
-      <c r="DL19" s="119"/>
-      <c r="DM19" s="119"/>
-      <c r="DN19" s="119"/>
-      <c r="DO19" s="120"/>
+      <c r="DB19" s="131"/>
+      <c r="DC19" s="131"/>
+      <c r="DD19" s="131"/>
+      <c r="DE19" s="131"/>
+      <c r="DF19" s="131"/>
+      <c r="DG19" s="131"/>
+      <c r="DH19" s="131"/>
+      <c r="DI19" s="131"/>
+      <c r="DJ19" s="131"/>
+      <c r="DK19" s="131"/>
+      <c r="DL19" s="131"/>
+      <c r="DM19" s="131"/>
+      <c r="DN19" s="131"/>
+      <c r="DO19" s="132"/>
       <c r="DP19" s="114"/>
       <c r="DQ19" s="32"/>
       <c r="DR19" s="32"/>
@@ -5696,20 +5764,20 @@
       <c r="CY20" s="32"/>
       <c r="CZ20" s="32"/>
       <c r="DA20" s="32"/>
-      <c r="DB20" s="119"/>
-      <c r="DC20" s="119"/>
-      <c r="DD20" s="119"/>
-      <c r="DE20" s="119"/>
-      <c r="DF20" s="119"/>
-      <c r="DG20" s="119"/>
-      <c r="DH20" s="119"/>
-      <c r="DI20" s="119"/>
-      <c r="DJ20" s="119"/>
-      <c r="DK20" s="119"/>
-      <c r="DL20" s="119"/>
-      <c r="DM20" s="119"/>
-      <c r="DN20" s="119"/>
-      <c r="DO20" s="120"/>
+      <c r="DB20" s="131"/>
+      <c r="DC20" s="131"/>
+      <c r="DD20" s="131"/>
+      <c r="DE20" s="131"/>
+      <c r="DF20" s="131"/>
+      <c r="DG20" s="131"/>
+      <c r="DH20" s="131"/>
+      <c r="DI20" s="131"/>
+      <c r="DJ20" s="131"/>
+      <c r="DK20" s="131"/>
+      <c r="DL20" s="131"/>
+      <c r="DM20" s="131"/>
+      <c r="DN20" s="131"/>
+      <c r="DO20" s="132"/>
       <c r="DP20" s="114"/>
       <c r="DQ20" s="32"/>
       <c r="DR20" s="32"/>
@@ -5851,20 +5919,20 @@
       <c r="CY21" s="42"/>
       <c r="CZ21" s="42"/>
       <c r="DA21" s="42"/>
-      <c r="DB21" s="119"/>
-      <c r="DC21" s="119"/>
-      <c r="DD21" s="119"/>
-      <c r="DE21" s="119"/>
-      <c r="DF21" s="119"/>
-      <c r="DG21" s="119"/>
-      <c r="DH21" s="119"/>
-      <c r="DI21" s="119"/>
-      <c r="DJ21" s="119"/>
-      <c r="DK21" s="119"/>
-      <c r="DL21" s="119"/>
-      <c r="DM21" s="119"/>
-      <c r="DN21" s="119"/>
-      <c r="DO21" s="120"/>
+      <c r="DB21" s="131"/>
+      <c r="DC21" s="131"/>
+      <c r="DD21" s="131"/>
+      <c r="DE21" s="131"/>
+      <c r="DF21" s="131"/>
+      <c r="DG21" s="131"/>
+      <c r="DH21" s="131"/>
+      <c r="DI21" s="131"/>
+      <c r="DJ21" s="131"/>
+      <c r="DK21" s="131"/>
+      <c r="DL21" s="131"/>
+      <c r="DM21" s="131"/>
+      <c r="DN21" s="131"/>
+      <c r="DO21" s="132"/>
       <c r="DP21" s="42"/>
       <c r="DQ21" s="42"/>
       <c r="DR21" s="42"/>
@@ -6012,20 +6080,20 @@
       <c r="CY22" s="32"/>
       <c r="CZ22" s="32"/>
       <c r="DA22" s="32"/>
-      <c r="DB22" s="119"/>
-      <c r="DC22" s="119"/>
-      <c r="DD22" s="119"/>
-      <c r="DE22" s="119"/>
-      <c r="DF22" s="119"/>
-      <c r="DG22" s="119"/>
-      <c r="DH22" s="119"/>
-      <c r="DI22" s="119"/>
-      <c r="DJ22" s="119"/>
-      <c r="DK22" s="119"/>
-      <c r="DL22" s="119"/>
-      <c r="DM22" s="119"/>
-      <c r="DN22" s="119"/>
-      <c r="DO22" s="120"/>
+      <c r="DB22" s="131"/>
+      <c r="DC22" s="131"/>
+      <c r="DD22" s="131"/>
+      <c r="DE22" s="131"/>
+      <c r="DF22" s="131"/>
+      <c r="DG22" s="131"/>
+      <c r="DH22" s="131"/>
+      <c r="DI22" s="131"/>
+      <c r="DJ22" s="131"/>
+      <c r="DK22" s="131"/>
+      <c r="DL22" s="131"/>
+      <c r="DM22" s="131"/>
+      <c r="DN22" s="131"/>
+      <c r="DO22" s="132"/>
       <c r="DP22" s="114"/>
       <c r="DQ22" s="32"/>
       <c r="DR22" s="32"/>
@@ -6173,20 +6241,20 @@
       <c r="CY23" s="32"/>
       <c r="CZ23" s="32"/>
       <c r="DA23" s="32"/>
-      <c r="DB23" s="119"/>
-      <c r="DC23" s="119"/>
-      <c r="DD23" s="119"/>
-      <c r="DE23" s="119"/>
-      <c r="DF23" s="119"/>
-      <c r="DG23" s="119"/>
-      <c r="DH23" s="119"/>
-      <c r="DI23" s="119"/>
-      <c r="DJ23" s="119"/>
-      <c r="DK23" s="119"/>
-      <c r="DL23" s="119"/>
-      <c r="DM23" s="119"/>
-      <c r="DN23" s="119"/>
-      <c r="DO23" s="120"/>
+      <c r="DB23" s="131"/>
+      <c r="DC23" s="131"/>
+      <c r="DD23" s="131"/>
+      <c r="DE23" s="131"/>
+      <c r="DF23" s="131"/>
+      <c r="DG23" s="131"/>
+      <c r="DH23" s="131"/>
+      <c r="DI23" s="131"/>
+      <c r="DJ23" s="131"/>
+      <c r="DK23" s="131"/>
+      <c r="DL23" s="131"/>
+      <c r="DM23" s="131"/>
+      <c r="DN23" s="131"/>
+      <c r="DO23" s="132"/>
       <c r="DP23" s="114"/>
       <c r="DQ23" s="32"/>
       <c r="DR23" s="32"/>
@@ -6328,20 +6396,20 @@
       <c r="CY24" s="47"/>
       <c r="CZ24" s="47"/>
       <c r="DA24" s="47"/>
-      <c r="DB24" s="119"/>
-      <c r="DC24" s="119"/>
-      <c r="DD24" s="119"/>
-      <c r="DE24" s="119"/>
-      <c r="DF24" s="119"/>
-      <c r="DG24" s="119"/>
-      <c r="DH24" s="119"/>
-      <c r="DI24" s="119"/>
-      <c r="DJ24" s="119"/>
-      <c r="DK24" s="119"/>
-      <c r="DL24" s="119"/>
-      <c r="DM24" s="119"/>
-      <c r="DN24" s="119"/>
-      <c r="DO24" s="120"/>
+      <c r="DB24" s="131"/>
+      <c r="DC24" s="131"/>
+      <c r="DD24" s="131"/>
+      <c r="DE24" s="131"/>
+      <c r="DF24" s="131"/>
+      <c r="DG24" s="131"/>
+      <c r="DH24" s="131"/>
+      <c r="DI24" s="131"/>
+      <c r="DJ24" s="131"/>
+      <c r="DK24" s="131"/>
+      <c r="DL24" s="131"/>
+      <c r="DM24" s="131"/>
+      <c r="DN24" s="131"/>
+      <c r="DO24" s="132"/>
       <c r="DP24" s="47"/>
       <c r="DQ24" s="47"/>
       <c r="DR24" s="47"/>
@@ -6489,20 +6557,20 @@
       <c r="CY25" s="32"/>
       <c r="CZ25" s="32"/>
       <c r="DA25" s="32"/>
-      <c r="DB25" s="119"/>
-      <c r="DC25" s="119"/>
-      <c r="DD25" s="119"/>
-      <c r="DE25" s="119"/>
-      <c r="DF25" s="119"/>
-      <c r="DG25" s="119"/>
-      <c r="DH25" s="119"/>
-      <c r="DI25" s="119"/>
-      <c r="DJ25" s="119"/>
-      <c r="DK25" s="119"/>
-      <c r="DL25" s="119"/>
-      <c r="DM25" s="119"/>
-      <c r="DN25" s="119"/>
-      <c r="DO25" s="120"/>
+      <c r="DB25" s="131"/>
+      <c r="DC25" s="131"/>
+      <c r="DD25" s="131"/>
+      <c r="DE25" s="131"/>
+      <c r="DF25" s="131"/>
+      <c r="DG25" s="131"/>
+      <c r="DH25" s="131"/>
+      <c r="DI25" s="131"/>
+      <c r="DJ25" s="131"/>
+      <c r="DK25" s="131"/>
+      <c r="DL25" s="131"/>
+      <c r="DM25" s="131"/>
+      <c r="DN25" s="131"/>
+      <c r="DO25" s="132"/>
       <c r="DP25" s="114"/>
       <c r="DQ25" s="32"/>
       <c r="DR25" s="32"/>
@@ -6650,20 +6718,20 @@
       <c r="CY26" s="32"/>
       <c r="CZ26" s="32"/>
       <c r="DA26" s="32"/>
-      <c r="DB26" s="119"/>
-      <c r="DC26" s="119"/>
-      <c r="DD26" s="119"/>
-      <c r="DE26" s="119"/>
-      <c r="DF26" s="119"/>
-      <c r="DG26" s="119"/>
-      <c r="DH26" s="119"/>
-      <c r="DI26" s="119"/>
-      <c r="DJ26" s="119"/>
-      <c r="DK26" s="119"/>
-      <c r="DL26" s="119"/>
-      <c r="DM26" s="119"/>
-      <c r="DN26" s="119"/>
-      <c r="DO26" s="120"/>
+      <c r="DB26" s="131"/>
+      <c r="DC26" s="131"/>
+      <c r="DD26" s="131"/>
+      <c r="DE26" s="131"/>
+      <c r="DF26" s="131"/>
+      <c r="DG26" s="131"/>
+      <c r="DH26" s="131"/>
+      <c r="DI26" s="131"/>
+      <c r="DJ26" s="131"/>
+      <c r="DK26" s="131"/>
+      <c r="DL26" s="131"/>
+      <c r="DM26" s="131"/>
+      <c r="DN26" s="131"/>
+      <c r="DO26" s="132"/>
       <c r="DP26" s="114"/>
       <c r="DQ26" s="32"/>
       <c r="DR26" s="32"/>
@@ -6811,20 +6879,20 @@
       <c r="CY27" s="32"/>
       <c r="CZ27" s="32"/>
       <c r="DA27" s="32"/>
-      <c r="DB27" s="119"/>
-      <c r="DC27" s="119"/>
-      <c r="DD27" s="119"/>
-      <c r="DE27" s="119"/>
-      <c r="DF27" s="119"/>
-      <c r="DG27" s="119"/>
-      <c r="DH27" s="119"/>
-      <c r="DI27" s="119"/>
-      <c r="DJ27" s="119"/>
-      <c r="DK27" s="119"/>
-      <c r="DL27" s="119"/>
-      <c r="DM27" s="119"/>
-      <c r="DN27" s="119"/>
-      <c r="DO27" s="120"/>
+      <c r="DB27" s="131"/>
+      <c r="DC27" s="131"/>
+      <c r="DD27" s="131"/>
+      <c r="DE27" s="131"/>
+      <c r="DF27" s="131"/>
+      <c r="DG27" s="131"/>
+      <c r="DH27" s="131"/>
+      <c r="DI27" s="131"/>
+      <c r="DJ27" s="131"/>
+      <c r="DK27" s="131"/>
+      <c r="DL27" s="131"/>
+      <c r="DM27" s="131"/>
+      <c r="DN27" s="131"/>
+      <c r="DO27" s="132"/>
       <c r="DP27" s="114"/>
       <c r="DQ27" s="32"/>
       <c r="DR27" s="32"/>
@@ -6972,20 +7040,20 @@
       <c r="CY28" s="32"/>
       <c r="CZ28" s="32"/>
       <c r="DA28" s="32"/>
-      <c r="DB28" s="119"/>
-      <c r="DC28" s="119"/>
-      <c r="DD28" s="119"/>
-      <c r="DE28" s="119"/>
-      <c r="DF28" s="119"/>
-      <c r="DG28" s="119"/>
-      <c r="DH28" s="119"/>
-      <c r="DI28" s="119"/>
-      <c r="DJ28" s="119"/>
-      <c r="DK28" s="119"/>
-      <c r="DL28" s="119"/>
-      <c r="DM28" s="119"/>
-      <c r="DN28" s="119"/>
-      <c r="DO28" s="120"/>
+      <c r="DB28" s="131"/>
+      <c r="DC28" s="131"/>
+      <c r="DD28" s="131"/>
+      <c r="DE28" s="131"/>
+      <c r="DF28" s="131"/>
+      <c r="DG28" s="131"/>
+      <c r="DH28" s="131"/>
+      <c r="DI28" s="131"/>
+      <c r="DJ28" s="131"/>
+      <c r="DK28" s="131"/>
+      <c r="DL28" s="131"/>
+      <c r="DM28" s="131"/>
+      <c r="DN28" s="131"/>
+      <c r="DO28" s="132"/>
       <c r="DP28" s="114"/>
       <c r="DQ28" s="32"/>
       <c r="DR28" s="32"/>
@@ -7127,20 +7195,20 @@
       <c r="CY29" s="47"/>
       <c r="CZ29" s="47"/>
       <c r="DA29" s="47"/>
-      <c r="DB29" s="119"/>
-      <c r="DC29" s="119"/>
-      <c r="DD29" s="119"/>
-      <c r="DE29" s="119"/>
-      <c r="DF29" s="119"/>
-      <c r="DG29" s="119"/>
-      <c r="DH29" s="119"/>
-      <c r="DI29" s="119"/>
-      <c r="DJ29" s="119"/>
-      <c r="DK29" s="119"/>
-      <c r="DL29" s="119"/>
-      <c r="DM29" s="119"/>
-      <c r="DN29" s="119"/>
-      <c r="DO29" s="120"/>
+      <c r="DB29" s="131"/>
+      <c r="DC29" s="131"/>
+      <c r="DD29" s="131"/>
+      <c r="DE29" s="131"/>
+      <c r="DF29" s="131"/>
+      <c r="DG29" s="131"/>
+      <c r="DH29" s="131"/>
+      <c r="DI29" s="131"/>
+      <c r="DJ29" s="131"/>
+      <c r="DK29" s="131"/>
+      <c r="DL29" s="131"/>
+      <c r="DM29" s="131"/>
+      <c r="DN29" s="131"/>
+      <c r="DO29" s="132"/>
       <c r="DP29" s="47"/>
       <c r="DQ29" s="47"/>
       <c r="DR29" s="47"/>
@@ -7288,20 +7356,20 @@
       <c r="CY30" s="32"/>
       <c r="CZ30" s="32"/>
       <c r="DA30" s="32"/>
-      <c r="DB30" s="119"/>
-      <c r="DC30" s="119"/>
-      <c r="DD30" s="119"/>
-      <c r="DE30" s="119"/>
-      <c r="DF30" s="119"/>
-      <c r="DG30" s="119"/>
-      <c r="DH30" s="119"/>
-      <c r="DI30" s="119"/>
-      <c r="DJ30" s="119"/>
-      <c r="DK30" s="119"/>
-      <c r="DL30" s="119"/>
-      <c r="DM30" s="119"/>
-      <c r="DN30" s="119"/>
-      <c r="DO30" s="120"/>
+      <c r="DB30" s="131"/>
+      <c r="DC30" s="131"/>
+      <c r="DD30" s="131"/>
+      <c r="DE30" s="131"/>
+      <c r="DF30" s="131"/>
+      <c r="DG30" s="131"/>
+      <c r="DH30" s="131"/>
+      <c r="DI30" s="131"/>
+      <c r="DJ30" s="131"/>
+      <c r="DK30" s="131"/>
+      <c r="DL30" s="131"/>
+      <c r="DM30" s="131"/>
+      <c r="DN30" s="131"/>
+      <c r="DO30" s="132"/>
       <c r="DP30" s="114"/>
       <c r="DQ30" s="32"/>
       <c r="DR30" s="32"/>
@@ -7449,20 +7517,20 @@
       <c r="CY31" s="32"/>
       <c r="CZ31" s="32"/>
       <c r="DA31" s="32"/>
-      <c r="DB31" s="119"/>
-      <c r="DC31" s="119"/>
-      <c r="DD31" s="119"/>
-      <c r="DE31" s="119"/>
-      <c r="DF31" s="119"/>
-      <c r="DG31" s="119"/>
-      <c r="DH31" s="119"/>
-      <c r="DI31" s="119"/>
-      <c r="DJ31" s="119"/>
-      <c r="DK31" s="119"/>
-      <c r="DL31" s="119"/>
-      <c r="DM31" s="119"/>
-      <c r="DN31" s="119"/>
-      <c r="DO31" s="120"/>
+      <c r="DB31" s="131"/>
+      <c r="DC31" s="131"/>
+      <c r="DD31" s="131"/>
+      <c r="DE31" s="131"/>
+      <c r="DF31" s="131"/>
+      <c r="DG31" s="131"/>
+      <c r="DH31" s="131"/>
+      <c r="DI31" s="131"/>
+      <c r="DJ31" s="131"/>
+      <c r="DK31" s="131"/>
+      <c r="DL31" s="131"/>
+      <c r="DM31" s="131"/>
+      <c r="DN31" s="131"/>
+      <c r="DO31" s="132"/>
       <c r="DP31" s="114"/>
       <c r="DQ31" s="32"/>
       <c r="DR31" s="32"/>
@@ -7610,20 +7678,20 @@
       <c r="CY32" s="32"/>
       <c r="CZ32" s="32"/>
       <c r="DA32" s="32"/>
-      <c r="DB32" s="119"/>
-      <c r="DC32" s="119"/>
-      <c r="DD32" s="119"/>
-      <c r="DE32" s="119"/>
-      <c r="DF32" s="119"/>
-      <c r="DG32" s="119"/>
-      <c r="DH32" s="119"/>
-      <c r="DI32" s="119"/>
-      <c r="DJ32" s="119"/>
-      <c r="DK32" s="119"/>
-      <c r="DL32" s="119"/>
-      <c r="DM32" s="119"/>
-      <c r="DN32" s="119"/>
-      <c r="DO32" s="120"/>
+      <c r="DB32" s="131"/>
+      <c r="DC32" s="131"/>
+      <c r="DD32" s="131"/>
+      <c r="DE32" s="131"/>
+      <c r="DF32" s="131"/>
+      <c r="DG32" s="131"/>
+      <c r="DH32" s="131"/>
+      <c r="DI32" s="131"/>
+      <c r="DJ32" s="131"/>
+      <c r="DK32" s="131"/>
+      <c r="DL32" s="131"/>
+      <c r="DM32" s="131"/>
+      <c r="DN32" s="131"/>
+      <c r="DO32" s="132"/>
       <c r="DP32" s="114"/>
       <c r="DQ32" s="32"/>
       <c r="DR32" s="32"/>
@@ -7771,20 +7839,20 @@
       <c r="CY33" s="32"/>
       <c r="CZ33" s="32"/>
       <c r="DA33" s="32"/>
-      <c r="DB33" s="119"/>
-      <c r="DC33" s="119"/>
-      <c r="DD33" s="119"/>
-      <c r="DE33" s="119"/>
-      <c r="DF33" s="119"/>
-      <c r="DG33" s="119"/>
-      <c r="DH33" s="119"/>
-      <c r="DI33" s="119"/>
-      <c r="DJ33" s="119"/>
-      <c r="DK33" s="119"/>
-      <c r="DL33" s="119"/>
-      <c r="DM33" s="119"/>
-      <c r="DN33" s="119"/>
-      <c r="DO33" s="120"/>
+      <c r="DB33" s="131"/>
+      <c r="DC33" s="131"/>
+      <c r="DD33" s="131"/>
+      <c r="DE33" s="131"/>
+      <c r="DF33" s="131"/>
+      <c r="DG33" s="131"/>
+      <c r="DH33" s="131"/>
+      <c r="DI33" s="131"/>
+      <c r="DJ33" s="131"/>
+      <c r="DK33" s="131"/>
+      <c r="DL33" s="131"/>
+      <c r="DM33" s="131"/>
+      <c r="DN33" s="131"/>
+      <c r="DO33" s="132"/>
       <c r="DP33" s="114"/>
       <c r="DQ33" s="32"/>
       <c r="DR33" s="32"/>
@@ -7926,20 +7994,20 @@
       <c r="CY34" s="47"/>
       <c r="CZ34" s="47"/>
       <c r="DA34" s="47"/>
-      <c r="DB34" s="119"/>
-      <c r="DC34" s="119"/>
-      <c r="DD34" s="119"/>
-      <c r="DE34" s="119"/>
-      <c r="DF34" s="119"/>
-      <c r="DG34" s="119"/>
-      <c r="DH34" s="119"/>
-      <c r="DI34" s="119"/>
-      <c r="DJ34" s="119"/>
-      <c r="DK34" s="119"/>
-      <c r="DL34" s="119"/>
-      <c r="DM34" s="119"/>
-      <c r="DN34" s="119"/>
-      <c r="DO34" s="120"/>
+      <c r="DB34" s="131"/>
+      <c r="DC34" s="131"/>
+      <c r="DD34" s="131"/>
+      <c r="DE34" s="131"/>
+      <c r="DF34" s="131"/>
+      <c r="DG34" s="131"/>
+      <c r="DH34" s="131"/>
+      <c r="DI34" s="131"/>
+      <c r="DJ34" s="131"/>
+      <c r="DK34" s="131"/>
+      <c r="DL34" s="131"/>
+      <c r="DM34" s="131"/>
+      <c r="DN34" s="131"/>
+      <c r="DO34" s="132"/>
       <c r="DP34" s="47"/>
       <c r="DQ34" s="47"/>
       <c r="DR34" s="47"/>
@@ -8087,20 +8155,20 @@
       <c r="CY35" s="32"/>
       <c r="CZ35" s="32"/>
       <c r="DA35" s="32"/>
-      <c r="DB35" s="119"/>
-      <c r="DC35" s="119"/>
-      <c r="DD35" s="119"/>
-      <c r="DE35" s="119"/>
-      <c r="DF35" s="119"/>
-      <c r="DG35" s="119"/>
-      <c r="DH35" s="119"/>
-      <c r="DI35" s="119"/>
-      <c r="DJ35" s="119"/>
-      <c r="DK35" s="119"/>
-      <c r="DL35" s="119"/>
-      <c r="DM35" s="119"/>
-      <c r="DN35" s="119"/>
-      <c r="DO35" s="120"/>
+      <c r="DB35" s="131"/>
+      <c r="DC35" s="131"/>
+      <c r="DD35" s="131"/>
+      <c r="DE35" s="131"/>
+      <c r="DF35" s="131"/>
+      <c r="DG35" s="131"/>
+      <c r="DH35" s="131"/>
+      <c r="DI35" s="131"/>
+      <c r="DJ35" s="131"/>
+      <c r="DK35" s="131"/>
+      <c r="DL35" s="131"/>
+      <c r="DM35" s="131"/>
+      <c r="DN35" s="131"/>
+      <c r="DO35" s="132"/>
       <c r="DP35" s="114"/>
       <c r="DQ35" s="32"/>
       <c r="DR35" s="32"/>
@@ -8248,20 +8316,20 @@
       <c r="CY36" s="32"/>
       <c r="CZ36" s="32"/>
       <c r="DA36" s="32"/>
-      <c r="DB36" s="119"/>
-      <c r="DC36" s="119"/>
-      <c r="DD36" s="119"/>
-      <c r="DE36" s="119"/>
-      <c r="DF36" s="119"/>
-      <c r="DG36" s="119"/>
-      <c r="DH36" s="119"/>
-      <c r="DI36" s="119"/>
-      <c r="DJ36" s="119"/>
-      <c r="DK36" s="119"/>
-      <c r="DL36" s="119"/>
-      <c r="DM36" s="119"/>
-      <c r="DN36" s="119"/>
-      <c r="DO36" s="120"/>
+      <c r="DB36" s="131"/>
+      <c r="DC36" s="131"/>
+      <c r="DD36" s="131"/>
+      <c r="DE36" s="131"/>
+      <c r="DF36" s="131"/>
+      <c r="DG36" s="131"/>
+      <c r="DH36" s="131"/>
+      <c r="DI36" s="131"/>
+      <c r="DJ36" s="131"/>
+      <c r="DK36" s="131"/>
+      <c r="DL36" s="131"/>
+      <c r="DM36" s="131"/>
+      <c r="DN36" s="131"/>
+      <c r="DO36" s="132"/>
       <c r="DP36" s="114"/>
       <c r="DQ36" s="32"/>
       <c r="DR36" s="32"/>
@@ -8409,20 +8477,20 @@
       <c r="CY37" s="32"/>
       <c r="CZ37" s="32"/>
       <c r="DA37" s="32"/>
-      <c r="DB37" s="119"/>
-      <c r="DC37" s="119"/>
-      <c r="DD37" s="119"/>
-      <c r="DE37" s="119"/>
-      <c r="DF37" s="119"/>
-      <c r="DG37" s="119"/>
-      <c r="DH37" s="119"/>
-      <c r="DI37" s="119"/>
-      <c r="DJ37" s="119"/>
-      <c r="DK37" s="119"/>
-      <c r="DL37" s="119"/>
-      <c r="DM37" s="119"/>
-      <c r="DN37" s="119"/>
-      <c r="DO37" s="120"/>
+      <c r="DB37" s="131"/>
+      <c r="DC37" s="131"/>
+      <c r="DD37" s="131"/>
+      <c r="DE37" s="131"/>
+      <c r="DF37" s="131"/>
+      <c r="DG37" s="131"/>
+      <c r="DH37" s="131"/>
+      <c r="DI37" s="131"/>
+      <c r="DJ37" s="131"/>
+      <c r="DK37" s="131"/>
+      <c r="DL37" s="131"/>
+      <c r="DM37" s="131"/>
+      <c r="DN37" s="131"/>
+      <c r="DO37" s="132"/>
       <c r="DP37" s="114"/>
       <c r="DQ37" s="32"/>
       <c r="DR37" s="32"/>
@@ -8570,20 +8638,20 @@
       <c r="CY38" s="32"/>
       <c r="CZ38" s="32"/>
       <c r="DA38" s="32"/>
-      <c r="DB38" s="119"/>
-      <c r="DC38" s="119"/>
-      <c r="DD38" s="119"/>
-      <c r="DE38" s="119"/>
-      <c r="DF38" s="119"/>
-      <c r="DG38" s="119"/>
-      <c r="DH38" s="119"/>
-      <c r="DI38" s="119"/>
-      <c r="DJ38" s="119"/>
-      <c r="DK38" s="119"/>
-      <c r="DL38" s="119"/>
-      <c r="DM38" s="119"/>
-      <c r="DN38" s="119"/>
-      <c r="DO38" s="120"/>
+      <c r="DB38" s="131"/>
+      <c r="DC38" s="131"/>
+      <c r="DD38" s="131"/>
+      <c r="DE38" s="131"/>
+      <c r="DF38" s="131"/>
+      <c r="DG38" s="131"/>
+      <c r="DH38" s="131"/>
+      <c r="DI38" s="131"/>
+      <c r="DJ38" s="131"/>
+      <c r="DK38" s="131"/>
+      <c r="DL38" s="131"/>
+      <c r="DM38" s="131"/>
+      <c r="DN38" s="131"/>
+      <c r="DO38" s="132"/>
       <c r="DP38" s="114"/>
       <c r="DQ38" s="32"/>
       <c r="DR38" s="32"/>
@@ -8731,20 +8799,20 @@
       <c r="CY39" s="32"/>
       <c r="CZ39" s="32"/>
       <c r="DA39" s="32"/>
-      <c r="DB39" s="119"/>
-      <c r="DC39" s="119"/>
-      <c r="DD39" s="119"/>
-      <c r="DE39" s="119"/>
-      <c r="DF39" s="119"/>
-      <c r="DG39" s="119"/>
-      <c r="DH39" s="119"/>
-      <c r="DI39" s="119"/>
-      <c r="DJ39" s="119"/>
-      <c r="DK39" s="119"/>
-      <c r="DL39" s="119"/>
-      <c r="DM39" s="119"/>
-      <c r="DN39" s="119"/>
-      <c r="DO39" s="120"/>
+      <c r="DB39" s="131"/>
+      <c r="DC39" s="131"/>
+      <c r="DD39" s="131"/>
+      <c r="DE39" s="131"/>
+      <c r="DF39" s="131"/>
+      <c r="DG39" s="131"/>
+      <c r="DH39" s="131"/>
+      <c r="DI39" s="131"/>
+      <c r="DJ39" s="131"/>
+      <c r="DK39" s="131"/>
+      <c r="DL39" s="131"/>
+      <c r="DM39" s="131"/>
+      <c r="DN39" s="131"/>
+      <c r="DO39" s="132"/>
       <c r="DP39" s="114"/>
       <c r="DQ39" s="32"/>
       <c r="DR39" s="32"/>
@@ -8886,20 +8954,20 @@
       <c r="CY40" s="28"/>
       <c r="CZ40" s="28"/>
       <c r="DA40" s="28"/>
-      <c r="DB40" s="119"/>
-      <c r="DC40" s="119"/>
-      <c r="DD40" s="119"/>
-      <c r="DE40" s="119"/>
-      <c r="DF40" s="119"/>
-      <c r="DG40" s="119"/>
-      <c r="DH40" s="119"/>
-      <c r="DI40" s="119"/>
-      <c r="DJ40" s="119"/>
-      <c r="DK40" s="119"/>
-      <c r="DL40" s="119"/>
-      <c r="DM40" s="119"/>
-      <c r="DN40" s="119"/>
-      <c r="DO40" s="120"/>
+      <c r="DB40" s="131"/>
+      <c r="DC40" s="131"/>
+      <c r="DD40" s="131"/>
+      <c r="DE40" s="131"/>
+      <c r="DF40" s="131"/>
+      <c r="DG40" s="131"/>
+      <c r="DH40" s="131"/>
+      <c r="DI40" s="131"/>
+      <c r="DJ40" s="131"/>
+      <c r="DK40" s="131"/>
+      <c r="DL40" s="131"/>
+      <c r="DM40" s="131"/>
+      <c r="DN40" s="131"/>
+      <c r="DO40" s="132"/>
       <c r="DP40" s="28"/>
       <c r="DQ40" s="28"/>
       <c r="DR40" s="28"/>
@@ -9047,20 +9115,20 @@
       <c r="CY41" s="32"/>
       <c r="CZ41" s="32"/>
       <c r="DA41" s="32"/>
-      <c r="DB41" s="119"/>
-      <c r="DC41" s="119"/>
-      <c r="DD41" s="119"/>
-      <c r="DE41" s="119"/>
-      <c r="DF41" s="119"/>
-      <c r="DG41" s="119"/>
-      <c r="DH41" s="119"/>
-      <c r="DI41" s="119"/>
-      <c r="DJ41" s="119"/>
-      <c r="DK41" s="119"/>
-      <c r="DL41" s="119"/>
-      <c r="DM41" s="119"/>
-      <c r="DN41" s="119"/>
-      <c r="DO41" s="120"/>
+      <c r="DB41" s="131"/>
+      <c r="DC41" s="131"/>
+      <c r="DD41" s="131"/>
+      <c r="DE41" s="131"/>
+      <c r="DF41" s="131"/>
+      <c r="DG41" s="131"/>
+      <c r="DH41" s="131"/>
+      <c r="DI41" s="131"/>
+      <c r="DJ41" s="131"/>
+      <c r="DK41" s="131"/>
+      <c r="DL41" s="131"/>
+      <c r="DM41" s="131"/>
+      <c r="DN41" s="131"/>
+      <c r="DO41" s="132"/>
       <c r="DP41" s="114"/>
       <c r="DQ41" s="32"/>
       <c r="DR41" s="32"/>
@@ -9208,20 +9276,20 @@
       <c r="CY42" s="32"/>
       <c r="CZ42" s="32"/>
       <c r="DA42" s="32"/>
-      <c r="DB42" s="119"/>
-      <c r="DC42" s="119"/>
-      <c r="DD42" s="119"/>
-      <c r="DE42" s="119"/>
-      <c r="DF42" s="119"/>
-      <c r="DG42" s="119"/>
-      <c r="DH42" s="119"/>
-      <c r="DI42" s="119"/>
-      <c r="DJ42" s="119"/>
-      <c r="DK42" s="119"/>
-      <c r="DL42" s="119"/>
-      <c r="DM42" s="119"/>
-      <c r="DN42" s="119"/>
-      <c r="DO42" s="120"/>
+      <c r="DB42" s="131"/>
+      <c r="DC42" s="131"/>
+      <c r="DD42" s="131"/>
+      <c r="DE42" s="131"/>
+      <c r="DF42" s="131"/>
+      <c r="DG42" s="131"/>
+      <c r="DH42" s="131"/>
+      <c r="DI42" s="131"/>
+      <c r="DJ42" s="131"/>
+      <c r="DK42" s="131"/>
+      <c r="DL42" s="131"/>
+      <c r="DM42" s="131"/>
+      <c r="DN42" s="131"/>
+      <c r="DO42" s="132"/>
       <c r="DP42" s="114"/>
       <c r="DQ42" s="32"/>
       <c r="DR42" s="32"/>
@@ -9369,20 +9437,20 @@
       <c r="CY43" s="32"/>
       <c r="CZ43" s="32"/>
       <c r="DA43" s="32"/>
-      <c r="DB43" s="119"/>
-      <c r="DC43" s="119"/>
-      <c r="DD43" s="119"/>
-      <c r="DE43" s="119"/>
-      <c r="DF43" s="119"/>
-      <c r="DG43" s="119"/>
-      <c r="DH43" s="119"/>
-      <c r="DI43" s="119"/>
-      <c r="DJ43" s="119"/>
-      <c r="DK43" s="119"/>
-      <c r="DL43" s="119"/>
-      <c r="DM43" s="119"/>
-      <c r="DN43" s="119"/>
-      <c r="DO43" s="120"/>
+      <c r="DB43" s="131"/>
+      <c r="DC43" s="131"/>
+      <c r="DD43" s="131"/>
+      <c r="DE43" s="131"/>
+      <c r="DF43" s="131"/>
+      <c r="DG43" s="131"/>
+      <c r="DH43" s="131"/>
+      <c r="DI43" s="131"/>
+      <c r="DJ43" s="131"/>
+      <c r="DK43" s="131"/>
+      <c r="DL43" s="131"/>
+      <c r="DM43" s="131"/>
+      <c r="DN43" s="131"/>
+      <c r="DO43" s="132"/>
       <c r="DP43" s="114"/>
       <c r="DQ43" s="32"/>
       <c r="DR43" s="32"/>
@@ -9527,20 +9595,20 @@
       <c r="CY44" s="32"/>
       <c r="CZ44" s="32"/>
       <c r="DA44" s="32"/>
-      <c r="DB44" s="119"/>
-      <c r="DC44" s="119"/>
-      <c r="DD44" s="119"/>
-      <c r="DE44" s="119"/>
-      <c r="DF44" s="119"/>
-      <c r="DG44" s="119"/>
-      <c r="DH44" s="119"/>
-      <c r="DI44" s="119"/>
-      <c r="DJ44" s="119"/>
-      <c r="DK44" s="119"/>
-      <c r="DL44" s="119"/>
-      <c r="DM44" s="119"/>
-      <c r="DN44" s="119"/>
-      <c r="DO44" s="120"/>
+      <c r="DB44" s="131"/>
+      <c r="DC44" s="131"/>
+      <c r="DD44" s="131"/>
+      <c r="DE44" s="131"/>
+      <c r="DF44" s="131"/>
+      <c r="DG44" s="131"/>
+      <c r="DH44" s="131"/>
+      <c r="DI44" s="131"/>
+      <c r="DJ44" s="131"/>
+      <c r="DK44" s="131"/>
+      <c r="DL44" s="131"/>
+      <c r="DM44" s="131"/>
+      <c r="DN44" s="131"/>
+      <c r="DO44" s="132"/>
       <c r="DP44" s="114"/>
       <c r="DQ44" s="32"/>
       <c r="DR44" s="32"/>
@@ -9584,20 +9652,20 @@
         <f t="shared" si="65"/>
         <v/>
       </c>
-      <c r="DB45" s="119"/>
-      <c r="DC45" s="119"/>
-      <c r="DD45" s="119"/>
-      <c r="DE45" s="119"/>
-      <c r="DF45" s="119"/>
-      <c r="DG45" s="119"/>
-      <c r="DH45" s="119"/>
-      <c r="DI45" s="119"/>
-      <c r="DJ45" s="119"/>
-      <c r="DK45" s="119"/>
-      <c r="DL45" s="119"/>
-      <c r="DM45" s="119"/>
-      <c r="DN45" s="119"/>
-      <c r="DO45" s="120"/>
+      <c r="DB45" s="131"/>
+      <c r="DC45" s="131"/>
+      <c r="DD45" s="131"/>
+      <c r="DE45" s="131"/>
+      <c r="DF45" s="131"/>
+      <c r="DG45" s="131"/>
+      <c r="DH45" s="131"/>
+      <c r="DI45" s="131"/>
+      <c r="DJ45" s="131"/>
+      <c r="DK45" s="131"/>
+      <c r="DL45" s="131"/>
+      <c r="DM45" s="131"/>
+      <c r="DN45" s="131"/>
+      <c r="DO45" s="132"/>
       <c r="EK45" s="113">
         <f t="shared" si="72"/>
         <v>2</v>
@@ -9724,20 +9792,20 @@
       <c r="CY46" s="32"/>
       <c r="CZ46" s="32"/>
       <c r="DA46" s="32"/>
-      <c r="DB46" s="119"/>
-      <c r="DC46" s="119"/>
-      <c r="DD46" s="119"/>
-      <c r="DE46" s="119"/>
-      <c r="DF46" s="119"/>
-      <c r="DG46" s="119"/>
-      <c r="DH46" s="119"/>
-      <c r="DI46" s="119"/>
-      <c r="DJ46" s="119"/>
-      <c r="DK46" s="119"/>
-      <c r="DL46" s="119"/>
-      <c r="DM46" s="119"/>
-      <c r="DN46" s="119"/>
-      <c r="DO46" s="120"/>
+      <c r="DB46" s="131"/>
+      <c r="DC46" s="131"/>
+      <c r="DD46" s="131"/>
+      <c r="DE46" s="131"/>
+      <c r="DF46" s="131"/>
+      <c r="DG46" s="131"/>
+      <c r="DH46" s="131"/>
+      <c r="DI46" s="131"/>
+      <c r="DJ46" s="131"/>
+      <c r="DK46" s="131"/>
+      <c r="DL46" s="131"/>
+      <c r="DM46" s="131"/>
+      <c r="DN46" s="131"/>
+      <c r="DO46" s="132"/>
       <c r="DP46" s="114"/>
       <c r="DQ46" s="32"/>
       <c r="DR46" s="32"/>
@@ -9885,20 +9953,20 @@
       <c r="CY47" s="32"/>
       <c r="CZ47" s="32"/>
       <c r="DA47" s="32"/>
-      <c r="DB47" s="119"/>
-      <c r="DC47" s="119"/>
-      <c r="DD47" s="119"/>
-      <c r="DE47" s="119"/>
-      <c r="DF47" s="119"/>
-      <c r="DG47" s="119"/>
-      <c r="DH47" s="119"/>
-      <c r="DI47" s="119"/>
-      <c r="DJ47" s="119"/>
-      <c r="DK47" s="119"/>
-      <c r="DL47" s="119"/>
-      <c r="DM47" s="119"/>
-      <c r="DN47" s="119"/>
-      <c r="DO47" s="120"/>
+      <c r="DB47" s="131"/>
+      <c r="DC47" s="131"/>
+      <c r="DD47" s="131"/>
+      <c r="DE47" s="131"/>
+      <c r="DF47" s="131"/>
+      <c r="DG47" s="131"/>
+      <c r="DH47" s="131"/>
+      <c r="DI47" s="131"/>
+      <c r="DJ47" s="131"/>
+      <c r="DK47" s="131"/>
+      <c r="DL47" s="131"/>
+      <c r="DM47" s="131"/>
+      <c r="DN47" s="131"/>
+      <c r="DO47" s="132"/>
       <c r="DP47" s="114"/>
       <c r="DQ47" s="32"/>
       <c r="DR47" s="32"/>
@@ -10041,20 +10109,20 @@
       <c r="CY48" s="32"/>
       <c r="CZ48" s="32"/>
       <c r="DA48" s="32"/>
-      <c r="DB48" s="119"/>
-      <c r="DC48" s="119"/>
-      <c r="DD48" s="119"/>
-      <c r="DE48" s="119"/>
-      <c r="DF48" s="119"/>
-      <c r="DG48" s="119"/>
-      <c r="DH48" s="119"/>
-      <c r="DI48" s="119"/>
-      <c r="DJ48" s="119"/>
-      <c r="DK48" s="119"/>
-      <c r="DL48" s="119"/>
-      <c r="DM48" s="119"/>
-      <c r="DN48" s="119"/>
-      <c r="DO48" s="120"/>
+      <c r="DB48" s="131"/>
+      <c r="DC48" s="131"/>
+      <c r="DD48" s="131"/>
+      <c r="DE48" s="131"/>
+      <c r="DF48" s="131"/>
+      <c r="DG48" s="131"/>
+      <c r="DH48" s="131"/>
+      <c r="DI48" s="131"/>
+      <c r="DJ48" s="131"/>
+      <c r="DK48" s="131"/>
+      <c r="DL48" s="131"/>
+      <c r="DM48" s="131"/>
+      <c r="DN48" s="131"/>
+      <c r="DO48" s="132"/>
       <c r="DP48" s="114"/>
       <c r="DQ48" s="32"/>
       <c r="DR48" s="32"/>
@@ -10197,20 +10265,20 @@
       <c r="CY49" s="32"/>
       <c r="CZ49" s="32"/>
       <c r="DA49" s="32"/>
-      <c r="DB49" s="119"/>
-      <c r="DC49" s="119"/>
-      <c r="DD49" s="119"/>
-      <c r="DE49" s="119"/>
-      <c r="DF49" s="119"/>
-      <c r="DG49" s="119"/>
-      <c r="DH49" s="119"/>
-      <c r="DI49" s="119"/>
-      <c r="DJ49" s="119"/>
-      <c r="DK49" s="119"/>
-      <c r="DL49" s="119"/>
-      <c r="DM49" s="119"/>
-      <c r="DN49" s="119"/>
-      <c r="DO49" s="120"/>
+      <c r="DB49" s="131"/>
+      <c r="DC49" s="131"/>
+      <c r="DD49" s="131"/>
+      <c r="DE49" s="131"/>
+      <c r="DF49" s="131"/>
+      <c r="DG49" s="131"/>
+      <c r="DH49" s="131"/>
+      <c r="DI49" s="131"/>
+      <c r="DJ49" s="131"/>
+      <c r="DK49" s="131"/>
+      <c r="DL49" s="131"/>
+      <c r="DM49" s="131"/>
+      <c r="DN49" s="131"/>
+      <c r="DO49" s="132"/>
       <c r="DP49" s="114"/>
       <c r="DQ49" s="32"/>
       <c r="DR49" s="32"/>
@@ -10353,20 +10421,20 @@
       <c r="CY50" s="32"/>
       <c r="CZ50" s="32"/>
       <c r="DA50" s="32"/>
-      <c r="DB50" s="119"/>
-      <c r="DC50" s="119"/>
-      <c r="DD50" s="119"/>
-      <c r="DE50" s="119"/>
-      <c r="DF50" s="119"/>
-      <c r="DG50" s="119"/>
-      <c r="DH50" s="119"/>
-      <c r="DI50" s="119"/>
-      <c r="DJ50" s="119"/>
-      <c r="DK50" s="119"/>
-      <c r="DL50" s="119"/>
-      <c r="DM50" s="119"/>
-      <c r="DN50" s="119"/>
-      <c r="DO50" s="120"/>
+      <c r="DB50" s="131"/>
+      <c r="DC50" s="131"/>
+      <c r="DD50" s="131"/>
+      <c r="DE50" s="131"/>
+      <c r="DF50" s="131"/>
+      <c r="DG50" s="131"/>
+      <c r="DH50" s="131"/>
+      <c r="DI50" s="131"/>
+      <c r="DJ50" s="131"/>
+      <c r="DK50" s="131"/>
+      <c r="DL50" s="131"/>
+      <c r="DM50" s="131"/>
+      <c r="DN50" s="131"/>
+      <c r="DO50" s="132"/>
       <c r="DP50" s="114"/>
       <c r="DQ50" s="32"/>
       <c r="DR50" s="32"/>
@@ -10509,20 +10577,20 @@
       <c r="CY51" s="32"/>
       <c r="CZ51" s="32"/>
       <c r="DA51" s="32"/>
-      <c r="DB51" s="119"/>
-      <c r="DC51" s="119"/>
-      <c r="DD51" s="119"/>
-      <c r="DE51" s="119"/>
-      <c r="DF51" s="119"/>
-      <c r="DG51" s="119"/>
-      <c r="DH51" s="119"/>
-      <c r="DI51" s="119"/>
-      <c r="DJ51" s="119"/>
-      <c r="DK51" s="119"/>
-      <c r="DL51" s="119"/>
-      <c r="DM51" s="119"/>
-      <c r="DN51" s="119"/>
-      <c r="DO51" s="120"/>
+      <c r="DB51" s="131"/>
+      <c r="DC51" s="131"/>
+      <c r="DD51" s="131"/>
+      <c r="DE51" s="131"/>
+      <c r="DF51" s="131"/>
+      <c r="DG51" s="131"/>
+      <c r="DH51" s="131"/>
+      <c r="DI51" s="131"/>
+      <c r="DJ51" s="131"/>
+      <c r="DK51" s="131"/>
+      <c r="DL51" s="131"/>
+      <c r="DM51" s="131"/>
+      <c r="DN51" s="131"/>
+      <c r="DO51" s="132"/>
       <c r="DP51" s="114"/>
       <c r="DQ51" s="32"/>
       <c r="DR51" s="32"/>
@@ -10665,20 +10733,20 @@
       <c r="CY52" s="32"/>
       <c r="CZ52" s="32"/>
       <c r="DA52" s="32"/>
-      <c r="DB52" s="119"/>
-      <c r="DC52" s="119"/>
-      <c r="DD52" s="119"/>
-      <c r="DE52" s="119"/>
-      <c r="DF52" s="119"/>
-      <c r="DG52" s="119"/>
-      <c r="DH52" s="119"/>
-      <c r="DI52" s="119"/>
-      <c r="DJ52" s="119"/>
-      <c r="DK52" s="119"/>
-      <c r="DL52" s="119"/>
-      <c r="DM52" s="119"/>
-      <c r="DN52" s="119"/>
-      <c r="DO52" s="120"/>
+      <c r="DB52" s="131"/>
+      <c r="DC52" s="131"/>
+      <c r="DD52" s="131"/>
+      <c r="DE52" s="131"/>
+      <c r="DF52" s="131"/>
+      <c r="DG52" s="131"/>
+      <c r="DH52" s="131"/>
+      <c r="DI52" s="131"/>
+      <c r="DJ52" s="131"/>
+      <c r="DK52" s="131"/>
+      <c r="DL52" s="131"/>
+      <c r="DM52" s="131"/>
+      <c r="DN52" s="131"/>
+      <c r="DO52" s="132"/>
       <c r="DP52" s="114"/>
       <c r="DQ52" s="32"/>
       <c r="DR52" s="32"/>
@@ -10821,20 +10889,20 @@
       <c r="CY53" s="32"/>
       <c r="CZ53" s="32"/>
       <c r="DA53" s="32"/>
-      <c r="DB53" s="119"/>
-      <c r="DC53" s="119"/>
-      <c r="DD53" s="119"/>
-      <c r="DE53" s="119"/>
-      <c r="DF53" s="119"/>
-      <c r="DG53" s="119"/>
-      <c r="DH53" s="119"/>
-      <c r="DI53" s="119"/>
-      <c r="DJ53" s="119"/>
-      <c r="DK53" s="119"/>
-      <c r="DL53" s="119"/>
-      <c r="DM53" s="119"/>
-      <c r="DN53" s="119"/>
-      <c r="DO53" s="120"/>
+      <c r="DB53" s="131"/>
+      <c r="DC53" s="131"/>
+      <c r="DD53" s="131"/>
+      <c r="DE53" s="131"/>
+      <c r="DF53" s="131"/>
+      <c r="DG53" s="131"/>
+      <c r="DH53" s="131"/>
+      <c r="DI53" s="131"/>
+      <c r="DJ53" s="131"/>
+      <c r="DK53" s="131"/>
+      <c r="DL53" s="131"/>
+      <c r="DM53" s="131"/>
+      <c r="DN53" s="131"/>
+      <c r="DO53" s="132"/>
       <c r="DP53" s="114"/>
       <c r="DQ53" s="32"/>
       <c r="DR53" s="32"/>
@@ -10969,20 +11037,20 @@
       <c r="CY54" s="32"/>
       <c r="CZ54" s="32"/>
       <c r="DA54" s="32"/>
-      <c r="DB54" s="119"/>
-      <c r="DC54" s="119"/>
-      <c r="DD54" s="119"/>
-      <c r="DE54" s="119"/>
-      <c r="DF54" s="119"/>
-      <c r="DG54" s="119"/>
-      <c r="DH54" s="119"/>
-      <c r="DI54" s="119"/>
-      <c r="DJ54" s="119"/>
-      <c r="DK54" s="119"/>
-      <c r="DL54" s="119"/>
-      <c r="DM54" s="119"/>
-      <c r="DN54" s="119"/>
-      <c r="DO54" s="120"/>
+      <c r="DB54" s="131"/>
+      <c r="DC54" s="131"/>
+      <c r="DD54" s="131"/>
+      <c r="DE54" s="131"/>
+      <c r="DF54" s="131"/>
+      <c r="DG54" s="131"/>
+      <c r="DH54" s="131"/>
+      <c r="DI54" s="131"/>
+      <c r="DJ54" s="131"/>
+      <c r="DK54" s="131"/>
+      <c r="DL54" s="131"/>
+      <c r="DM54" s="131"/>
+      <c r="DN54" s="131"/>
+      <c r="DO54" s="132"/>
       <c r="DP54" s="114"/>
       <c r="DQ54" s="32"/>
       <c r="DR54" s="32"/>
@@ -11010,12 +11078,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="DX4:EJ4"/>
-    <mergeCell ref="E5:E6"/>
     <mergeCell ref="P2:Y2"/>
     <mergeCell ref="P1:Y1"/>
     <mergeCell ref="H1:N1"/>
@@ -11025,6 +11087,12 @@
     <mergeCell ref="AJ4:BM4"/>
     <mergeCell ref="BN4:CR4"/>
     <mergeCell ref="CS4:DW4"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="DX4:EJ4"/>
+    <mergeCell ref="E5:E6"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C54">
     <cfRule type="dataBar" priority="61">
@@ -11116,14 +11184,14 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DB9">
-    <cfRule type="expression" dxfId="11" priority="155">
+    <cfRule type="expression" dxfId="11" priority="152">
+      <formula>AND(TODAY()&gt;=DF$5, TODAY()&lt;DG$5)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="10" priority="155">
       <formula>AND(task_start&lt;=DF$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=DF$5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="156" stopIfTrue="1">
+    <cfRule type="expression" dxfId="9" priority="156" stopIfTrue="1">
       <formula>AND(task_end&gt;=DF$5,task_start&lt;DG$5)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="9" priority="152">
-      <formula>AND(TODAY()&gt;=DF$5, TODAY()&lt;DG$5)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EC9:EC16 EJ9:EJ16 EC41:EC44 EJ41:EJ44">
@@ -11219,151 +11287,296 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E561D383-4357-A141-8828-FF5301F4BB1B}">
-  <dimension ref="A1:D15"/>
+  <dimension ref="A2:E31"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="17.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.1640625" customWidth="1"/>
+    <col min="4" max="4" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A1" t="s">
-        <v>59</v>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="D2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E2">
+        <f>COUNTIF(A8:A1048576,"&lt;&gt;")</f>
+        <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C2" t="s">
-        <v>71</v>
-      </c>
-      <c r="D2">
-        <f>COUNTIF(A2:A1048576,"&lt;&gt;")</f>
-        <v>14</v>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="D3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E3">
+        <f>E2*2500</f>
+        <v>60000</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D3">
-        <f>D2*2500</f>
-        <v>35000</v>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="D4" t="s">
+        <v>73</v>
+      </c>
+      <c r="E4">
+        <f>100000-E3</f>
+        <v>40000</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A4" t="s">
-        <v>62</v>
-      </c>
-      <c r="C4" t="s">
-        <v>73</v>
-      </c>
-      <c r="D4">
-        <f>100000-D3</f>
-        <v>65000</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A5" t="s">
-        <v>63</v>
-      </c>
-      <c r="C5" t="s">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="D5" t="s">
         <v>77</v>
       </c>
-      <c r="D5" t="e">
+      <c r="E5" t="e">
         <f>SUM([1]Sessions_data!$B$2:$B$1048576)</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A6" t="s">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A7" t="s">
+        <v>59</v>
+      </c>
+      <c r="B7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C7" t="s">
+        <v>90</v>
+      </c>
+      <c r="D7" t="s">
+        <v>86</v>
+      </c>
+      <c r="E7" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A8" t="s">
+        <v>60</v>
+      </c>
+      <c r="B8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A9" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A10" t="s">
+        <v>62</v>
+      </c>
+      <c r="B10" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A11" t="s">
+        <v>63</v>
+      </c>
+      <c r="B11" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A12" t="s">
         <v>64</v>
       </c>
+      <c r="B12" t="s">
+        <v>84</v>
+      </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A7" t="s">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A13" t="s">
         <v>65</v>
       </c>
+      <c r="B13" t="s">
+        <v>84</v>
+      </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A8" t="s">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A14" t="s">
         <v>66</v>
       </c>
+      <c r="B14" t="s">
+        <v>85</v>
+      </c>
+      <c r="C14" s="133" t="s">
+        <v>91</v>
+      </c>
+      <c r="D14">
+        <v>2</v>
+      </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A9" t="s">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A15" t="s">
         <v>67</v>
       </c>
+      <c r="B15" t="s">
+        <v>85</v>
+      </c>
+      <c r="C15" s="134" t="s">
+        <v>92</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A10" t="s">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A16" t="s">
         <v>68</v>
       </c>
+      <c r="B16" t="s">
+        <v>85</v>
+      </c>
+      <c r="C16" s="134" t="s">
+        <v>93</v>
+      </c>
+      <c r="D16">
+        <v>3</v>
+      </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A11" t="s">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A17" t="s">
         <v>69</v>
       </c>
+      <c r="B17" t="s">
+        <v>85</v>
+      </c>
+      <c r="C17" s="134" t="s">
+        <v>94</v>
+      </c>
+      <c r="D17">
+        <v>4</v>
+      </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A12" t="s">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A18" t="s">
         <v>70</v>
       </c>
+      <c r="B18" t="s">
+        <v>84</v>
+      </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A13" t="s">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A19" t="s">
         <v>76</v>
       </c>
+      <c r="B19" t="s">
+        <v>84</v>
+      </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A14" t="s">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A20" t="s">
         <v>74</v>
       </c>
+      <c r="B20" t="s">
+        <v>84</v>
+      </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A15" t="s">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A21" t="s">
         <v>75</v>
+      </c>
+      <c r="B21" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A22" t="s">
+        <v>78</v>
+      </c>
+      <c r="B22" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A23" t="s">
+        <v>79</v>
+      </c>
+      <c r="B23" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A24" t="s">
+        <v>80</v>
+      </c>
+      <c r="B24" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A25" t="s">
+        <v>81</v>
+      </c>
+      <c r="B25" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A26" t="s">
+        <v>82</v>
+      </c>
+      <c r="B26" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A27" t="s">
+        <v>88</v>
+      </c>
+      <c r="B27" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A28" t="s">
+        <v>89</v>
+      </c>
+      <c r="B28" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A29" t="s">
+        <v>95</v>
+      </c>
+      <c r="B29" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A30" t="s">
+        <v>96</v>
+      </c>
+      <c r="B30" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A31" t="s">
+        <v>97</v>
+      </c>
+      <c r="B31" t="s">
+        <v>84</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C15" r:id="rId1" xr:uid="{46183A95-0072-454C-9B26-8DD5043ECE48}"/>
+    <hyperlink ref="C16" r:id="rId2" xr:uid="{C3ADE675-AFD6-3E44-A0EC-47AAEAD6169A}"/>
+    <hyperlink ref="C17" r:id="rId3" xr:uid="{B2725EE1-2C0D-A440-8ABB-AF14054D6FF3}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Url xsi:nil="true"/>
-      <Description xsi:nil="true"/>
-    </Image>
-    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
-    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ImageTagsTaxHTField>
-    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
-    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010079F111ED35F8CC479449609E8A0923A6" ma:contentTypeVersion="28" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="60f5a4f2d2b0abadcf532d48ebf9cb71">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xmlns:ns3="16c05727-aa75-4e4a-9b5f-8a80a1165891" xmlns:ns4="230e9df3-be65-4c73-a93b-d1236ebd677e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7dd78129e6a1811f84807ad11c651531" ns1:_="" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -11675,10 +11888,52 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Url xsi:nil="true"/>
+      <Description xsi:nil="true"/>
+    </Image>
+    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
+    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ImageTagsTaxHTField>
+    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
+    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97245281-08F3-4104-84BD-39F3D8CFB195}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A09426A3-87E9-4865-8A6C-3456B026AE03}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
+    <ds:schemaRef ds:uri="16c05727-aa75-4e4a-9b5f-8a80a1165891"/>
+    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -11703,22 +11958,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A09426A3-87E9-4865-8A6C-3456B026AE03}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97245281-08F3-4104-84BD-39F3D8CFB195}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
-    <ds:schemaRef ds:uri="16c05727-aa75-4e4a-9b5f-8a80a1165891"/>
-    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
